--- a/server/data/DATA B2B LADO.xlsx
+++ b/server/data/DATA B2B LADO.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1789" uniqueCount="679">
   <si>
     <t>Mã KH</t>
   </si>
@@ -302,6 +302,1653 @@
   </si>
   <si>
     <t>87 Đường Số 17 Khu B,Phường An Phú,Thành Phố Thủ Đức,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP012</t>
+  </si>
+  <si>
+    <t>Aion Spa &amp; Clinic</t>
+  </si>
+  <si>
+    <t>668 Đường Lê Đức Thọ,Phường 15,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP013</t>
+  </si>
+  <si>
+    <t>Kim Beauty Spa &amp; Phun Xăm</t>
+  </si>
+  <si>
+    <t>Hẻm 616 Lê Đức Thọ,Phường 15,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP014</t>
+  </si>
+  <si>
+    <t>Thúy Nga Spa &amp; Beauty</t>
+  </si>
+  <si>
+    <t>688/22B Đường Lê Đức Thọ,Phường 15,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP015</t>
+  </si>
+  <si>
+    <t>Sparrows Wedding Event</t>
+  </si>
+  <si>
+    <t>Phường 3,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP016</t>
+  </si>
+  <si>
+    <t>Trung Tâm Thẩm Mỹ Viện Mai Phuong Spa Hair Salon</t>
+  </si>
+  <si>
+    <t>622 Ngõ Thống Nhất,Phường 15,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP017</t>
+  </si>
+  <si>
+    <t>Light Spark Production</t>
+  </si>
+  <si>
+    <t>Phường 10,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP018</t>
+  </si>
+  <si>
+    <t>Spad Company Limited</t>
+  </si>
+  <si>
+    <t>52/9 Ngõ Quang Trung,Phường 10,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP019</t>
+  </si>
+  <si>
+    <t>Olee Space</t>
+  </si>
+  <si>
+    <t>Phường 14,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP020</t>
+  </si>
+  <si>
+    <t>Sửa Xe Hảo Spark</t>
+  </si>
+  <si>
+    <t>38 Nguyễn Oanh,Phường 1,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP021</t>
+  </si>
+  <si>
+    <t>The Space Coffee &amp; Tea</t>
+  </si>
+  <si>
+    <t>Phường 8,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP022</t>
+  </si>
+  <si>
+    <t>Sò Spa</t>
+  </si>
+  <si>
+    <t>Phường 17,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP023</t>
+  </si>
+  <si>
+    <t>Spa Trị Liệu</t>
+  </si>
+  <si>
+    <t>SP024</t>
+  </si>
+  <si>
+    <t>Spa Thiên Y</t>
+  </si>
+  <si>
+    <t>SP025</t>
+  </si>
+  <si>
+    <t>Diễm Kiều Clinic &amp; Spa</t>
+  </si>
+  <si>
+    <t>Phường 6,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP026</t>
+  </si>
+  <si>
+    <t>Mon Spa</t>
+  </si>
+  <si>
+    <t>110/2/2D3,Phường 6,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP027</t>
+  </si>
+  <si>
+    <t>Vula Spa</t>
+  </si>
+  <si>
+    <t>14 Nguyễn Văn Lượng,Phường 6,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP028</t>
+  </si>
+  <si>
+    <t>Đèn Livestream-Chụp Hình-Spa: Thư Min Shop</t>
+  </si>
+  <si>
+    <t>Hẻm 162 Cây Trâm,Phường 8,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP029</t>
+  </si>
+  <si>
+    <t>Beauty Spa</t>
+  </si>
+  <si>
+    <t>SP030</t>
+  </si>
+  <si>
+    <t>Linh Spa</t>
+  </si>
+  <si>
+    <t>SP031</t>
+  </si>
+  <si>
+    <t>Mynn Spa</t>
+  </si>
+  <si>
+    <t>Phường 16,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP032</t>
+  </si>
+  <si>
+    <t>Khả Như Spa</t>
+  </si>
+  <si>
+    <t>671 Ngõ Thống Nhất,Phường 13,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP033</t>
+  </si>
+  <si>
+    <t>Mei Spa Gò Vấp</t>
+  </si>
+  <si>
+    <t>187/22 Đường Số 28,Phường 6,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP034</t>
+  </si>
+  <si>
+    <t>Tiny Beauty Spa</t>
+  </si>
+  <si>
+    <t>SP035</t>
+  </si>
+  <si>
+    <t>Quyên Home Spa</t>
+  </si>
+  <si>
+    <t>SP036</t>
+  </si>
+  <si>
+    <t>Ngọc Ngà Spa</t>
+  </si>
+  <si>
+    <t>SP037</t>
+  </si>
+  <si>
+    <t>An Nhiên Spa</t>
+  </si>
+  <si>
+    <t>SP038</t>
+  </si>
+  <si>
+    <t>Mai Sương Spa</t>
+  </si>
+  <si>
+    <t>Phường 13,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP039</t>
+  </si>
+  <si>
+    <t>Hoài Vy Spa</t>
+  </si>
+  <si>
+    <t>SP040</t>
+  </si>
+  <si>
+    <t>Spa Huyền Tây</t>
+  </si>
+  <si>
+    <t>SP041</t>
+  </si>
+  <si>
+    <t>Ong Nâu Spaghetti</t>
+  </si>
+  <si>
+    <t>511 Ngõ Lê Quang Định,Phường 1,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP042</t>
+  </si>
+  <si>
+    <t>Spacy Hoàng Huy</t>
+  </si>
+  <si>
+    <t>529 Lê Quang Định,Phường 1,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP043</t>
+  </si>
+  <si>
+    <t>Thanh Spa</t>
+  </si>
+  <si>
+    <t>SP044</t>
+  </si>
+  <si>
+    <t>Sahala Home Spa</t>
+  </si>
+  <si>
+    <t>Phường 11,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP045</t>
+  </si>
+  <si>
+    <t>Thanh Thảo Spa</t>
+  </si>
+  <si>
+    <t>SP046</t>
+  </si>
+  <si>
+    <t>Ti House Spa</t>
+  </si>
+  <si>
+    <t>Phường 12,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP047</t>
+  </si>
+  <si>
+    <t>Công Ty TNHH Kiến Trúc Xây Dựng Spacecons</t>
+  </si>
+  <si>
+    <t>366 Đường Phan Văn Trị,Phường 5,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP048</t>
+  </si>
+  <si>
+    <t>Space Cofee</t>
+  </si>
+  <si>
+    <t>474 Nguyễn Thái Sơn,Phường 5,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP049</t>
+  </si>
+  <si>
+    <t>Sửa Chữa Xe Máy Khánh Spacy</t>
+  </si>
+  <si>
+    <t>98 Nguyên Hồng,Phường 1,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP050</t>
+  </si>
+  <si>
+    <t>Spa Hoa Kiều</t>
+  </si>
+  <si>
+    <t>SP051</t>
+  </si>
+  <si>
+    <t>Spa Triệt Lông</t>
+  </si>
+  <si>
+    <t>SP052</t>
+  </si>
+  <si>
+    <t>Snooze Space</t>
+  </si>
+  <si>
+    <t>138 Ngõ Lương Ngọc Quyến,Phường 5,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP053</t>
+  </si>
+  <si>
+    <t>Mac Space</t>
+  </si>
+  <si>
+    <t>63 Đường Số 6,Phường 10,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP054</t>
+  </si>
+  <si>
+    <t>Mindx Startup Space</t>
+  </si>
+  <si>
+    <t>1 Ngõ Quang Trung,Phường 10,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP055</t>
+  </si>
+  <si>
+    <t>Sắc Đẹp Spa</t>
+  </si>
+  <si>
+    <t>SP056</t>
+  </si>
+  <si>
+    <t>3T Spa &amp; Healthcare</t>
+  </si>
+  <si>
+    <t>SP057</t>
+  </si>
+  <si>
+    <t>Mộc Chu Spa</t>
+  </si>
+  <si>
+    <t>SP058</t>
+  </si>
+  <si>
+    <t>Spa Ngọc Beauty</t>
+  </si>
+  <si>
+    <t>SP059</t>
+  </si>
+  <si>
+    <t>Pod Husky Space</t>
+  </si>
+  <si>
+    <t>819/14 Đường Số 7,Phường 3,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP060</t>
+  </si>
+  <si>
+    <t>Lê Vi Cosmetic &amp; Spa</t>
+  </si>
+  <si>
+    <t>SP061</t>
+  </si>
+  <si>
+    <t>Kim Ngân Hà Spa</t>
+  </si>
+  <si>
+    <t>SP062</t>
+  </si>
+  <si>
+    <t>Erika Spa</t>
+  </si>
+  <si>
+    <t>22 Phạm Văn Đồng,Phường 3,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP063</t>
+  </si>
+  <si>
+    <t>D'ORO Spa</t>
+  </si>
+  <si>
+    <t>62 Nguyễn Thái Sơn,Phường 3,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP064</t>
+  </si>
+  <si>
+    <t>Spa Minh Châu</t>
+  </si>
+  <si>
+    <t>27 Nguyễn Kiệm,Phường 3,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP065</t>
+  </si>
+  <si>
+    <t>Sweet Home Spa</t>
+  </si>
+  <si>
+    <t>891/31/28,Phường 3,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP066</t>
+  </si>
+  <si>
+    <t>New Hair Spa</t>
+  </si>
+  <si>
+    <t>27 Nguyễn Thái Sơn,Phường 3,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP067</t>
+  </si>
+  <si>
+    <t>Spa Linh Nhi</t>
+  </si>
+  <si>
+    <t>115/8 Nguyễn Kiệm,Phường 3,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP068</t>
+  </si>
+  <si>
+    <t>Sửa Chữa Xe Máy Hoàng Spacy</t>
+  </si>
+  <si>
+    <t>4/4 Lê Đức Thọ,Phường 13,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP069</t>
+  </si>
+  <si>
+    <t>Spa Hồng Nhung</t>
+  </si>
+  <si>
+    <t>515 Phạm Văn Chiêu,Phường 13,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP070</t>
+  </si>
+  <si>
+    <t>Anh Spa</t>
+  </si>
+  <si>
+    <t>1110 Đường Lê Đức Thọ,Phường 13,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP071</t>
+  </si>
+  <si>
+    <t>Spa Kim Thu</t>
+  </si>
+  <si>
+    <t>5/4 Lê Đức Thọ,Phường 13,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP072</t>
+  </si>
+  <si>
+    <t>Thuỷ Beauty Spa Gội Đầu Dưỡng Sinh Gò Vấp Trị Liệu Gò Vấp Dưỡng Sinh Gò Vấp Spa Gội Đầu Dưỡng</t>
+  </si>
+  <si>
+    <t>1267/9,Phường 13,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP073</t>
+  </si>
+  <si>
+    <t>Viện Thẩm Mỹ Lyn Beauty Spa &amp; Pmu</t>
+  </si>
+  <si>
+    <t>30 Phạm Văn Chiêu,Phường 13,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP074</t>
+  </si>
+  <si>
+    <t>Viện Chăm Sóc Da Và Spa Kim Thư</t>
+  </si>
+  <si>
+    <t>SP075</t>
+  </si>
+  <si>
+    <t>Romance Spa &amp; Massage Yoni</t>
+  </si>
+  <si>
+    <t>18 Phạm Văn Chiêu,Phường 16,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP076</t>
+  </si>
+  <si>
+    <t>Spa Ánh Nguyệt</t>
+  </si>
+  <si>
+    <t>SP077</t>
+  </si>
+  <si>
+    <t>Hoàng Yến Spa</t>
+  </si>
+  <si>
+    <t>SP078</t>
+  </si>
+  <si>
+    <t>Hà Quyên Spa &amp; Cosmetics</t>
+  </si>
+  <si>
+    <t>82 Đường Số 59,Phường 14,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP079</t>
+  </si>
+  <si>
+    <t>Mì Ý Phố Spaghetti</t>
+  </si>
+  <si>
+    <t>535/8 Ngõ Thống Nhất,Phường 16,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP080</t>
+  </si>
+  <si>
+    <t>Jessie Beauty International Spa</t>
+  </si>
+  <si>
+    <t>SP081</t>
+  </si>
+  <si>
+    <t>Miền Thảo Mộc Spa</t>
+  </si>
+  <si>
+    <t>SP082</t>
+  </si>
+  <si>
+    <t>Mụi Spa</t>
+  </si>
+  <si>
+    <t>465 Lê Văn Thọ,Phường 8,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP083</t>
+  </si>
+  <si>
+    <t>Zen Spa</t>
+  </si>
+  <si>
+    <t>100 Đường Số 3,Phường 8,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP084</t>
+  </si>
+  <si>
+    <t>Spa (Chuỗi - 2 chi nhánh)</t>
+  </si>
+  <si>
+    <t>78/19 Phạm Văn Chiêu,Phường 14,Quận Gò Vấp,Thành Phố Hồ Chí Minh ; 13 Thống Nhất,Phường 11,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP085</t>
+  </si>
+  <si>
+    <t>Meedi Beauty Spa</t>
+  </si>
+  <si>
+    <t>SP086</t>
+  </si>
+  <si>
+    <t>Takashi Spa</t>
+  </si>
+  <si>
+    <t>69 Đường Số 9,Phường 16,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP087</t>
+  </si>
+  <si>
+    <t>Trang Spa</t>
+  </si>
+  <si>
+    <t>69 Ngõ Thống Nhất,Phường 16,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP088</t>
+  </si>
+  <si>
+    <t>Ms.Hoà Spa</t>
+  </si>
+  <si>
+    <t>497 Ngõ Thống Nhất,Phường 16,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP089</t>
+  </si>
+  <si>
+    <t>Hanna Beauty Spa</t>
+  </si>
+  <si>
+    <t>129 Đường Số 1,Phường 11,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP090</t>
+  </si>
+  <si>
+    <t>Yến Nhi Spa Gò Vấp</t>
+  </si>
+  <si>
+    <t>779 Đường Lê Đức Thọ,Phường 16,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP091</t>
+  </si>
+  <si>
+    <t>Spa Mai Lan</t>
+  </si>
+  <si>
+    <t>15/4A Đường Lê Đức Thọ,Phường 16,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP092</t>
+  </si>
+  <si>
+    <t>Minh Thủy Spa</t>
+  </si>
+  <si>
+    <t>276/27/2 Thống Nhất,Phường 16,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP093</t>
+  </si>
+  <si>
+    <t>Thiết Bị Spa Kim Phúc</t>
+  </si>
+  <si>
+    <t>522 Ngõ Thống Nhất,Phường 16,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP094</t>
+  </si>
+  <si>
+    <t>Spa Thẩm Mỹ Hồng Phúc</t>
+  </si>
+  <si>
+    <t>405/6/17 Ngõ Thống Nhất,Phường 11,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP095</t>
+  </si>
+  <si>
+    <t>Như Anh Spa</t>
+  </si>
+  <si>
+    <t>188 Đường Số 8,Phường 11,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP096</t>
+  </si>
+  <si>
+    <t>Jz Natural Spa</t>
+  </si>
+  <si>
+    <t>300 Đường Số 8,Phường 11,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP097</t>
+  </si>
+  <si>
+    <t>Orie Spa</t>
+  </si>
+  <si>
+    <t>308/2 Đường Số 8,Phường 11,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP098</t>
+  </si>
+  <si>
+    <t>Hạnh Lê Spa</t>
+  </si>
+  <si>
+    <t>132 Đường Số 1,Phường 16,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP099</t>
+  </si>
+  <si>
+    <t>Sửa Chữa Xe Máy Tùng Spacy</t>
+  </si>
+  <si>
+    <t>255 Lê Văn Thọ,Phường 8,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP100</t>
+  </si>
+  <si>
+    <t>Hớt Tóc Spa Hiên Anh</t>
+  </si>
+  <si>
+    <t>SP101</t>
+  </si>
+  <si>
+    <t>Bông Spa</t>
+  </si>
+  <si>
+    <t>78 Ngõ Quang Trung,Phường 11,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP102</t>
+  </si>
+  <si>
+    <t>Mosi Spa</t>
+  </si>
+  <si>
+    <t>61 Đường Số 11,Phường 11,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP103</t>
+  </si>
+  <si>
+    <t>Bông Beauty Spa Điều Trị Da Gò Vấp Spa Uy Tín Gò Vấp</t>
+  </si>
+  <si>
+    <t>56/7C1,Phường 11,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP104</t>
+  </si>
+  <si>
+    <t>Spa Lê Hiền</t>
+  </si>
+  <si>
+    <t>84 Đường Số 8,Phường 11,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP105</t>
+  </si>
+  <si>
+    <t>Jivi Spa</t>
+  </si>
+  <si>
+    <t>872/88 Đ,Phường 8,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP106</t>
+  </si>
+  <si>
+    <t>Cafe New Space</t>
+  </si>
+  <si>
+    <t>85 Lê Đức Thọ,Phường 17,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP107</t>
+  </si>
+  <si>
+    <t>Hair Salon Spa Trinh</t>
+  </si>
+  <si>
+    <t>SP108</t>
+  </si>
+  <si>
+    <t>Emi Spa</t>
+  </si>
+  <si>
+    <t>255A7 Nguyễn Văn Lượng,Phường 17,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP109</t>
+  </si>
+  <si>
+    <t>Thanh Thùy Medical Spa</t>
+  </si>
+  <si>
+    <t>21 Nguyễn Oanh,Phường 17,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP110</t>
+  </si>
+  <si>
+    <t>Evas Spa</t>
+  </si>
+  <si>
+    <t>951 Đường Phan Văn Trị,Phường 17,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP111</t>
+  </si>
+  <si>
+    <t>Linh Beauty Spa</t>
+  </si>
+  <si>
+    <t>135 Nguyễn Văn Lượng,Phường 17,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP112</t>
+  </si>
+  <si>
+    <t>Cloud69 Spa</t>
+  </si>
+  <si>
+    <t>Hẻm 363 Lê Đức Thọ,Phường 17,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP113</t>
+  </si>
+  <si>
+    <t>Lê Spa</t>
+  </si>
+  <si>
+    <t>85 Ngõ Lê Hoàng Phái,Phường 17,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP114</t>
+  </si>
+  <si>
+    <t>Spa Hoàng Kim</t>
+  </si>
+  <si>
+    <t>10 Đường Lê Đức Thọ,Phường 17,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP115</t>
+  </si>
+  <si>
+    <t>Lani Spa Beauty &amp; Clinic</t>
+  </si>
+  <si>
+    <t>522 Đường Lê Đức Thọ,Phường 17,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP116</t>
+  </si>
+  <si>
+    <t>Spa Trị Liệu K.O Therapy</t>
+  </si>
+  <si>
+    <t>67/2/25,Phường 17,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP117</t>
+  </si>
+  <si>
+    <t>Milisa Spa</t>
+  </si>
+  <si>
+    <t>65/719 Lê Đức Thọ,Phường 6,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP118</t>
+  </si>
+  <si>
+    <t>Trum Beauty Spa</t>
+  </si>
+  <si>
+    <t>226/45 Nguyễn Văn Lượng,Phường 17,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP119</t>
+  </si>
+  <si>
+    <t>Spa Ngân Nguễn</t>
+  </si>
+  <si>
+    <t>34 Hẻm 226 Nguyễn Văn Lượng,Phường 17,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP120</t>
+  </si>
+  <si>
+    <t>Spa Thiên Anh</t>
+  </si>
+  <si>
+    <t>115/2 Đường Lê Đức Thọ,Phường 17,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP121</t>
+  </si>
+  <si>
+    <t>Clover Beauty &amp; Spa</t>
+  </si>
+  <si>
+    <t>39/43 Hẻm 226 Nguyễn Văn Lượng,Phường 17,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP122</t>
+  </si>
+  <si>
+    <t>Spa Thiên Nhiên</t>
+  </si>
+  <si>
+    <t>SP123</t>
+  </si>
+  <si>
+    <t>Ngô Spa</t>
+  </si>
+  <si>
+    <t>115/29 Đường Lê Đức Thọ,Phường 17,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP124</t>
+  </si>
+  <si>
+    <t>Madame Beauty Spa &amp; Clinic</t>
+  </si>
+  <si>
+    <t>SP125</t>
+  </si>
+  <si>
+    <t>Ngọc Nhà Quê Spa</t>
+  </si>
+  <si>
+    <t>286/5 Nguyễn Oanh,Phường 17,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP126</t>
+  </si>
+  <si>
+    <t>Spa Kim Chi</t>
+  </si>
+  <si>
+    <t>11 Ngõ Lê Hoàng Phái,Phường 17,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP127</t>
+  </si>
+  <si>
+    <t>Vân Beauty &amp; Spa</t>
+  </si>
+  <si>
+    <t>21/3 Ngõ Lê Hoàng Phái,Phường 17,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP128</t>
+  </si>
+  <si>
+    <t>Thái Spa</t>
+  </si>
+  <si>
+    <t>33,Phường 16,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP129</t>
+  </si>
+  <si>
+    <t>Spa Hồng Tám</t>
+  </si>
+  <si>
+    <t>SP130</t>
+  </si>
+  <si>
+    <t>Vhbeauty Spa</t>
+  </si>
+  <si>
+    <t>45 Số 9,Phường 10,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP131</t>
+  </si>
+  <si>
+    <t>Keiko Esthetic Spa</t>
+  </si>
+  <si>
+    <t>45 Đường Số 9,Phường 10,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP132</t>
+  </si>
+  <si>
+    <t>Thủy Tiên Spa</t>
+  </si>
+  <si>
+    <t>350/1A Nguyễn Văn Lượng,Phường 16,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP133</t>
+  </si>
+  <si>
+    <t>Spa Mỹ Nguyễn</t>
+  </si>
+  <si>
+    <t>57 Ngõ Quảng Hàm,Phường 6,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP134</t>
+  </si>
+  <si>
+    <t>Thu House Spa &amp; Cosmetics</t>
+  </si>
+  <si>
+    <t>29/7/30,Phường 1,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP135</t>
+  </si>
+  <si>
+    <t>Hoàn Mỹ Spa</t>
+  </si>
+  <si>
+    <t>D13 Đường Số 4,Phường 1,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP136</t>
+  </si>
+  <si>
+    <t>Queen Spa Xxii</t>
+  </si>
+  <si>
+    <t>72 Đường Lê Đức Thọ,Phường 1,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP137</t>
+  </si>
+  <si>
+    <t>Ry Beauty Spa</t>
+  </si>
+  <si>
+    <t>128/1 Đường Lê Đức Thọ,Phường 6,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP138</t>
+  </si>
+  <si>
+    <t>Enbi Bảo Bảo Nail &amp; Spa</t>
+  </si>
+  <si>
+    <t>58 Đường Lê Đức Thọ,Phường 1,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP139</t>
+  </si>
+  <si>
+    <t>Green Field Spa Bầu Sau Sinh</t>
+  </si>
+  <si>
+    <t>63 Đường Lê Đức Thọ,Phường 6,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP140</t>
+  </si>
+  <si>
+    <t>Dr.Yh Clinic &amp; Spa Gò Vấp</t>
+  </si>
+  <si>
+    <t>40/21 Đường Lê Đức Thọ,Phường 1,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP141</t>
+  </si>
+  <si>
+    <t>Spa Hoa Sen</t>
+  </si>
+  <si>
+    <t>100,Phường 10,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP142</t>
+  </si>
+  <si>
+    <t>Tam's Beauty Spa</t>
+  </si>
+  <si>
+    <t>SP143</t>
+  </si>
+  <si>
+    <t>Bắp Spa</t>
+  </si>
+  <si>
+    <t>144 Nguyễn Văn Lượng,Phường 16,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP144</t>
+  </si>
+  <si>
+    <t>Spa Cắt Tóc Cao Cấp</t>
+  </si>
+  <si>
+    <t>21/22A Lê Văn Thọ,Phường 16,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP145</t>
+  </si>
+  <si>
+    <t>Camila Spa &amp; Clinic</t>
+  </si>
+  <si>
+    <t>401 Lê Văn Thọ,Phường 8,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP146</t>
+  </si>
+  <si>
+    <t>Spa Ngọc Bích</t>
+  </si>
+  <si>
+    <t>104 Hẻm 102 Lê Văn Thọ,Phường 16,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP147</t>
+  </si>
+  <si>
+    <t>Be Beauty Nail Mi Spa</t>
+  </si>
+  <si>
+    <t>SP148</t>
+  </si>
+  <si>
+    <t>Nắng Spa</t>
+  </si>
+  <si>
+    <t>51 Hẻm 208 Số 9,Phường 16,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP149</t>
+  </si>
+  <si>
+    <t>Quý Phi Spa.</t>
+  </si>
+  <si>
+    <t>276/7 Ngõ Thống Nhất,Phường 16,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP150</t>
+  </si>
+  <si>
+    <t>Spa Ở Gò Vấp</t>
+  </si>
+  <si>
+    <t>97 Ngõ Thống Nhất,Phường 16,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP151</t>
+  </si>
+  <si>
+    <t>Golf Spa</t>
+  </si>
+  <si>
+    <t>675 Tân Sơn,Phường 12,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP152</t>
+  </si>
+  <si>
+    <t>Andy Spa</t>
+  </si>
+  <si>
+    <t>Đường Phạm Văn Bạch,Phường 12,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP153</t>
+  </si>
+  <si>
+    <t>Kim Spa</t>
+  </si>
+  <si>
+    <t>56 Nguyễn Tư Giản,Phường 12,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP154</t>
+  </si>
+  <si>
+    <t>Aura Spa Beauty Trị Mụn Gò Vấp Spa Gần Đây</t>
+  </si>
+  <si>
+    <t>55 Phan Huy Ch,Phường 12,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP155</t>
+  </si>
+  <si>
+    <t>Spa Châu Ngọc</t>
+  </si>
+  <si>
+    <t>853 Quang Trung,Phường 12,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP156</t>
+  </si>
+  <si>
+    <t>Levi Spa</t>
+  </si>
+  <si>
+    <t>448 Phan Huy Ch,Phường 12,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP157</t>
+  </si>
+  <si>
+    <t>Spa Massage Hoàng Hải</t>
+  </si>
+  <si>
+    <t>443 Tân Sơn,Phường 12,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP158</t>
+  </si>
+  <si>
+    <t>Rum Pet's Spa &amp; Grooming</t>
+  </si>
+  <si>
+    <t>471 Tân Sơn,Phường 12,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP159</t>
+  </si>
+  <si>
+    <t>Spa Tiên Thảo</t>
+  </si>
+  <si>
+    <t>SP160</t>
+  </si>
+  <si>
+    <t>Bu House Spa</t>
+  </si>
+  <si>
+    <t>218B Nguyễn Duy Cung,Phường 12,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP161</t>
+  </si>
+  <si>
+    <t>Spa Ngọc Vân Anh</t>
+  </si>
+  <si>
+    <t>111 Nguyễn Duy Cung,Phường 12,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP162</t>
+  </si>
+  <si>
+    <t>Nam Nhân Spa</t>
+  </si>
+  <si>
+    <t>27/8Y Phan Huy Ch,Phường 12,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP163</t>
+  </si>
+  <si>
+    <t>Nails-Mi-Spa Thảo Lê</t>
+  </si>
+  <si>
+    <t>745/99 Quang Trung,Phường 12,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP164</t>
+  </si>
+  <si>
+    <t>Cozy Beauty Spa</t>
+  </si>
+  <si>
+    <t>745/62/ Ngõ 8 Quang Trung,Phường 12,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP165</t>
+  </si>
+  <si>
+    <t>Thu Hiền Beauty &amp; Spa</t>
+  </si>
+  <si>
+    <t>SP166</t>
+  </si>
+  <si>
+    <t>Quyên Waxing &amp; Beauty Spa</t>
+  </si>
+  <si>
+    <t>256/42 Phan Huy Ch,Phường 12,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP167</t>
+  </si>
+  <si>
+    <t>Hair Salon And Spa Cỏ Xanh</t>
+  </si>
+  <si>
+    <t>SP168</t>
+  </si>
+  <si>
+    <t>Vy Spa</t>
+  </si>
+  <si>
+    <t>9/55B Phan Huy Ích,Phường 14,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP169</t>
+  </si>
+  <si>
+    <t>Thanh Loan Spa</t>
+  </si>
+  <si>
+    <t>51 Phạm Văn Chiêu,Phường 14,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP170</t>
+  </si>
+  <si>
+    <t>Dony Beauty And Spa</t>
+  </si>
+  <si>
+    <t>14 Phan Huy Ch,Phường 14,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP171</t>
+  </si>
+  <si>
+    <t>Thy House Spa</t>
+  </si>
+  <si>
+    <t>SP172</t>
+  </si>
+  <si>
+    <t>Lúa Spa</t>
+  </si>
+  <si>
+    <t>10 Nguyễn Văn,Phường 8,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP173</t>
+  </si>
+  <si>
+    <t>Anh Hạt Dẻ Private Spa</t>
+  </si>
+  <si>
+    <t>1050/35/40,Phường 8,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP174</t>
+  </si>
+  <si>
+    <t>Hồng Nhung Spa</t>
+  </si>
+  <si>
+    <t>23 Ngõ Bùi Quang Là,Phường 12,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP175</t>
+  </si>
+  <si>
+    <t>Thẩm Mỹ And Spa Mỹ Huyền</t>
+  </si>
+  <si>
+    <t>49/9 Bùi Quang Là,Phường 12,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP176</t>
+  </si>
+  <si>
+    <t>Spa Hoàn Minh</t>
+  </si>
+  <si>
+    <t>112/59 Bùi Quang Là,Phường 12,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP177</t>
+  </si>
+  <si>
+    <t>Spa Đồ Hiệu Vanspa</t>
+  </si>
+  <si>
+    <t>28 Nguyễn Tư Giản,Phường 12,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP178</t>
+  </si>
+  <si>
+    <t>Spa Sunny</t>
+  </si>
+  <si>
+    <t>169/19 Nguyễn Tư Giản,Phường 12,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP179</t>
+  </si>
+  <si>
+    <t>Spa I Chi Mai</t>
+  </si>
+  <si>
+    <t>488 Phạm Văn Bạch,Phường 12,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP180</t>
+  </si>
+  <si>
+    <t>H&amp;T Beauty Spa</t>
+  </si>
+  <si>
+    <t>231 Đường Huỳnh Văn Nghệ,Phường 12,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP181</t>
+  </si>
+  <si>
+    <t>Spa Massage Người Mù Tân Biên</t>
+  </si>
+  <si>
+    <t>174/32 Nguyễn Tư Giản,Phường 12,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP182</t>
+  </si>
+  <si>
+    <t>Spa Quang Cường</t>
+  </si>
+  <si>
+    <t>SP183</t>
+  </si>
+  <si>
+    <t>Workflow Gò Vấp-Working Space &amp; Café</t>
+  </si>
+  <si>
+    <t>Đường Số 2,Phường 10,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP184</t>
+  </si>
+  <si>
+    <t>Spa Song Trúc</t>
+  </si>
+  <si>
+    <t>499/6,Phường 10,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP185</t>
+  </si>
+  <si>
+    <t>Phần Mềm Quản Lý Spa Vttech</t>
+  </si>
+  <si>
+    <t>135/2 Ngõ Lê Hồng Phong,Phường 10,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP186</t>
+  </si>
+  <si>
+    <t>HB Spa</t>
+  </si>
+  <si>
+    <t>Đường Phan Văn Trị,Phường 10,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP187</t>
+  </si>
+  <si>
+    <t>Gà Spa</t>
+  </si>
+  <si>
+    <t>1457 Phan Văn Trị,Phường 10,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP188</t>
+  </si>
+  <si>
+    <t>Rugosa Spa &amp; Yoga</t>
+  </si>
+  <si>
+    <t>57 Ngõ Quang Trung,Phường 10,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP189</t>
+  </si>
+  <si>
+    <t>Tộc Dưỡng Spa</t>
+  </si>
+  <si>
+    <t>28 Đường Số 8,Phường 10,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP190</t>
+  </si>
+  <si>
+    <t>Học Viện Spa Puderma</t>
+  </si>
+  <si>
+    <t>40 Đường Số 12,Phường 10,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP191</t>
+  </si>
+  <si>
+    <t>Nhật Kiều Spa</t>
+  </si>
+  <si>
+    <t>6 Đường Số 1,Phường 10,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP192</t>
+  </si>
+  <si>
+    <t>Dai Sy Spa</t>
+  </si>
+  <si>
+    <t>261 Nguyễn Văn Lượng,Phường 10,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP193</t>
+  </si>
+  <si>
+    <t>Zest Health Spa</t>
+  </si>
+  <si>
+    <t>1397 Đường Phan Văn Trị,Phường 10,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP194</t>
+  </si>
+  <si>
+    <t>Hair Spa Thanh Hà</t>
+  </si>
+  <si>
+    <t>499 Ngõ Quang Trung,Phường 10,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP195</t>
+  </si>
+  <si>
+    <t>Spa Thẩm Mỹ Da Ngọc Ánh</t>
+  </si>
+  <si>
+    <t>SP196</t>
+  </si>
+  <si>
+    <t>An Châu Spa</t>
+  </si>
+  <si>
+    <t>5 Ngõ Quang Trung,Phường 10,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP197</t>
+  </si>
+  <si>
+    <t>Tam's Beauty Home Spa</t>
+  </si>
+  <si>
+    <t>22 Ngõ Quang Trung,Phường 10,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP198</t>
+  </si>
+  <si>
+    <t>Lệ Quân Spa</t>
+  </si>
+  <si>
+    <t>23 Ngõ Thông Tây Hội,Phường 10,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP199</t>
+  </si>
+  <si>
+    <t>Cà Na Baby And Mom Spa Spa Mẹ Và Bé Gò Vấp Massage Bầu</t>
+  </si>
+  <si>
+    <t>672A13 Đường Phan Văn Trị,Phường 10,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP200</t>
+  </si>
+  <si>
+    <t>Spa And Foot Lisa</t>
+  </si>
+  <si>
+    <t>394-396 Quang Trung,Phường 10,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP201</t>
+  </si>
+  <si>
+    <t>Lisa Spa Gò Vấp</t>
+  </si>
+  <si>
+    <t>396 Ngõ Quang Trung,Phường 10,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP202</t>
+  </si>
+  <si>
+    <t>Spa Mầm</t>
+  </si>
+  <si>
+    <t>50 Ngõ 31Quang Trung,Phường 10,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP203</t>
+  </si>
+  <si>
+    <t>Bệnh Viện Máy Tính Quốc Tế Space</t>
+  </si>
+  <si>
+    <t>34-36 Quang Trung,Phường 10,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP204</t>
+  </si>
+  <si>
+    <t>Minh Trang Spa</t>
+  </si>
+  <si>
+    <t>50/19 Ngõ Quang Trung,Phường 10,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP205</t>
+  </si>
+  <si>
+    <t>Beauty Spa Duyên Vĩnh Hoàng</t>
+  </si>
+  <si>
+    <t>5 Bis Quang Trung,Phường 10,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP206</t>
+  </si>
+  <si>
+    <t>Diamond Spa And Yoga</t>
+  </si>
+  <si>
+    <t>50/4/46 Ngõ Quang Trung,Phường 10,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
+  </si>
+  <si>
+    <t>SP207</t>
+  </si>
+  <si>
+    <t>Trung Tâm Bảo Dưỡng Sửa Chí Thanh Spacy</t>
+  </si>
+  <si>
+    <t>229 Phạm Ngũ Lão,Phường 1,Quận Gò Vấp,Thành Phố Hồ Chí Minh</t>
   </si>
   <si>
     <t>Người liên hệ</t>
@@ -1406,2161 +3053,5101 @@
         <v>63</v>
       </c>
     </row>
-    <row r="26" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A26" s="6"/>
-      <c r="B26" s="6"/>
-      <c r="C26" s="6"/>
-      <c r="D26" s="6"/>
-      <c r="E26" s="6"/>
-      <c r="F26" s="6"/>
-      <c r="G26" s="6"/>
-      <c r="H26" s="6"/>
-      <c r="I26" s="6"/>
-    </row>
-    <row r="27" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A27" s="6"/>
-      <c r="B27" s="6"/>
-      <c r="C27" s="6"/>
-      <c r="D27" s="6"/>
-      <c r="E27" s="6"/>
-      <c r="F27" s="6"/>
-      <c r="G27" s="6"/>
-      <c r="H27" s="6"/>
-      <c r="I27" s="6"/>
-    </row>
-    <row r="28" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A28" s="6"/>
-      <c r="B28" s="6"/>
-      <c r="C28" s="6"/>
-      <c r="D28" s="6"/>
-      <c r="E28" s="6"/>
-      <c r="F28" s="6"/>
-      <c r="G28" s="6"/>
-      <c r="H28" s="6"/>
-      <c r="I28" s="6"/>
-    </row>
-    <row r="29" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A29" s="6"/>
-      <c r="B29" s="6"/>
-      <c r="C29" s="6"/>
-      <c r="D29" s="6"/>
-      <c r="E29" s="6"/>
-      <c r="F29" s="6"/>
-      <c r="G29" s="6"/>
-      <c r="H29" s="6"/>
-      <c r="I29" s="6"/>
-    </row>
-    <row r="30" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A30" s="6"/>
-      <c r="B30" s="6"/>
-      <c r="C30" s="6"/>
-      <c r="D30" s="6"/>
-      <c r="E30" s="6"/>
-      <c r="F30" s="6"/>
-      <c r="G30" s="6"/>
-      <c r="H30" s="6"/>
-      <c r="I30" s="6"/>
-    </row>
-    <row r="31" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A31" s="6"/>
-      <c r="B31" s="6"/>
-      <c r="C31" s="6"/>
-      <c r="D31" s="6"/>
-      <c r="E31" s="6"/>
-      <c r="F31" s="6"/>
-      <c r="G31" s="6"/>
-      <c r="H31" s="6"/>
-      <c r="I31" s="6"/>
-    </row>
-    <row r="32" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A32" s="6"/>
-      <c r="B32" s="6"/>
-      <c r="C32" s="6"/>
-      <c r="D32" s="6"/>
-      <c r="E32" s="6"/>
-      <c r="F32" s="6"/>
-      <c r="G32" s="6"/>
-      <c r="H32" s="6"/>
-      <c r="I32" s="6"/>
-    </row>
-    <row r="33" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A33" s="6"/>
-      <c r="B33" s="6"/>
-      <c r="C33" s="6"/>
-      <c r="D33" s="6"/>
-      <c r="E33" s="6"/>
-      <c r="F33" s="6"/>
-      <c r="G33" s="6"/>
-      <c r="H33" s="6"/>
-      <c r="I33" s="6"/>
-    </row>
-    <row r="34" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A34" s="6"/>
-      <c r="B34" s="6"/>
-      <c r="C34" s="6"/>
-      <c r="D34" s="6"/>
-      <c r="E34" s="6"/>
-      <c r="F34" s="6"/>
-      <c r="G34" s="6"/>
-      <c r="H34" s="6"/>
-      <c r="I34" s="6"/>
-    </row>
-    <row r="35" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A35" s="6"/>
-      <c r="B35" s="6"/>
-      <c r="C35" s="6"/>
-      <c r="D35" s="6"/>
-      <c r="E35" s="6"/>
-      <c r="F35" s="6"/>
-      <c r="G35" s="6"/>
-      <c r="H35" s="6"/>
-      <c r="I35" s="6"/>
-    </row>
-    <row r="36" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A36" s="6"/>
-      <c r="B36" s="6"/>
-      <c r="C36" s="6"/>
-      <c r="D36" s="6"/>
-      <c r="E36" s="6"/>
-      <c r="F36" s="6"/>
-      <c r="G36" s="6"/>
-      <c r="H36" s="6"/>
-      <c r="I36" s="6"/>
-    </row>
-    <row r="37" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A37" s="6"/>
-      <c r="B37" s="6"/>
-      <c r="C37" s="6"/>
-      <c r="D37" s="6"/>
-      <c r="E37" s="6"/>
-      <c r="F37" s="6"/>
-      <c r="G37" s="6"/>
-      <c r="H37" s="6"/>
-      <c r="I37" s="6"/>
-    </row>
-    <row r="38" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A38" s="6"/>
-      <c r="B38" s="6"/>
-      <c r="C38" s="6"/>
-      <c r="D38" s="6"/>
-      <c r="E38" s="6"/>
-      <c r="F38" s="6"/>
-      <c r="G38" s="6"/>
-      <c r="H38" s="6"/>
-      <c r="I38" s="6"/>
-    </row>
-    <row r="39" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A39" s="6"/>
-      <c r="B39" s="6"/>
-      <c r="C39" s="6"/>
-      <c r="D39" s="6"/>
-      <c r="E39" s="6"/>
-      <c r="F39" s="6"/>
-      <c r="G39" s="6"/>
-      <c r="H39" s="6"/>
-      <c r="I39" s="6"/>
-    </row>
-    <row r="40" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A40" s="6"/>
-      <c r="B40" s="6"/>
-      <c r="C40" s="6"/>
-      <c r="D40" s="6"/>
-      <c r="E40" s="6"/>
-      <c r="F40" s="6"/>
-      <c r="G40" s="6"/>
-      <c r="H40" s="6"/>
-      <c r="I40" s="6"/>
-    </row>
-    <row r="41" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A41" s="6"/>
-      <c r="B41" s="6"/>
-      <c r="C41" s="6"/>
-      <c r="D41" s="6"/>
-      <c r="E41" s="6"/>
-      <c r="F41" s="6"/>
-      <c r="G41" s="6"/>
-      <c r="H41" s="6"/>
-      <c r="I41" s="6"/>
-    </row>
-    <row r="42" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A42" s="6"/>
-      <c r="B42" s="6"/>
-      <c r="C42" s="6"/>
-      <c r="D42" s="6"/>
-      <c r="E42" s="6"/>
-      <c r="F42" s="6"/>
-      <c r="G42" s="6"/>
-      <c r="H42" s="6"/>
-      <c r="I42" s="6"/>
-    </row>
-    <row r="43" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A43" s="6"/>
-      <c r="B43" s="6"/>
-      <c r="C43" s="6"/>
-      <c r="D43" s="6"/>
-      <c r="E43" s="6"/>
-      <c r="F43" s="6"/>
-      <c r="G43" s="6"/>
-      <c r="H43" s="6"/>
-      <c r="I43" s="6"/>
-    </row>
-    <row r="44" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A44" s="6"/>
-      <c r="B44" s="6"/>
-      <c r="C44" s="6"/>
-      <c r="D44" s="6"/>
-      <c r="E44" s="6"/>
-      <c r="F44" s="6"/>
-      <c r="G44" s="6"/>
-      <c r="H44" s="6"/>
-      <c r="I44" s="6"/>
-    </row>
-    <row r="45" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A45" s="6"/>
-      <c r="B45" s="6"/>
-      <c r="C45" s="6"/>
-      <c r="D45" s="6"/>
-      <c r="E45" s="6"/>
-      <c r="F45" s="6"/>
-      <c r="G45" s="6"/>
-      <c r="H45" s="6"/>
-      <c r="I45" s="6"/>
-    </row>
-    <row r="46" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A46" s="6"/>
-      <c r="B46" s="6"/>
-      <c r="C46" s="6"/>
-      <c r="D46" s="6"/>
-      <c r="E46" s="6"/>
-      <c r="F46" s="6"/>
-      <c r="G46" s="6"/>
-      <c r="H46" s="6"/>
-      <c r="I46" s="6"/>
-    </row>
-    <row r="47" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A47" s="6"/>
-      <c r="B47" s="6"/>
-      <c r="C47" s="6"/>
-      <c r="D47" s="6"/>
-      <c r="E47" s="6"/>
-      <c r="F47" s="6"/>
-      <c r="G47" s="6"/>
-      <c r="H47" s="6"/>
-      <c r="I47" s="6"/>
-    </row>
-    <row r="48" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A48" s="6"/>
-      <c r="B48" s="6"/>
-      <c r="C48" s="6"/>
-      <c r="D48" s="6"/>
-      <c r="E48" s="6"/>
-      <c r="F48" s="6"/>
-      <c r="G48" s="6"/>
-      <c r="H48" s="6"/>
-      <c r="I48" s="6"/>
-    </row>
-    <row r="49" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A49" s="6"/>
-      <c r="B49" s="6"/>
-      <c r="C49" s="6"/>
-      <c r="D49" s="6"/>
-      <c r="E49" s="6"/>
-      <c r="F49" s="6"/>
-      <c r="G49" s="6"/>
-      <c r="H49" s="6"/>
-      <c r="I49" s="6"/>
-    </row>
-    <row r="50" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A50" s="6"/>
-      <c r="B50" s="6"/>
-      <c r="C50" s="6"/>
-      <c r="D50" s="6"/>
-      <c r="E50" s="6"/>
-      <c r="F50" s="6"/>
-      <c r="G50" s="6"/>
-      <c r="H50" s="6"/>
-      <c r="I50" s="6"/>
-    </row>
-    <row r="51" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A51" s="6"/>
-      <c r="B51" s="6"/>
-      <c r="C51" s="6"/>
-      <c r="D51" s="6"/>
-      <c r="E51" s="6"/>
-      <c r="F51" s="6"/>
-      <c r="G51" s="6"/>
-      <c r="H51" s="6"/>
-      <c r="I51" s="6"/>
-    </row>
-    <row r="52" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A52" s="6"/>
-      <c r="B52" s="6"/>
-      <c r="C52" s="6"/>
-      <c r="D52" s="6"/>
-      <c r="E52" s="6"/>
-      <c r="F52" s="6"/>
-      <c r="G52" s="6"/>
-      <c r="H52" s="6"/>
-      <c r="I52" s="6"/>
-    </row>
-    <row r="53" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A53" s="6"/>
-      <c r="B53" s="6"/>
-      <c r="C53" s="6"/>
-      <c r="D53" s="6"/>
-      <c r="E53" s="6"/>
-      <c r="F53" s="6"/>
-      <c r="G53" s="6"/>
-      <c r="H53" s="6"/>
-      <c r="I53" s="6"/>
-    </row>
-    <row r="54" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A54" s="6"/>
-      <c r="B54" s="6"/>
-      <c r="C54" s="6"/>
-      <c r="D54" s="6"/>
-      <c r="E54" s="6"/>
-      <c r="F54" s="6"/>
-      <c r="G54" s="6"/>
-      <c r="H54" s="6"/>
-      <c r="I54" s="6"/>
-    </row>
-    <row r="55" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A55" s="6"/>
-      <c r="B55" s="6"/>
-      <c r="C55" s="6"/>
-      <c r="D55" s="6"/>
-      <c r="E55" s="6"/>
-      <c r="F55" s="6"/>
-      <c r="G55" s="6"/>
-      <c r="H55" s="6"/>
-      <c r="I55" s="6"/>
-    </row>
-    <row r="56" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A56" s="6"/>
-      <c r="B56" s="6"/>
-      <c r="C56" s="6"/>
-      <c r="D56" s="6"/>
-      <c r="E56" s="6"/>
-      <c r="F56" s="6"/>
-      <c r="G56" s="6"/>
-      <c r="H56" s="6"/>
-      <c r="I56" s="6"/>
-    </row>
-    <row r="57" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A57" s="6"/>
-      <c r="B57" s="6"/>
-      <c r="C57" s="6"/>
-      <c r="D57" s="6"/>
-      <c r="E57" s="6"/>
-      <c r="F57" s="6"/>
-      <c r="G57" s="6"/>
-      <c r="H57" s="6"/>
-      <c r="I57" s="6"/>
-    </row>
-    <row r="58" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A58" s="6"/>
-      <c r="B58" s="6"/>
-      <c r="C58" s="6"/>
-      <c r="D58" s="6"/>
-      <c r="E58" s="6"/>
-      <c r="F58" s="6"/>
-      <c r="G58" s="6"/>
-      <c r="H58" s="6"/>
-      <c r="I58" s="6"/>
-    </row>
-    <row r="59" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A59" s="6"/>
-      <c r="B59" s="6"/>
-      <c r="C59" s="6"/>
-      <c r="D59" s="6"/>
-      <c r="E59" s="6"/>
-      <c r="F59" s="6"/>
-      <c r="G59" s="6"/>
-      <c r="H59" s="6"/>
-      <c r="I59" s="6"/>
-    </row>
-    <row r="60" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A60" s="6"/>
-      <c r="B60" s="6"/>
-      <c r="C60" s="6"/>
-      <c r="D60" s="6"/>
-      <c r="E60" s="6"/>
-      <c r="F60" s="6"/>
-      <c r="G60" s="6"/>
-      <c r="H60" s="6"/>
-      <c r="I60" s="6"/>
-    </row>
-    <row r="61" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A61" s="6"/>
-      <c r="B61" s="6"/>
-      <c r="C61" s="6"/>
-      <c r="D61" s="6"/>
-      <c r="E61" s="6"/>
-      <c r="F61" s="6"/>
-      <c r="G61" s="6"/>
-      <c r="H61" s="6"/>
-      <c r="I61" s="6"/>
-    </row>
-    <row r="62" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A62" s="6"/>
-      <c r="B62" s="6"/>
-      <c r="C62" s="6"/>
-      <c r="D62" s="6"/>
-      <c r="E62" s="6"/>
-      <c r="F62" s="6"/>
-      <c r="G62" s="6"/>
-      <c r="H62" s="6"/>
-      <c r="I62" s="6"/>
-    </row>
-    <row r="63" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A63" s="6"/>
-      <c r="B63" s="6"/>
-      <c r="C63" s="6"/>
-      <c r="D63" s="6"/>
-      <c r="E63" s="6"/>
-      <c r="F63" s="6"/>
-      <c r="G63" s="6"/>
-      <c r="H63" s="6"/>
-      <c r="I63" s="6"/>
-    </row>
-    <row r="64" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A64" s="6"/>
-      <c r="B64" s="6"/>
-      <c r="C64" s="6"/>
-      <c r="D64" s="6"/>
-      <c r="E64" s="6"/>
-      <c r="F64" s="6"/>
-      <c r="G64" s="6"/>
-      <c r="H64" s="6"/>
-      <c r="I64" s="6"/>
-    </row>
-    <row r="65" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A65" s="6"/>
-      <c r="B65" s="6"/>
-      <c r="C65" s="6"/>
-      <c r="D65" s="6"/>
-      <c r="E65" s="6"/>
-      <c r="F65" s="6"/>
-      <c r="G65" s="6"/>
-      <c r="H65" s="6"/>
-      <c r="I65" s="6"/>
-    </row>
-    <row r="66" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A66" s="6"/>
-      <c r="B66" s="6"/>
-      <c r="C66" s="6"/>
-      <c r="D66" s="6"/>
-      <c r="E66" s="6"/>
-      <c r="F66" s="6"/>
-      <c r="G66" s="6"/>
-      <c r="H66" s="6"/>
-      <c r="I66" s="6"/>
-    </row>
-    <row r="67" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A67" s="6"/>
-      <c r="B67" s="6"/>
-      <c r="C67" s="6"/>
-      <c r="D67" s="6"/>
-      <c r="E67" s="6"/>
-      <c r="F67" s="6"/>
-      <c r="G67" s="6"/>
-      <c r="H67" s="6"/>
-      <c r="I67" s="6"/>
-    </row>
-    <row r="68" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A68" s="6"/>
-      <c r="B68" s="6"/>
-      <c r="C68" s="6"/>
-      <c r="D68" s="6"/>
-      <c r="E68" s="6"/>
-      <c r="F68" s="6"/>
-      <c r="G68" s="6"/>
-      <c r="H68" s="6"/>
-      <c r="I68" s="6"/>
-    </row>
-    <row r="69" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A69" s="6"/>
-      <c r="B69" s="6"/>
-      <c r="C69" s="6"/>
-      <c r="D69" s="6"/>
-      <c r="E69" s="6"/>
-      <c r="F69" s="6"/>
-      <c r="G69" s="6"/>
-      <c r="H69" s="6"/>
-      <c r="I69" s="6"/>
-    </row>
-    <row r="70" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A70" s="6"/>
-      <c r="B70" s="6"/>
-      <c r="C70" s="6"/>
-      <c r="D70" s="6"/>
-      <c r="E70" s="6"/>
-      <c r="F70" s="6"/>
-      <c r="G70" s="6"/>
-      <c r="H70" s="6"/>
-      <c r="I70" s="6"/>
-    </row>
-    <row r="71" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A71" s="6"/>
-      <c r="B71" s="6"/>
-      <c r="C71" s="6"/>
-      <c r="D71" s="6"/>
-      <c r="E71" s="6"/>
-      <c r="F71" s="6"/>
-      <c r="G71" s="6"/>
-      <c r="H71" s="6"/>
-      <c r="I71" s="6"/>
-    </row>
-    <row r="72" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A72" s="6"/>
-      <c r="B72" s="6"/>
-      <c r="C72" s="6"/>
-      <c r="D72" s="6"/>
-      <c r="E72" s="6"/>
-      <c r="F72" s="6"/>
-      <c r="G72" s="6"/>
-      <c r="H72" s="6"/>
-      <c r="I72" s="6"/>
-    </row>
-    <row r="73" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A73" s="6"/>
-      <c r="B73" s="6"/>
-      <c r="C73" s="6"/>
-      <c r="D73" s="6"/>
-      <c r="E73" s="6"/>
-      <c r="F73" s="6"/>
-      <c r="G73" s="6"/>
-      <c r="H73" s="6"/>
-      <c r="I73" s="6"/>
-    </row>
-    <row r="74" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A74" s="6"/>
-      <c r="B74" s="6"/>
-      <c r="C74" s="6"/>
-      <c r="D74" s="6"/>
-      <c r="E74" s="6"/>
-      <c r="F74" s="6"/>
-      <c r="G74" s="6"/>
-      <c r="H74" s="6"/>
-      <c r="I74" s="6"/>
-    </row>
-    <row r="75" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A75" s="6"/>
-      <c r="B75" s="6"/>
-      <c r="C75" s="6"/>
-      <c r="D75" s="6"/>
-      <c r="E75" s="6"/>
-      <c r="F75" s="6"/>
-      <c r="G75" s="6"/>
-      <c r="H75" s="6"/>
-      <c r="I75" s="6"/>
-    </row>
-    <row r="76" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A76" s="6"/>
-      <c r="B76" s="6"/>
-      <c r="C76" s="6"/>
-      <c r="D76" s="6"/>
-      <c r="E76" s="6"/>
-      <c r="F76" s="6"/>
-      <c r="G76" s="6"/>
-      <c r="H76" s="6"/>
-      <c r="I76" s="6"/>
-    </row>
-    <row r="77" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A77" s="6"/>
-      <c r="B77" s="6"/>
-      <c r="C77" s="6"/>
-      <c r="D77" s="6"/>
-      <c r="E77" s="6"/>
-      <c r="F77" s="6"/>
-      <c r="G77" s="6"/>
-      <c r="H77" s="6"/>
-      <c r="I77" s="6"/>
-    </row>
-    <row r="78" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A78" s="6"/>
-      <c r="B78" s="6"/>
-      <c r="C78" s="6"/>
-      <c r="D78" s="6"/>
-      <c r="E78" s="6"/>
-      <c r="F78" s="6"/>
-      <c r="G78" s="6"/>
-      <c r="H78" s="6"/>
-      <c r="I78" s="6"/>
-    </row>
-    <row r="79" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A79" s="6"/>
-      <c r="B79" s="6"/>
-      <c r="C79" s="6"/>
-      <c r="D79" s="6"/>
-      <c r="E79" s="6"/>
-      <c r="F79" s="6"/>
-      <c r="G79" s="6"/>
-      <c r="H79" s="6"/>
-      <c r="I79" s="6"/>
-    </row>
-    <row r="80" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A80" s="6"/>
-      <c r="B80" s="6"/>
-      <c r="C80" s="6"/>
-      <c r="D80" s="6"/>
-      <c r="E80" s="6"/>
-      <c r="F80" s="6"/>
-      <c r="G80" s="6"/>
-      <c r="H80" s="6"/>
-      <c r="I80" s="6"/>
-    </row>
-    <row r="81" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A81" s="6"/>
-      <c r="B81" s="6"/>
-      <c r="C81" s="6"/>
-      <c r="D81" s="6"/>
-      <c r="E81" s="6"/>
-      <c r="F81" s="6"/>
-      <c r="G81" s="6"/>
-      <c r="H81" s="6"/>
-      <c r="I81" s="6"/>
-    </row>
-    <row r="82" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A82" s="6"/>
-      <c r="B82" s="6"/>
-      <c r="C82" s="6"/>
-      <c r="D82" s="6"/>
-      <c r="E82" s="6"/>
-      <c r="F82" s="6"/>
-      <c r="G82" s="6"/>
-      <c r="H82" s="6"/>
-      <c r="I82" s="6"/>
-    </row>
-    <row r="83" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A83" s="6"/>
-      <c r="B83" s="6"/>
-      <c r="C83" s="6"/>
-      <c r="D83" s="6"/>
-      <c r="E83" s="6"/>
-      <c r="F83" s="6"/>
-      <c r="G83" s="6"/>
-      <c r="H83" s="6"/>
-      <c r="I83" s="6"/>
-    </row>
-    <row r="84" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A84" s="6"/>
-      <c r="B84" s="6"/>
-      <c r="C84" s="6"/>
-      <c r="D84" s="6"/>
-      <c r="E84" s="6"/>
-      <c r="F84" s="6"/>
-      <c r="G84" s="6"/>
-      <c r="H84" s="6"/>
-      <c r="I84" s="6"/>
-    </row>
-    <row r="85" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A85" s="6"/>
-      <c r="B85" s="6"/>
-      <c r="C85" s="6"/>
-      <c r="D85" s="6"/>
-      <c r="E85" s="6"/>
-      <c r="F85" s="6"/>
-      <c r="G85" s="6"/>
-      <c r="H85" s="6"/>
-      <c r="I85" s="6"/>
-    </row>
-    <row r="86" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A86" s="6"/>
-      <c r="B86" s="6"/>
-      <c r="C86" s="6"/>
-      <c r="D86" s="6"/>
-      <c r="E86" s="6"/>
-      <c r="F86" s="6"/>
-      <c r="G86" s="6"/>
-      <c r="H86" s="6"/>
-      <c r="I86" s="6"/>
-    </row>
-    <row r="87" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A87" s="6"/>
-      <c r="B87" s="6"/>
-      <c r="C87" s="6"/>
-      <c r="D87" s="6"/>
-      <c r="E87" s="6"/>
-      <c r="F87" s="6"/>
-      <c r="G87" s="6"/>
-      <c r="H87" s="6"/>
-      <c r="I87" s="6"/>
-    </row>
-    <row r="88" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A88" s="6"/>
-      <c r="B88" s="6"/>
-      <c r="C88" s="6"/>
-      <c r="D88" s="6"/>
-      <c r="E88" s="6"/>
-      <c r="F88" s="6"/>
-      <c r="G88" s="6"/>
-      <c r="H88" s="6"/>
-      <c r="I88" s="6"/>
-    </row>
-    <row r="89" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A89" s="6"/>
-      <c r="B89" s="6"/>
-      <c r="C89" s="6"/>
-      <c r="D89" s="6"/>
-      <c r="E89" s="6"/>
-      <c r="F89" s="6"/>
-      <c r="G89" s="6"/>
-      <c r="H89" s="6"/>
-      <c r="I89" s="6"/>
-    </row>
-    <row r="90" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A90" s="6"/>
-      <c r="B90" s="6"/>
-      <c r="C90" s="6"/>
-      <c r="D90" s="6"/>
-      <c r="E90" s="6"/>
-      <c r="F90" s="6"/>
-      <c r="G90" s="6"/>
-      <c r="H90" s="6"/>
-      <c r="I90" s="6"/>
-    </row>
-    <row r="91" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A91" s="6"/>
-      <c r="B91" s="6"/>
-      <c r="C91" s="6"/>
-      <c r="D91" s="6"/>
-      <c r="E91" s="6"/>
-      <c r="F91" s="6"/>
-      <c r="G91" s="6"/>
-      <c r="H91" s="6"/>
-      <c r="I91" s="6"/>
-    </row>
-    <row r="92" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A92" s="6"/>
-      <c r="B92" s="6"/>
-      <c r="C92" s="6"/>
-      <c r="D92" s="6"/>
-      <c r="E92" s="6"/>
-      <c r="F92" s="6"/>
-      <c r="G92" s="6"/>
-      <c r="H92" s="6"/>
-      <c r="I92" s="6"/>
-    </row>
-    <row r="93" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A93" s="6"/>
-      <c r="B93" s="6"/>
-      <c r="C93" s="6"/>
-      <c r="D93" s="6"/>
-      <c r="E93" s="6"/>
-      <c r="F93" s="6"/>
-      <c r="G93" s="6"/>
-      <c r="H93" s="6"/>
-      <c r="I93" s="6"/>
-    </row>
-    <row r="94" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A94" s="6"/>
-      <c r="B94" s="6"/>
-      <c r="C94" s="6"/>
-      <c r="D94" s="6"/>
-      <c r="E94" s="6"/>
-      <c r="F94" s="6"/>
-      <c r="G94" s="6"/>
-      <c r="H94" s="6"/>
-      <c r="I94" s="6"/>
-    </row>
-    <row r="95" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A95" s="6"/>
-      <c r="B95" s="6"/>
-      <c r="C95" s="6"/>
-      <c r="D95" s="6"/>
-      <c r="E95" s="6"/>
-      <c r="F95" s="6"/>
-      <c r="G95" s="6"/>
-      <c r="H95" s="6"/>
-      <c r="I95" s="6"/>
-    </row>
-    <row r="96" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A96" s="6"/>
-      <c r="B96" s="6"/>
-      <c r="C96" s="6"/>
-      <c r="D96" s="6"/>
-      <c r="E96" s="6"/>
-      <c r="F96" s="6"/>
-      <c r="G96" s="6"/>
-      <c r="H96" s="6"/>
-      <c r="I96" s="6"/>
-    </row>
-    <row r="97" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A97" s="6"/>
-      <c r="B97" s="6"/>
-      <c r="C97" s="6"/>
-      <c r="D97" s="6"/>
-      <c r="E97" s="6"/>
-      <c r="F97" s="6"/>
-      <c r="G97" s="6"/>
-      <c r="H97" s="6"/>
-      <c r="I97" s="6"/>
-    </row>
-    <row r="98" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A98" s="6"/>
-      <c r="B98" s="6"/>
-      <c r="C98" s="6"/>
-      <c r="D98" s="6"/>
-      <c r="E98" s="6"/>
-      <c r="F98" s="6"/>
-      <c r="G98" s="6"/>
-      <c r="H98" s="6"/>
-      <c r="I98" s="6"/>
-    </row>
-    <row r="99" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A99" s="6"/>
-      <c r="B99" s="6"/>
-      <c r="C99" s="6"/>
-      <c r="D99" s="6"/>
-      <c r="E99" s="6"/>
-      <c r="F99" s="6"/>
-      <c r="G99" s="6"/>
-      <c r="H99" s="6"/>
-      <c r="I99" s="6"/>
-    </row>
-    <row r="100" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A100" s="6"/>
-      <c r="B100" s="6"/>
-      <c r="C100" s="6"/>
-      <c r="D100" s="6"/>
-      <c r="E100" s="6"/>
-      <c r="F100" s="6"/>
-      <c r="G100" s="6"/>
-      <c r="H100" s="6"/>
-      <c r="I100" s="6"/>
-    </row>
-    <row r="101" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A101" s="6"/>
-      <c r="B101" s="6"/>
-      <c r="C101" s="6"/>
-      <c r="D101" s="6"/>
-      <c r="E101" s="6"/>
-      <c r="F101" s="6"/>
-      <c r="G101" s="6"/>
-      <c r="H101" s="6"/>
-      <c r="I101" s="6"/>
-    </row>
-    <row r="102" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A102" s="6"/>
-      <c r="B102" s="6"/>
-      <c r="C102" s="6"/>
-      <c r="D102" s="6"/>
-      <c r="E102" s="6"/>
-      <c r="F102" s="6"/>
-      <c r="G102" s="6"/>
-      <c r="H102" s="6"/>
-      <c r="I102" s="6"/>
-    </row>
-    <row r="103" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A103" s="6"/>
-      <c r="B103" s="6"/>
-      <c r="C103" s="6"/>
-      <c r="D103" s="6"/>
-      <c r="E103" s="6"/>
-      <c r="F103" s="6"/>
-      <c r="G103" s="6"/>
-      <c r="H103" s="6"/>
-      <c r="I103" s="6"/>
-    </row>
-    <row r="104" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A104" s="6"/>
-      <c r="B104" s="6"/>
-      <c r="C104" s="6"/>
-      <c r="D104" s="6"/>
-      <c r="E104" s="6"/>
-      <c r="F104" s="6"/>
-      <c r="G104" s="6"/>
-      <c r="H104" s="6"/>
-      <c r="I104" s="6"/>
-    </row>
-    <row r="105" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A105" s="6"/>
-      <c r="B105" s="6"/>
-      <c r="C105" s="6"/>
-      <c r="D105" s="6"/>
-      <c r="E105" s="6"/>
-      <c r="F105" s="6"/>
-      <c r="G105" s="6"/>
-      <c r="H105" s="6"/>
-      <c r="I105" s="6"/>
-    </row>
-    <row r="106" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A106" s="6"/>
-      <c r="B106" s="6"/>
-      <c r="C106" s="6"/>
-      <c r="D106" s="6"/>
-      <c r="E106" s="6"/>
-      <c r="F106" s="6"/>
-      <c r="G106" s="6"/>
-      <c r="H106" s="6"/>
-      <c r="I106" s="6"/>
-    </row>
-    <row r="107" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A107" s="6"/>
-      <c r="B107" s="6"/>
-      <c r="C107" s="6"/>
-      <c r="D107" s="6"/>
-      <c r="E107" s="6"/>
-      <c r="F107" s="6"/>
-      <c r="G107" s="6"/>
-      <c r="H107" s="6"/>
-      <c r="I107" s="6"/>
-    </row>
-    <row r="108" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A108" s="6"/>
-      <c r="B108" s="6"/>
-      <c r="C108" s="6"/>
-      <c r="D108" s="6"/>
-      <c r="E108" s="6"/>
-      <c r="F108" s="6"/>
-      <c r="G108" s="6"/>
-      <c r="H108" s="6"/>
-      <c r="I108" s="6"/>
-    </row>
-    <row r="109" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A109" s="6"/>
-      <c r="B109" s="6"/>
-      <c r="C109" s="6"/>
-      <c r="D109" s="6"/>
-      <c r="E109" s="6"/>
-      <c r="F109" s="6"/>
-      <c r="G109" s="6"/>
-      <c r="H109" s="6"/>
-      <c r="I109" s="6"/>
-    </row>
-    <row r="110" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A110" s="6"/>
-      <c r="B110" s="6"/>
-      <c r="C110" s="6"/>
-      <c r="D110" s="6"/>
-      <c r="E110" s="6"/>
-      <c r="F110" s="6"/>
-      <c r="G110" s="6"/>
-      <c r="H110" s="6"/>
-      <c r="I110" s="6"/>
-    </row>
-    <row r="111" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A111" s="6"/>
-      <c r="B111" s="6"/>
-      <c r="C111" s="6"/>
-      <c r="D111" s="6"/>
-      <c r="E111" s="6"/>
-      <c r="F111" s="6"/>
-      <c r="G111" s="6"/>
-      <c r="H111" s="6"/>
-      <c r="I111" s="6"/>
-    </row>
-    <row r="112" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A112" s="6"/>
-      <c r="B112" s="6"/>
-      <c r="C112" s="6"/>
-      <c r="D112" s="6"/>
-      <c r="E112" s="6"/>
-      <c r="F112" s="6"/>
-      <c r="G112" s="6"/>
-      <c r="H112" s="6"/>
-      <c r="I112" s="6"/>
-    </row>
-    <row r="113" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A113" s="6"/>
-      <c r="B113" s="6"/>
-      <c r="C113" s="6"/>
-      <c r="D113" s="6"/>
-      <c r="E113" s="6"/>
-      <c r="F113" s="6"/>
-      <c r="G113" s="6"/>
-      <c r="H113" s="6"/>
-      <c r="I113" s="6"/>
-    </row>
-    <row r="114" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A114" s="6"/>
-      <c r="B114" s="6"/>
-      <c r="C114" s="6"/>
-      <c r="D114" s="6"/>
-      <c r="E114" s="6"/>
-      <c r="F114" s="6"/>
-      <c r="G114" s="6"/>
-      <c r="H114" s="6"/>
-      <c r="I114" s="6"/>
-    </row>
-    <row r="115" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A115" s="6"/>
-      <c r="B115" s="6"/>
-      <c r="C115" s="6"/>
-      <c r="D115" s="6"/>
-      <c r="E115" s="6"/>
-      <c r="F115" s="6"/>
-      <c r="G115" s="6"/>
-      <c r="H115" s="6"/>
-      <c r="I115" s="6"/>
-    </row>
-    <row r="116" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A116" s="6"/>
-      <c r="B116" s="6"/>
-      <c r="C116" s="6"/>
-      <c r="D116" s="6"/>
-      <c r="E116" s="6"/>
-      <c r="F116" s="6"/>
-      <c r="G116" s="6"/>
-      <c r="H116" s="6"/>
-      <c r="I116" s="6"/>
-    </row>
-    <row r="117" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A117" s="6"/>
-      <c r="B117" s="6"/>
-      <c r="C117" s="6"/>
-      <c r="D117" s="6"/>
-      <c r="E117" s="6"/>
-      <c r="F117" s="6"/>
-      <c r="G117" s="6"/>
-      <c r="H117" s="6"/>
-      <c r="I117" s="6"/>
-    </row>
-    <row r="118" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A118" s="6"/>
-      <c r="B118" s="6"/>
-      <c r="C118" s="6"/>
-      <c r="D118" s="6"/>
-      <c r="E118" s="6"/>
-      <c r="F118" s="6"/>
-      <c r="G118" s="6"/>
-      <c r="H118" s="6"/>
-      <c r="I118" s="6"/>
-    </row>
-    <row r="119" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A119" s="6"/>
-      <c r="B119" s="6"/>
-      <c r="C119" s="6"/>
-      <c r="D119" s="6"/>
-      <c r="E119" s="6"/>
-      <c r="F119" s="6"/>
-      <c r="G119" s="6"/>
-      <c r="H119" s="6"/>
-      <c r="I119" s="6"/>
-    </row>
-    <row r="120" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A120" s="6"/>
-      <c r="B120" s="6"/>
-      <c r="C120" s="6"/>
-      <c r="D120" s="6"/>
-      <c r="E120" s="6"/>
-      <c r="F120" s="6"/>
-      <c r="G120" s="6"/>
-      <c r="H120" s="6"/>
-      <c r="I120" s="6"/>
-    </row>
-    <row r="121" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A121" s="6"/>
-      <c r="B121" s="6"/>
-      <c r="C121" s="6"/>
-      <c r="D121" s="6"/>
-      <c r="E121" s="6"/>
-      <c r="F121" s="6"/>
-      <c r="G121" s="6"/>
-      <c r="H121" s="6"/>
-      <c r="I121" s="6"/>
-    </row>
-    <row r="122" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A122" s="6"/>
-      <c r="B122" s="6"/>
-      <c r="C122" s="6"/>
-      <c r="D122" s="6"/>
-      <c r="E122" s="6"/>
-      <c r="F122" s="6"/>
-      <c r="G122" s="6"/>
-      <c r="H122" s="6"/>
-      <c r="I122" s="6"/>
-    </row>
-    <row r="123" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A123" s="6"/>
-      <c r="B123" s="6"/>
-      <c r="C123" s="6"/>
-      <c r="D123" s="6"/>
-      <c r="E123" s="6"/>
-      <c r="F123" s="6"/>
-      <c r="G123" s="6"/>
-      <c r="H123" s="6"/>
-      <c r="I123" s="6"/>
-    </row>
-    <row r="124" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A124" s="6"/>
-      <c r="B124" s="6"/>
-      <c r="C124" s="6"/>
-      <c r="D124" s="6"/>
-      <c r="E124" s="6"/>
-      <c r="F124" s="6"/>
-      <c r="G124" s="6"/>
-      <c r="H124" s="6"/>
-      <c r="I124" s="6"/>
-    </row>
-    <row r="125" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A125" s="6"/>
-      <c r="B125" s="6"/>
-      <c r="C125" s="6"/>
-      <c r="D125" s="6"/>
-      <c r="E125" s="6"/>
-      <c r="F125" s="6"/>
-      <c r="G125" s="6"/>
-      <c r="H125" s="6"/>
-      <c r="I125" s="6"/>
-    </row>
-    <row r="126" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A126" s="6"/>
-      <c r="B126" s="6"/>
-      <c r="C126" s="6"/>
-      <c r="D126" s="6"/>
-      <c r="E126" s="6"/>
-      <c r="F126" s="6"/>
-      <c r="G126" s="6"/>
-      <c r="H126" s="6"/>
-      <c r="I126" s="6"/>
-    </row>
-    <row r="127" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A127" s="6"/>
-      <c r="B127" s="6"/>
-      <c r="C127" s="6"/>
-      <c r="D127" s="6"/>
-      <c r="E127" s="6"/>
-      <c r="F127" s="6"/>
-      <c r="G127" s="6"/>
-      <c r="H127" s="6"/>
-      <c r="I127" s="6"/>
-    </row>
-    <row r="128" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A128" s="6"/>
-      <c r="B128" s="6"/>
-      <c r="C128" s="6"/>
-      <c r="D128" s="6"/>
-      <c r="E128" s="6"/>
-      <c r="F128" s="6"/>
-      <c r="G128" s="6"/>
-      <c r="H128" s="6"/>
-      <c r="I128" s="6"/>
-    </row>
-    <row r="129" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A129" s="6"/>
-      <c r="B129" s="6"/>
-      <c r="C129" s="6"/>
-      <c r="D129" s="6"/>
-      <c r="E129" s="6"/>
-      <c r="F129" s="6"/>
-      <c r="G129" s="6"/>
-      <c r="H129" s="6"/>
-      <c r="I129" s="6"/>
-    </row>
-    <row r="130" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A130" s="6"/>
-      <c r="B130" s="6"/>
-      <c r="C130" s="6"/>
-      <c r="D130" s="6"/>
-      <c r="E130" s="6"/>
-      <c r="F130" s="6"/>
-      <c r="G130" s="6"/>
-      <c r="H130" s="6"/>
-      <c r="I130" s="6"/>
-    </row>
-    <row r="131" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A131" s="6"/>
-      <c r="B131" s="6"/>
-      <c r="C131" s="6"/>
-      <c r="D131" s="6"/>
-      <c r="E131" s="6"/>
-      <c r="F131" s="6"/>
-      <c r="G131" s="6"/>
-      <c r="H131" s="6"/>
-      <c r="I131" s="6"/>
-    </row>
-    <row r="132" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A132" s="6"/>
-      <c r="B132" s="6"/>
-      <c r="C132" s="6"/>
-      <c r="D132" s="6"/>
-      <c r="E132" s="6"/>
-      <c r="F132" s="6"/>
-      <c r="G132" s="6"/>
-      <c r="H132" s="6"/>
-      <c r="I132" s="6"/>
-    </row>
-    <row r="133" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A133" s="6"/>
-      <c r="B133" s="6"/>
-      <c r="C133" s="6"/>
-      <c r="D133" s="6"/>
-      <c r="E133" s="6"/>
-      <c r="F133" s="6"/>
-      <c r="G133" s="6"/>
-      <c r="H133" s="6"/>
-      <c r="I133" s="6"/>
-    </row>
-    <row r="134" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A134" s="6"/>
-      <c r="B134" s="6"/>
-      <c r="C134" s="6"/>
-      <c r="D134" s="6"/>
-      <c r="E134" s="6"/>
-      <c r="F134" s="6"/>
-      <c r="G134" s="6"/>
-      <c r="H134" s="6"/>
-      <c r="I134" s="6"/>
-    </row>
-    <row r="135" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A135" s="6"/>
-      <c r="B135" s="6"/>
-      <c r="C135" s="6"/>
-      <c r="D135" s="6"/>
-      <c r="E135" s="6"/>
-      <c r="F135" s="6"/>
-      <c r="G135" s="6"/>
-      <c r="H135" s="6"/>
-      <c r="I135" s="6"/>
-    </row>
-    <row r="136" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A136" s="6"/>
-      <c r="B136" s="6"/>
-      <c r="C136" s="6"/>
-      <c r="D136" s="6"/>
-      <c r="E136" s="6"/>
-      <c r="F136" s="6"/>
-      <c r="G136" s="6"/>
-      <c r="H136" s="6"/>
-      <c r="I136" s="6"/>
-    </row>
-    <row r="137" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A137" s="6"/>
-      <c r="B137" s="6"/>
-      <c r="C137" s="6"/>
-      <c r="D137" s="6"/>
-      <c r="E137" s="6"/>
-      <c r="F137" s="6"/>
-      <c r="G137" s="6"/>
-      <c r="H137" s="6"/>
-      <c r="I137" s="6"/>
-    </row>
-    <row r="138" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A138" s="6"/>
-      <c r="B138" s="6"/>
-      <c r="C138" s="6"/>
-      <c r="D138" s="6"/>
-      <c r="E138" s="6"/>
-      <c r="F138" s="6"/>
-      <c r="G138" s="6"/>
-      <c r="H138" s="6"/>
-      <c r="I138" s="6"/>
-    </row>
-    <row r="139" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A139" s="6"/>
-      <c r="B139" s="6"/>
-      <c r="C139" s="6"/>
-      <c r="D139" s="6"/>
-      <c r="E139" s="6"/>
-      <c r="F139" s="6"/>
-      <c r="G139" s="6"/>
-      <c r="H139" s="6"/>
-      <c r="I139" s="6"/>
-    </row>
-    <row r="140" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A140" s="6"/>
-      <c r="B140" s="6"/>
-      <c r="C140" s="6"/>
-      <c r="D140" s="6"/>
-      <c r="E140" s="6"/>
-      <c r="F140" s="6"/>
-      <c r="G140" s="6"/>
-      <c r="H140" s="6"/>
-      <c r="I140" s="6"/>
-    </row>
-    <row r="141" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A141" s="6"/>
-      <c r="B141" s="6"/>
-      <c r="C141" s="6"/>
-      <c r="D141" s="6"/>
-      <c r="E141" s="6"/>
-      <c r="F141" s="6"/>
-      <c r="G141" s="6"/>
-      <c r="H141" s="6"/>
-      <c r="I141" s="6"/>
-    </row>
-    <row r="142" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A142" s="6"/>
-      <c r="B142" s="6"/>
-      <c r="C142" s="6"/>
-      <c r="D142" s="6"/>
-      <c r="E142" s="6"/>
-      <c r="F142" s="6"/>
-      <c r="G142" s="6"/>
-      <c r="H142" s="6"/>
-      <c r="I142" s="6"/>
-    </row>
-    <row r="143" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A143" s="6"/>
-      <c r="B143" s="6"/>
-      <c r="C143" s="6"/>
-      <c r="D143" s="6"/>
-      <c r="E143" s="6"/>
-      <c r="F143" s="6"/>
-      <c r="G143" s="6"/>
-      <c r="H143" s="6"/>
-      <c r="I143" s="6"/>
-    </row>
-    <row r="144" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A144" s="6"/>
-      <c r="B144" s="6"/>
-      <c r="C144" s="6"/>
-      <c r="D144" s="6"/>
-      <c r="E144" s="6"/>
-      <c r="F144" s="6"/>
-      <c r="G144" s="6"/>
-      <c r="H144" s="6"/>
-      <c r="I144" s="6"/>
-    </row>
-    <row r="145" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A145" s="6"/>
-      <c r="B145" s="6"/>
-      <c r="C145" s="6"/>
-      <c r="D145" s="6"/>
-      <c r="E145" s="6"/>
-      <c r="F145" s="6"/>
-      <c r="G145" s="6"/>
-      <c r="H145" s="6"/>
-      <c r="I145" s="6"/>
-    </row>
-    <row r="146" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A146" s="6"/>
-      <c r="B146" s="6"/>
-      <c r="C146" s="6"/>
-      <c r="D146" s="6"/>
-      <c r="E146" s="6"/>
-      <c r="F146" s="6"/>
-      <c r="G146" s="6"/>
-      <c r="H146" s="6"/>
-      <c r="I146" s="6"/>
-    </row>
-    <row r="147" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A147" s="6"/>
-      <c r="B147" s="6"/>
-      <c r="C147" s="6"/>
-      <c r="D147" s="6"/>
-      <c r="E147" s="6"/>
-      <c r="F147" s="6"/>
-      <c r="G147" s="6"/>
-      <c r="H147" s="6"/>
-      <c r="I147" s="6"/>
-    </row>
-    <row r="148" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A148" s="6"/>
-      <c r="B148" s="6"/>
-      <c r="C148" s="6"/>
-      <c r="D148" s="6"/>
-      <c r="E148" s="6"/>
-      <c r="F148" s="6"/>
-      <c r="G148" s="6"/>
-      <c r="H148" s="6"/>
-      <c r="I148" s="6"/>
-    </row>
-    <row r="149" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A149" s="6"/>
-      <c r="B149" s="6"/>
-      <c r="C149" s="6"/>
-      <c r="D149" s="6"/>
-      <c r="E149" s="6"/>
-      <c r="F149" s="6"/>
-      <c r="G149" s="6"/>
-      <c r="H149" s="6"/>
-      <c r="I149" s="6"/>
-    </row>
-    <row r="150" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A150" s="6"/>
-      <c r="B150" s="6"/>
-      <c r="C150" s="6"/>
-      <c r="D150" s="6"/>
-      <c r="E150" s="6"/>
-      <c r="F150" s="6"/>
-      <c r="G150" s="6"/>
-      <c r="H150" s="6"/>
-      <c r="I150" s="6"/>
-    </row>
-    <row r="151" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A151" s="6"/>
-      <c r="B151" s="6"/>
-      <c r="C151" s="6"/>
-      <c r="D151" s="6"/>
-      <c r="E151" s="6"/>
-      <c r="F151" s="6"/>
-      <c r="G151" s="6"/>
-      <c r="H151" s="6"/>
-      <c r="I151" s="6"/>
-    </row>
-    <row r="152" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A152" s="6"/>
-      <c r="B152" s="6"/>
-      <c r="C152" s="6"/>
-      <c r="D152" s="6"/>
-      <c r="E152" s="6"/>
-      <c r="F152" s="6"/>
-      <c r="G152" s="6"/>
-      <c r="H152" s="6"/>
-      <c r="I152" s="6"/>
-    </row>
-    <row r="153" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A153" s="6"/>
-      <c r="B153" s="6"/>
-      <c r="C153" s="6"/>
-      <c r="D153" s="6"/>
-      <c r="E153" s="6"/>
-      <c r="F153" s="6"/>
-      <c r="G153" s="6"/>
-      <c r="H153" s="6"/>
-      <c r="I153" s="6"/>
-    </row>
-    <row r="154" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A154" s="6"/>
-      <c r="B154" s="6"/>
-      <c r="C154" s="6"/>
-      <c r="D154" s="6"/>
-      <c r="E154" s="6"/>
-      <c r="F154" s="6"/>
-      <c r="G154" s="6"/>
-      <c r="H154" s="6"/>
-      <c r="I154" s="6"/>
-    </row>
-    <row r="155" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A155" s="6"/>
-      <c r="B155" s="6"/>
-      <c r="C155" s="6"/>
-      <c r="D155" s="6"/>
-      <c r="E155" s="6"/>
-      <c r="F155" s="6"/>
-      <c r="G155" s="6"/>
-      <c r="H155" s="6"/>
-      <c r="I155" s="6"/>
-    </row>
-    <row r="156" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A156" s="6"/>
-      <c r="B156" s="6"/>
-      <c r="C156" s="6"/>
-      <c r="D156" s="6"/>
-      <c r="E156" s="6"/>
-      <c r="F156" s="6"/>
-      <c r="G156" s="6"/>
-      <c r="H156" s="6"/>
-      <c r="I156" s="6"/>
-    </row>
-    <row r="157" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A157" s="6"/>
-      <c r="B157" s="6"/>
-      <c r="C157" s="6"/>
-      <c r="D157" s="6"/>
-      <c r="E157" s="6"/>
-      <c r="F157" s="6"/>
-      <c r="G157" s="6"/>
-      <c r="H157" s="6"/>
-      <c r="I157" s="6"/>
-    </row>
-    <row r="158" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A158" s="6"/>
-      <c r="B158" s="6"/>
-      <c r="C158" s="6"/>
-      <c r="D158" s="6"/>
-      <c r="E158" s="6"/>
-      <c r="F158" s="6"/>
-      <c r="G158" s="6"/>
-      <c r="H158" s="6"/>
-      <c r="I158" s="6"/>
-    </row>
-    <row r="159" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A159" s="6"/>
-      <c r="B159" s="6"/>
-      <c r="C159" s="6"/>
-      <c r="D159" s="6"/>
-      <c r="E159" s="6"/>
-      <c r="F159" s="6"/>
-      <c r="G159" s="6"/>
-      <c r="H159" s="6"/>
-      <c r="I159" s="6"/>
-    </row>
-    <row r="160" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A160" s="6"/>
-      <c r="B160" s="6"/>
-      <c r="C160" s="6"/>
-      <c r="D160" s="6"/>
-      <c r="E160" s="6"/>
-      <c r="F160" s="6"/>
-      <c r="G160" s="6"/>
-      <c r="H160" s="6"/>
-      <c r="I160" s="6"/>
-    </row>
-    <row r="161" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A161" s="6"/>
-      <c r="B161" s="6"/>
-      <c r="C161" s="6"/>
-      <c r="D161" s="6"/>
-      <c r="E161" s="6"/>
-      <c r="F161" s="6"/>
-      <c r="G161" s="6"/>
-      <c r="H161" s="6"/>
-      <c r="I161" s="6"/>
-    </row>
-    <row r="162" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A162" s="6"/>
-      <c r="B162" s="6"/>
-      <c r="C162" s="6"/>
-      <c r="D162" s="6"/>
-      <c r="E162" s="6"/>
-      <c r="F162" s="6"/>
-      <c r="G162" s="6"/>
-      <c r="H162" s="6"/>
-      <c r="I162" s="6"/>
-    </row>
-    <row r="163" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A163" s="6"/>
-      <c r="B163" s="6"/>
-      <c r="C163" s="6"/>
-      <c r="D163" s="6"/>
-      <c r="E163" s="6"/>
-      <c r="F163" s="6"/>
-      <c r="G163" s="6"/>
-      <c r="H163" s="6"/>
-      <c r="I163" s="6"/>
-    </row>
-    <row r="164" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A164" s="6"/>
-      <c r="B164" s="6"/>
-      <c r="C164" s="6"/>
-      <c r="D164" s="6"/>
-      <c r="E164" s="6"/>
-      <c r="F164" s="6"/>
-      <c r="G164" s="6"/>
-      <c r="H164" s="6"/>
-      <c r="I164" s="6"/>
-    </row>
-    <row r="165" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A165" s="6"/>
-      <c r="B165" s="6"/>
-      <c r="C165" s="6"/>
-      <c r="D165" s="6"/>
-      <c r="E165" s="6"/>
-      <c r="F165" s="6"/>
-      <c r="G165" s="6"/>
-      <c r="H165" s="6"/>
-      <c r="I165" s="6"/>
-    </row>
-    <row r="166" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A166" s="6"/>
-      <c r="B166" s="6"/>
-      <c r="C166" s="6"/>
-      <c r="D166" s="6"/>
-      <c r="E166" s="6"/>
-      <c r="F166" s="6"/>
-      <c r="G166" s="6"/>
-      <c r="H166" s="6"/>
-      <c r="I166" s="6"/>
-    </row>
-    <row r="167" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A167" s="6"/>
-      <c r="B167" s="6"/>
-      <c r="C167" s="6"/>
-      <c r="D167" s="6"/>
-      <c r="E167" s="6"/>
-      <c r="F167" s="6"/>
-      <c r="G167" s="6"/>
-      <c r="H167" s="6"/>
-      <c r="I167" s="6"/>
-    </row>
-    <row r="168" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A168" s="6"/>
-      <c r="B168" s="6"/>
-      <c r="C168" s="6"/>
-      <c r="D168" s="6"/>
-      <c r="E168" s="6"/>
-      <c r="F168" s="6"/>
-      <c r="G168" s="6"/>
-      <c r="H168" s="6"/>
-      <c r="I168" s="6"/>
-    </row>
-    <row r="169" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A169" s="6"/>
-      <c r="B169" s="6"/>
-      <c r="C169" s="6"/>
-      <c r="D169" s="6"/>
-      <c r="E169" s="6"/>
-      <c r="F169" s="6"/>
-      <c r="G169" s="6"/>
-      <c r="H169" s="6"/>
-      <c r="I169" s="6"/>
-    </row>
-    <row r="170" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A170" s="6"/>
-      <c r="B170" s="6"/>
-      <c r="C170" s="6"/>
-      <c r="D170" s="6"/>
-      <c r="E170" s="6"/>
-      <c r="F170" s="6"/>
-      <c r="G170" s="6"/>
-      <c r="H170" s="6"/>
-      <c r="I170" s="6"/>
-    </row>
-    <row r="171" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A171" s="6"/>
-      <c r="B171" s="6"/>
-      <c r="C171" s="6"/>
-      <c r="D171" s="6"/>
-      <c r="E171" s="6"/>
-      <c r="F171" s="6"/>
-      <c r="G171" s="6"/>
-      <c r="H171" s="6"/>
-      <c r="I171" s="6"/>
-    </row>
-    <row r="172" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A172" s="6"/>
-      <c r="B172" s="6"/>
-      <c r="C172" s="6"/>
-      <c r="D172" s="6"/>
-      <c r="E172" s="6"/>
-      <c r="F172" s="6"/>
-      <c r="G172" s="6"/>
-      <c r="H172" s="6"/>
-      <c r="I172" s="6"/>
-    </row>
-    <row r="173" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A173" s="6"/>
-      <c r="B173" s="6"/>
-      <c r="C173" s="6"/>
-      <c r="D173" s="6"/>
-      <c r="E173" s="6"/>
-      <c r="F173" s="6"/>
-      <c r="G173" s="6"/>
-      <c r="H173" s="6"/>
-      <c r="I173" s="6"/>
-    </row>
-    <row r="174" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A174" s="6"/>
-      <c r="B174" s="6"/>
-      <c r="C174" s="6"/>
-      <c r="D174" s="6"/>
-      <c r="E174" s="6"/>
-      <c r="F174" s="6"/>
-      <c r="G174" s="6"/>
-      <c r="H174" s="6"/>
-      <c r="I174" s="6"/>
-    </row>
-    <row r="175" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A175" s="6"/>
-      <c r="B175" s="6"/>
-      <c r="C175" s="6"/>
-      <c r="D175" s="6"/>
-      <c r="E175" s="6"/>
-      <c r="F175" s="6"/>
-      <c r="G175" s="6"/>
-      <c r="H175" s="6"/>
-      <c r="I175" s="6"/>
-    </row>
-    <row r="176" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A176" s="6"/>
-      <c r="B176" s="6"/>
-      <c r="C176" s="6"/>
-      <c r="D176" s="6"/>
-      <c r="E176" s="6"/>
-      <c r="F176" s="6"/>
-      <c r="G176" s="6"/>
-      <c r="H176" s="6"/>
-      <c r="I176" s="6"/>
-    </row>
-    <row r="177" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A177" s="6"/>
-      <c r="B177" s="6"/>
-      <c r="C177" s="6"/>
-      <c r="D177" s="6"/>
-      <c r="E177" s="6"/>
-      <c r="F177" s="6"/>
-      <c r="G177" s="6"/>
-      <c r="H177" s="6"/>
-      <c r="I177" s="6"/>
-    </row>
-    <row r="178" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A178" s="6"/>
-      <c r="B178" s="6"/>
-      <c r="C178" s="6"/>
-      <c r="D178" s="6"/>
-      <c r="E178" s="6"/>
-      <c r="F178" s="6"/>
-      <c r="G178" s="6"/>
-      <c r="H178" s="6"/>
-      <c r="I178" s="6"/>
-    </row>
-    <row r="179" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A179" s="6"/>
-      <c r="B179" s="6"/>
-      <c r="C179" s="6"/>
-      <c r="D179" s="6"/>
-      <c r="E179" s="6"/>
-      <c r="F179" s="6"/>
-      <c r="G179" s="6"/>
-      <c r="H179" s="6"/>
-      <c r="I179" s="6"/>
-    </row>
-    <row r="180" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A180" s="6"/>
-      <c r="B180" s="6"/>
-      <c r="C180" s="6"/>
-      <c r="D180" s="6"/>
-      <c r="E180" s="6"/>
-      <c r="F180" s="6"/>
-      <c r="G180" s="6"/>
-      <c r="H180" s="6"/>
-      <c r="I180" s="6"/>
-    </row>
-    <row r="181" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A181" s="6"/>
-      <c r="B181" s="6"/>
-      <c r="C181" s="6"/>
-      <c r="D181" s="6"/>
-      <c r="E181" s="6"/>
-      <c r="F181" s="6"/>
-      <c r="G181" s="6"/>
-      <c r="H181" s="6"/>
-      <c r="I181" s="6"/>
-    </row>
-    <row r="182" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A182" s="6"/>
-      <c r="B182" s="6"/>
-      <c r="C182" s="6"/>
-      <c r="D182" s="6"/>
-      <c r="E182" s="6"/>
-      <c r="F182" s="6"/>
-      <c r="G182" s="6"/>
-      <c r="H182" s="6"/>
-      <c r="I182" s="6"/>
-    </row>
-    <row r="183" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A183" s="6"/>
-      <c r="B183" s="6"/>
-      <c r="C183" s="6"/>
-      <c r="D183" s="6"/>
-      <c r="E183" s="6"/>
-      <c r="F183" s="6"/>
-      <c r="G183" s="6"/>
-      <c r="H183" s="6"/>
-      <c r="I183" s="6"/>
-    </row>
-    <row r="184" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A184" s="6"/>
-      <c r="B184" s="6"/>
-      <c r="C184" s="6"/>
-      <c r="D184" s="6"/>
-      <c r="E184" s="6"/>
-      <c r="F184" s="6"/>
-      <c r="G184" s="6"/>
-      <c r="H184" s="6"/>
-      <c r="I184" s="6"/>
-    </row>
-    <row r="185" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A185" s="6"/>
-      <c r="B185" s="6"/>
-      <c r="C185" s="6"/>
-      <c r="D185" s="6"/>
-      <c r="E185" s="6"/>
-      <c r="F185" s="6"/>
-      <c r="G185" s="6"/>
-      <c r="H185" s="6"/>
-      <c r="I185" s="6"/>
-    </row>
-    <row r="186" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A186" s="6"/>
-      <c r="B186" s="6"/>
-      <c r="C186" s="6"/>
-      <c r="D186" s="6"/>
-      <c r="E186" s="6"/>
-      <c r="F186" s="6"/>
-      <c r="G186" s="6"/>
-      <c r="H186" s="6"/>
-      <c r="I186" s="6"/>
-    </row>
-    <row r="187" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A187" s="6"/>
-      <c r="B187" s="6"/>
-      <c r="C187" s="6"/>
-      <c r="D187" s="6"/>
-      <c r="E187" s="6"/>
-      <c r="F187" s="6"/>
-      <c r="G187" s="6"/>
-      <c r="H187" s="6"/>
-      <c r="I187" s="6"/>
-    </row>
-    <row r="188" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A188" s="6"/>
-      <c r="B188" s="6"/>
-      <c r="C188" s="6"/>
-      <c r="D188" s="6"/>
-      <c r="E188" s="6"/>
-      <c r="F188" s="6"/>
-      <c r="G188" s="6"/>
-      <c r="H188" s="6"/>
-      <c r="I188" s="6"/>
-    </row>
-    <row r="189" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A189" s="6"/>
-      <c r="B189" s="6"/>
-      <c r="C189" s="6"/>
-      <c r="D189" s="6"/>
-      <c r="E189" s="6"/>
-      <c r="F189" s="6"/>
-      <c r="G189" s="6"/>
-      <c r="H189" s="6"/>
-      <c r="I189" s="6"/>
-    </row>
-    <row r="190" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A190" s="6"/>
-      <c r="B190" s="6"/>
-      <c r="C190" s="6"/>
-      <c r="D190" s="6"/>
-      <c r="E190" s="6"/>
-      <c r="F190" s="6"/>
-      <c r="G190" s="6"/>
-      <c r="H190" s="6"/>
-      <c r="I190" s="6"/>
-    </row>
-    <row r="191" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A191" s="6"/>
-      <c r="B191" s="6"/>
-      <c r="C191" s="6"/>
-      <c r="D191" s="6"/>
-      <c r="E191" s="6"/>
-      <c r="F191" s="6"/>
-      <c r="G191" s="6"/>
-      <c r="H191" s="6"/>
-      <c r="I191" s="6"/>
-    </row>
-    <row r="192" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A192" s="6"/>
-      <c r="B192" s="6"/>
-      <c r="C192" s="6"/>
-      <c r="D192" s="6"/>
-      <c r="E192" s="6"/>
-      <c r="F192" s="6"/>
-      <c r="G192" s="6"/>
-      <c r="H192" s="6"/>
-      <c r="I192" s="6"/>
-    </row>
-    <row r="193" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A193" s="6"/>
-      <c r="B193" s="6"/>
-      <c r="C193" s="6"/>
-      <c r="D193" s="6"/>
-      <c r="E193" s="6"/>
-      <c r="F193" s="6"/>
-      <c r="G193" s="6"/>
-      <c r="H193" s="6"/>
-      <c r="I193" s="6"/>
-    </row>
-    <row r="194" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A194" s="6"/>
-      <c r="B194" s="6"/>
-      <c r="C194" s="6"/>
-      <c r="D194" s="6"/>
-      <c r="E194" s="6"/>
-      <c r="F194" s="6"/>
-      <c r="G194" s="6"/>
-      <c r="H194" s="6"/>
-      <c r="I194" s="6"/>
-    </row>
-    <row r="195" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A195" s="6"/>
-      <c r="B195" s="6"/>
-      <c r="C195" s="6"/>
-      <c r="D195" s="6"/>
-      <c r="E195" s="6"/>
-      <c r="F195" s="6"/>
-      <c r="G195" s="6"/>
-      <c r="H195" s="6"/>
-      <c r="I195" s="6"/>
-    </row>
-    <row r="196" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A196" s="6"/>
-      <c r="B196" s="6"/>
-      <c r="C196" s="6"/>
-      <c r="D196" s="6"/>
-      <c r="E196" s="6"/>
-      <c r="F196" s="6"/>
-      <c r="G196" s="6"/>
-      <c r="H196" s="6"/>
-      <c r="I196" s="6"/>
-    </row>
-    <row r="197" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A197" s="6"/>
-      <c r="B197" s="6"/>
-      <c r="C197" s="6"/>
-      <c r="D197" s="6"/>
-      <c r="E197" s="6"/>
-      <c r="F197" s="6"/>
-      <c r="G197" s="6"/>
-      <c r="H197" s="6"/>
-      <c r="I197" s="6"/>
-    </row>
-    <row r="198" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A198" s="6"/>
-      <c r="B198" s="6"/>
-      <c r="C198" s="6"/>
-      <c r="D198" s="6"/>
-      <c r="E198" s="6"/>
-      <c r="F198" s="6"/>
-      <c r="G198" s="6"/>
-      <c r="H198" s="6"/>
-      <c r="I198" s="6"/>
-    </row>
-    <row r="199" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A199" s="6"/>
-      <c r="B199" s="6"/>
-      <c r="C199" s="6"/>
-      <c r="D199" s="6"/>
-      <c r="E199" s="6"/>
-      <c r="F199" s="6"/>
-      <c r="G199" s="6"/>
-      <c r="H199" s="6"/>
-      <c r="I199" s="6"/>
-    </row>
-    <row r="200" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A200" s="6"/>
-      <c r="B200" s="6"/>
-      <c r="C200" s="6"/>
-      <c r="D200" s="6"/>
-      <c r="E200" s="6"/>
-      <c r="F200" s="6"/>
-      <c r="G200" s="6"/>
-      <c r="H200" s="6"/>
-      <c r="I200" s="6"/>
-    </row>
-    <row r="201" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A201" s="6"/>
-      <c r="B201" s="6"/>
-      <c r="C201" s="6"/>
-      <c r="D201" s="6"/>
-      <c r="E201" s="6"/>
-      <c r="F201" s="6"/>
-      <c r="G201" s="6"/>
-      <c r="H201" s="6"/>
-      <c r="I201" s="6"/>
-    </row>
-    <row r="202" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A202" s="6"/>
-      <c r="B202" s="6"/>
-      <c r="C202" s="6"/>
-      <c r="D202" s="6"/>
-      <c r="E202" s="6"/>
-      <c r="F202" s="6"/>
-      <c r="G202" s="6"/>
-      <c r="H202" s="6"/>
-      <c r="I202" s="6"/>
-    </row>
-    <row r="203" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A203" s="6"/>
-      <c r="B203" s="6"/>
-      <c r="C203" s="6"/>
-      <c r="D203" s="6"/>
-      <c r="E203" s="6"/>
-      <c r="F203" s="6"/>
-      <c r="G203" s="6"/>
-      <c r="H203" s="6"/>
-      <c r="I203" s="6"/>
-    </row>
-    <row r="204" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A204" s="6"/>
-      <c r="B204" s="6"/>
-      <c r="C204" s="6"/>
-      <c r="D204" s="6"/>
-      <c r="E204" s="6"/>
-      <c r="F204" s="6"/>
-      <c r="G204" s="6"/>
-      <c r="H204" s="6"/>
-      <c r="I204" s="6"/>
-    </row>
-    <row r="205" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A205" s="6"/>
-      <c r="B205" s="6"/>
-      <c r="C205" s="6"/>
-      <c r="D205" s="6"/>
-      <c r="E205" s="6"/>
-      <c r="F205" s="6"/>
-      <c r="G205" s="6"/>
-      <c r="H205" s="6"/>
-      <c r="I205" s="6"/>
-    </row>
-    <row r="206" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A206" s="6"/>
-      <c r="B206" s="6"/>
-      <c r="C206" s="6"/>
-      <c r="D206" s="6"/>
-      <c r="E206" s="6"/>
-      <c r="F206" s="6"/>
-      <c r="G206" s="6"/>
-      <c r="H206" s="6"/>
-      <c r="I206" s="6"/>
-    </row>
-    <row r="207" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A207" s="6"/>
-      <c r="B207" s="6"/>
-      <c r="C207" s="6"/>
-      <c r="D207" s="6"/>
-      <c r="E207" s="6"/>
-      <c r="F207" s="6"/>
-      <c r="G207" s="6"/>
-      <c r="H207" s="6"/>
-      <c r="I207" s="6"/>
-    </row>
-    <row r="208" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A208" s="6"/>
-      <c r="B208" s="6"/>
-      <c r="C208" s="6"/>
-      <c r="D208" s="6"/>
-      <c r="E208" s="6"/>
-      <c r="F208" s="6"/>
-      <c r="G208" s="6"/>
-      <c r="H208" s="6"/>
-      <c r="I208" s="6"/>
-    </row>
-    <row r="209" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A209" s="6"/>
-      <c r="B209" s="6"/>
-      <c r="C209" s="6"/>
-      <c r="D209" s="6"/>
-      <c r="E209" s="6"/>
-      <c r="F209" s="6"/>
-      <c r="G209" s="6"/>
-      <c r="H209" s="6"/>
-      <c r="I209" s="6"/>
-    </row>
-    <row r="210" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A210" s="6"/>
-      <c r="B210" s="6"/>
-      <c r="C210" s="6"/>
-      <c r="D210" s="6"/>
-      <c r="E210" s="6"/>
-      <c r="F210" s="6"/>
-      <c r="G210" s="6"/>
-      <c r="H210" s="6"/>
-      <c r="I210" s="6"/>
-    </row>
-    <row r="211" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A211" s="6"/>
-      <c r="B211" s="6"/>
-      <c r="C211" s="6"/>
-      <c r="D211" s="6"/>
-      <c r="E211" s="6"/>
-      <c r="F211" s="6"/>
-      <c r="G211" s="6"/>
-      <c r="H211" s="6"/>
-      <c r="I211" s="6"/>
-    </row>
-    <row r="212" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A212" s="6"/>
-      <c r="B212" s="6"/>
-      <c r="C212" s="6"/>
-      <c r="D212" s="6"/>
-      <c r="E212" s="6"/>
-      <c r="F212" s="6"/>
-      <c r="G212" s="6"/>
-      <c r="H212" s="6"/>
-      <c r="I212" s="6"/>
-    </row>
-    <row r="213" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A213" s="6"/>
-      <c r="B213" s="6"/>
-      <c r="C213" s="6"/>
-      <c r="D213" s="6"/>
-      <c r="E213" s="6"/>
-      <c r="F213" s="6"/>
-      <c r="G213" s="6"/>
-      <c r="H213" s="6"/>
-      <c r="I213" s="6"/>
-    </row>
-    <row r="214" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A214" s="6"/>
-      <c r="B214" s="6"/>
-      <c r="C214" s="6"/>
-      <c r="D214" s="6"/>
-      <c r="E214" s="6"/>
-      <c r="F214" s="6"/>
-      <c r="G214" s="6"/>
-      <c r="H214" s="6"/>
-      <c r="I214" s="6"/>
-    </row>
-    <row r="215" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A215" s="6"/>
-      <c r="B215" s="6"/>
-      <c r="C215" s="6"/>
-      <c r="D215" s="6"/>
-      <c r="E215" s="6"/>
-      <c r="F215" s="6"/>
-      <c r="G215" s="6"/>
-      <c r="H215" s="6"/>
-      <c r="I215" s="6"/>
-    </row>
-    <row r="216" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A216" s="6"/>
-      <c r="B216" s="6"/>
-      <c r="C216" s="6"/>
-      <c r="D216" s="6"/>
-      <c r="E216" s="6"/>
-      <c r="F216" s="6"/>
-      <c r="G216" s="6"/>
-      <c r="H216" s="6"/>
-      <c r="I216" s="6"/>
-    </row>
-    <row r="217" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A217" s="6"/>
-      <c r="B217" s="6"/>
-      <c r="C217" s="6"/>
-      <c r="D217" s="6"/>
-      <c r="E217" s="6"/>
-      <c r="F217" s="6"/>
-      <c r="G217" s="6"/>
-      <c r="H217" s="6"/>
-      <c r="I217" s="6"/>
-    </row>
-    <row r="218" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A218" s="6"/>
-      <c r="B218" s="6"/>
-      <c r="C218" s="6"/>
-      <c r="D218" s="6"/>
-      <c r="E218" s="6"/>
-      <c r="F218" s="6"/>
-      <c r="G218" s="6"/>
-      <c r="H218" s="6"/>
-      <c r="I218" s="6"/>
-    </row>
-    <row r="219" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A219" s="6"/>
-      <c r="B219" s="6"/>
-      <c r="C219" s="6"/>
-      <c r="D219" s="6"/>
-      <c r="E219" s="6"/>
-      <c r="F219" s="6"/>
-      <c r="G219" s="6"/>
-      <c r="H219" s="6"/>
-      <c r="I219" s="6"/>
-    </row>
-    <row r="220" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A220" s="6"/>
-      <c r="B220" s="6"/>
-      <c r="C220" s="6"/>
-      <c r="D220" s="6"/>
-      <c r="E220" s="6"/>
-      <c r="F220" s="6"/>
-      <c r="G220" s="6"/>
-      <c r="H220" s="6"/>
-      <c r="I220" s="6"/>
-    </row>
-    <row r="221" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A221" s="6"/>
-      <c r="B221" s="6"/>
-      <c r="C221" s="6"/>
-      <c r="D221" s="6"/>
-      <c r="E221" s="6"/>
-      <c r="F221" s="6"/>
-      <c r="G221" s="6"/>
-      <c r="H221" s="6"/>
-      <c r="I221" s="6"/>
+    <row r="26" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>93</v>
+      </c>
+      <c r="B26" t="s">
+        <v>94</v>
+      </c>
+      <c r="C26" t="s">
+        <v>62</v>
+      </c>
+      <c r="D26" t="s">
+        <v>63</v>
+      </c>
+      <c r="E26" t="s">
+        <v>10</v>
+      </c>
+      <c r="F26" t="s">
+        <v>95</v>
+      </c>
+      <c r="G26" t="s">
+        <v>63</v>
+      </c>
+      <c r="H26" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="27" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>96</v>
+      </c>
+      <c r="B27" t="s">
+        <v>97</v>
+      </c>
+      <c r="C27" t="s">
+        <v>62</v>
+      </c>
+      <c r="D27" t="s">
+        <v>63</v>
+      </c>
+      <c r="E27" t="s">
+        <v>10</v>
+      </c>
+      <c r="F27" t="s">
+        <v>98</v>
+      </c>
+      <c r="G27" t="s">
+        <v>63</v>
+      </c>
+      <c r="H27" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="28" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>99</v>
+      </c>
+      <c r="B28" t="s">
+        <v>100</v>
+      </c>
+      <c r="C28" t="s">
+        <v>62</v>
+      </c>
+      <c r="D28" t="s">
+        <v>63</v>
+      </c>
+      <c r="E28" t="s">
+        <v>10</v>
+      </c>
+      <c r="F28" t="s">
+        <v>101</v>
+      </c>
+      <c r="G28" t="s">
+        <v>63</v>
+      </c>
+      <c r="H28" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="29" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>102</v>
+      </c>
+      <c r="B29" t="s">
+        <v>103</v>
+      </c>
+      <c r="C29" t="s">
+        <v>62</v>
+      </c>
+      <c r="D29" t="s">
+        <v>63</v>
+      </c>
+      <c r="E29" t="s">
+        <v>10</v>
+      </c>
+      <c r="F29" t="s">
+        <v>104</v>
+      </c>
+      <c r="G29" t="s">
+        <v>63</v>
+      </c>
+      <c r="H29" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="30" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>105</v>
+      </c>
+      <c r="B30" t="s">
+        <v>106</v>
+      </c>
+      <c r="C30" t="s">
+        <v>62</v>
+      </c>
+      <c r="D30" t="s">
+        <v>63</v>
+      </c>
+      <c r="E30" t="s">
+        <v>10</v>
+      </c>
+      <c r="F30" t="s">
+        <v>107</v>
+      </c>
+      <c r="G30" t="s">
+        <v>63</v>
+      </c>
+      <c r="H30" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="31" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>108</v>
+      </c>
+      <c r="B31" t="s">
+        <v>109</v>
+      </c>
+      <c r="C31" t="s">
+        <v>62</v>
+      </c>
+      <c r="D31" t="s">
+        <v>63</v>
+      </c>
+      <c r="E31" t="s">
+        <v>10</v>
+      </c>
+      <c r="F31" t="s">
+        <v>110</v>
+      </c>
+      <c r="G31" t="s">
+        <v>63</v>
+      </c>
+      <c r="H31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="32" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>111</v>
+      </c>
+      <c r="B32" t="s">
+        <v>112</v>
+      </c>
+      <c r="C32" t="s">
+        <v>62</v>
+      </c>
+      <c r="D32" t="s">
+        <v>63</v>
+      </c>
+      <c r="E32" t="s">
+        <v>10</v>
+      </c>
+      <c r="F32" t="s">
+        <v>113</v>
+      </c>
+      <c r="G32" t="s">
+        <v>63</v>
+      </c>
+      <c r="H32" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="33" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>114</v>
+      </c>
+      <c r="B33" t="s">
+        <v>115</v>
+      </c>
+      <c r="C33" t="s">
+        <v>62</v>
+      </c>
+      <c r="D33" t="s">
+        <v>63</v>
+      </c>
+      <c r="E33" t="s">
+        <v>10</v>
+      </c>
+      <c r="F33" t="s">
+        <v>116</v>
+      </c>
+      <c r="G33" t="s">
+        <v>63</v>
+      </c>
+      <c r="H33" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="34" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>117</v>
+      </c>
+      <c r="B34" t="s">
+        <v>118</v>
+      </c>
+      <c r="C34" t="s">
+        <v>62</v>
+      </c>
+      <c r="D34" t="s">
+        <v>63</v>
+      </c>
+      <c r="E34" t="s">
+        <v>10</v>
+      </c>
+      <c r="F34" t="s">
+        <v>119</v>
+      </c>
+      <c r="G34" t="s">
+        <v>63</v>
+      </c>
+      <c r="H34" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="35" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>120</v>
+      </c>
+      <c r="B35" t="s">
+        <v>121</v>
+      </c>
+      <c r="C35" t="s">
+        <v>62</v>
+      </c>
+      <c r="D35" t="s">
+        <v>63</v>
+      </c>
+      <c r="E35" t="s">
+        <v>10</v>
+      </c>
+      <c r="F35" t="s">
+        <v>122</v>
+      </c>
+      <c r="G35" t="s">
+        <v>63</v>
+      </c>
+      <c r="H35" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="36" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>123</v>
+      </c>
+      <c r="B36" t="s">
+        <v>124</v>
+      </c>
+      <c r="C36" t="s">
+        <v>62</v>
+      </c>
+      <c r="D36" t="s">
+        <v>63</v>
+      </c>
+      <c r="E36" t="s">
+        <v>10</v>
+      </c>
+      <c r="F36" t="s">
+        <v>125</v>
+      </c>
+      <c r="G36" t="s">
+        <v>63</v>
+      </c>
+      <c r="H36" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="37" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>126</v>
+      </c>
+      <c r="B37" t="s">
+        <v>127</v>
+      </c>
+      <c r="C37" t="s">
+        <v>62</v>
+      </c>
+      <c r="D37" t="s">
+        <v>63</v>
+      </c>
+      <c r="E37" t="s">
+        <v>10</v>
+      </c>
+      <c r="F37" t="s">
+        <v>67</v>
+      </c>
+      <c r="G37" t="s">
+        <v>63</v>
+      </c>
+      <c r="H37" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="38" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>128</v>
+      </c>
+      <c r="B38" t="s">
+        <v>129</v>
+      </c>
+      <c r="C38" t="s">
+        <v>62</v>
+      </c>
+      <c r="D38" t="s">
+        <v>63</v>
+      </c>
+      <c r="E38" t="s">
+        <v>10</v>
+      </c>
+      <c r="F38" t="s">
+        <v>67</v>
+      </c>
+      <c r="G38" t="s">
+        <v>63</v>
+      </c>
+      <c r="H38" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="39" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>130</v>
+      </c>
+      <c r="B39" t="s">
+        <v>131</v>
+      </c>
+      <c r="C39" t="s">
+        <v>62</v>
+      </c>
+      <c r="D39" t="s">
+        <v>63</v>
+      </c>
+      <c r="E39" t="s">
+        <v>10</v>
+      </c>
+      <c r="F39" t="s">
+        <v>132</v>
+      </c>
+      <c r="G39" t="s">
+        <v>63</v>
+      </c>
+      <c r="H39" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="40" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>133</v>
+      </c>
+      <c r="B40" t="s">
+        <v>134</v>
+      </c>
+      <c r="C40" t="s">
+        <v>62</v>
+      </c>
+      <c r="D40" t="s">
+        <v>63</v>
+      </c>
+      <c r="E40" t="s">
+        <v>10</v>
+      </c>
+      <c r="F40" t="s">
+        <v>135</v>
+      </c>
+      <c r="G40" t="s">
+        <v>63</v>
+      </c>
+      <c r="H40" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="41" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>136</v>
+      </c>
+      <c r="B41" t="s">
+        <v>137</v>
+      </c>
+      <c r="C41" t="s">
+        <v>62</v>
+      </c>
+      <c r="D41" t="s">
+        <v>63</v>
+      </c>
+      <c r="E41" t="s">
+        <v>10</v>
+      </c>
+      <c r="F41" t="s">
+        <v>138</v>
+      </c>
+      <c r="G41" t="s">
+        <v>63</v>
+      </c>
+      <c r="H41" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="42" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>139</v>
+      </c>
+      <c r="B42" t="s">
+        <v>140</v>
+      </c>
+      <c r="C42" t="s">
+        <v>62</v>
+      </c>
+      <c r="D42" t="s">
+        <v>63</v>
+      </c>
+      <c r="E42" t="s">
+        <v>10</v>
+      </c>
+      <c r="F42" t="s">
+        <v>141</v>
+      </c>
+      <c r="G42" t="s">
+        <v>63</v>
+      </c>
+      <c r="H42" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="43" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>142</v>
+      </c>
+      <c r="B43" t="s">
+        <v>143</v>
+      </c>
+      <c r="C43" t="s">
+        <v>62</v>
+      </c>
+      <c r="D43" t="s">
+        <v>63</v>
+      </c>
+      <c r="E43" t="s">
+        <v>10</v>
+      </c>
+      <c r="F43" t="s">
+        <v>122</v>
+      </c>
+      <c r="G43" t="s">
+        <v>63</v>
+      </c>
+      <c r="H43" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="44" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>144</v>
+      </c>
+      <c r="B44" t="s">
+        <v>145</v>
+      </c>
+      <c r="C44" t="s">
+        <v>62</v>
+      </c>
+      <c r="D44" t="s">
+        <v>63</v>
+      </c>
+      <c r="E44" t="s">
+        <v>10</v>
+      </c>
+      <c r="F44" t="s">
+        <v>122</v>
+      </c>
+      <c r="G44" t="s">
+        <v>63</v>
+      </c>
+      <c r="H44" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="45" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>146</v>
+      </c>
+      <c r="B45" t="s">
+        <v>147</v>
+      </c>
+      <c r="C45" t="s">
+        <v>62</v>
+      </c>
+      <c r="D45" t="s">
+        <v>63</v>
+      </c>
+      <c r="E45" t="s">
+        <v>10</v>
+      </c>
+      <c r="F45" t="s">
+        <v>148</v>
+      </c>
+      <c r="G45" t="s">
+        <v>63</v>
+      </c>
+      <c r="H45" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="46" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>149</v>
+      </c>
+      <c r="B46" t="s">
+        <v>150</v>
+      </c>
+      <c r="C46" t="s">
+        <v>62</v>
+      </c>
+      <c r="D46" t="s">
+        <v>63</v>
+      </c>
+      <c r="E46" t="s">
+        <v>10</v>
+      </c>
+      <c r="F46" t="s">
+        <v>151</v>
+      </c>
+      <c r="G46" t="s">
+        <v>63</v>
+      </c>
+      <c r="H46" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="47" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>152</v>
+      </c>
+      <c r="B47" t="s">
+        <v>153</v>
+      </c>
+      <c r="C47" t="s">
+        <v>62</v>
+      </c>
+      <c r="D47" t="s">
+        <v>63</v>
+      </c>
+      <c r="E47" t="s">
+        <v>10</v>
+      </c>
+      <c r="F47" t="s">
+        <v>154</v>
+      </c>
+      <c r="G47" t="s">
+        <v>63</v>
+      </c>
+      <c r="H47" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="48" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>155</v>
+      </c>
+      <c r="B48" t="s">
+        <v>156</v>
+      </c>
+      <c r="C48" t="s">
+        <v>62</v>
+      </c>
+      <c r="D48" t="s">
+        <v>63</v>
+      </c>
+      <c r="E48" t="s">
+        <v>10</v>
+      </c>
+      <c r="F48" t="s">
+        <v>148</v>
+      </c>
+      <c r="G48" t="s">
+        <v>63</v>
+      </c>
+      <c r="H48" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="49" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>157</v>
+      </c>
+      <c r="B49" t="s">
+        <v>158</v>
+      </c>
+      <c r="C49" t="s">
+        <v>62</v>
+      </c>
+      <c r="D49" t="s">
+        <v>63</v>
+      </c>
+      <c r="E49" t="s">
+        <v>10</v>
+      </c>
+      <c r="F49" t="s">
+        <v>122</v>
+      </c>
+      <c r="G49" t="s">
+        <v>63</v>
+      </c>
+      <c r="H49" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="50" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>159</v>
+      </c>
+      <c r="B50" t="s">
+        <v>160</v>
+      </c>
+      <c r="C50" t="s">
+        <v>62</v>
+      </c>
+      <c r="D50" t="s">
+        <v>63</v>
+      </c>
+      <c r="E50" t="s">
+        <v>10</v>
+      </c>
+      <c r="F50" t="s">
+        <v>148</v>
+      </c>
+      <c r="G50" t="s">
+        <v>63</v>
+      </c>
+      <c r="H50" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="51" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>161</v>
+      </c>
+      <c r="B51" t="s">
+        <v>162</v>
+      </c>
+      <c r="C51" t="s">
+        <v>62</v>
+      </c>
+      <c r="D51" t="s">
+        <v>63</v>
+      </c>
+      <c r="E51" t="s">
+        <v>10</v>
+      </c>
+      <c r="F51" t="s">
+        <v>122</v>
+      </c>
+      <c r="G51" t="s">
+        <v>63</v>
+      </c>
+      <c r="H51" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="52" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>163</v>
+      </c>
+      <c r="B52" t="s">
+        <v>164</v>
+      </c>
+      <c r="C52" t="s">
+        <v>62</v>
+      </c>
+      <c r="D52" t="s">
+        <v>63</v>
+      </c>
+      <c r="E52" t="s">
+        <v>10</v>
+      </c>
+      <c r="F52" t="s">
+        <v>165</v>
+      </c>
+      <c r="G52" t="s">
+        <v>63</v>
+      </c>
+      <c r="H52" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="53" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>166</v>
+      </c>
+      <c r="B53" t="s">
+        <v>167</v>
+      </c>
+      <c r="C53" t="s">
+        <v>62</v>
+      </c>
+      <c r="D53" t="s">
+        <v>63</v>
+      </c>
+      <c r="E53" t="s">
+        <v>10</v>
+      </c>
+      <c r="F53" t="s">
+        <v>122</v>
+      </c>
+      <c r="G53" t="s">
+        <v>63</v>
+      </c>
+      <c r="H53" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="54" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>168</v>
+      </c>
+      <c r="B54" t="s">
+        <v>169</v>
+      </c>
+      <c r="C54" t="s">
+        <v>62</v>
+      </c>
+      <c r="D54" t="s">
+        <v>63</v>
+      </c>
+      <c r="E54" t="s">
+        <v>10</v>
+      </c>
+      <c r="F54" t="s">
+        <v>116</v>
+      </c>
+      <c r="G54" t="s">
+        <v>63</v>
+      </c>
+      <c r="H54" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="55" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>170</v>
+      </c>
+      <c r="B55" t="s">
+        <v>171</v>
+      </c>
+      <c r="C55" t="s">
+        <v>62</v>
+      </c>
+      <c r="D55" t="s">
+        <v>63</v>
+      </c>
+      <c r="E55" t="s">
+        <v>10</v>
+      </c>
+      <c r="F55" t="s">
+        <v>172</v>
+      </c>
+      <c r="G55" t="s">
+        <v>63</v>
+      </c>
+      <c r="H55" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="56" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>173</v>
+      </c>
+      <c r="B56" t="s">
+        <v>174</v>
+      </c>
+      <c r="C56" t="s">
+        <v>62</v>
+      </c>
+      <c r="D56" t="s">
+        <v>63</v>
+      </c>
+      <c r="E56" t="s">
+        <v>10</v>
+      </c>
+      <c r="F56" t="s">
+        <v>175</v>
+      </c>
+      <c r="G56" t="s">
+        <v>63</v>
+      </c>
+      <c r="H56" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="57" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>176</v>
+      </c>
+      <c r="B57" t="s">
+        <v>177</v>
+      </c>
+      <c r="C57" t="s">
+        <v>62</v>
+      </c>
+      <c r="D57" t="s">
+        <v>63</v>
+      </c>
+      <c r="E57" t="s">
+        <v>10</v>
+      </c>
+      <c r="F57" t="s">
+        <v>67</v>
+      </c>
+      <c r="G57" t="s">
+        <v>63</v>
+      </c>
+      <c r="H57" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="58" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>178</v>
+      </c>
+      <c r="B58" t="s">
+        <v>179</v>
+      </c>
+      <c r="C58" t="s">
+        <v>62</v>
+      </c>
+      <c r="D58" t="s">
+        <v>63</v>
+      </c>
+      <c r="E58" t="s">
+        <v>10</v>
+      </c>
+      <c r="F58" t="s">
+        <v>180</v>
+      </c>
+      <c r="G58" t="s">
+        <v>63</v>
+      </c>
+      <c r="H58" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="59" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>181</v>
+      </c>
+      <c r="B59" t="s">
+        <v>182</v>
+      </c>
+      <c r="C59" t="s">
+        <v>62</v>
+      </c>
+      <c r="D59" t="s">
+        <v>63</v>
+      </c>
+      <c r="E59" t="s">
+        <v>10</v>
+      </c>
+      <c r="F59" t="s">
+        <v>180</v>
+      </c>
+      <c r="G59" t="s">
+        <v>63</v>
+      </c>
+      <c r="H59" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="60" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>183</v>
+      </c>
+      <c r="B60" t="s">
+        <v>184</v>
+      </c>
+      <c r="C60" t="s">
+        <v>62</v>
+      </c>
+      <c r="D60" t="s">
+        <v>63</v>
+      </c>
+      <c r="E60" t="s">
+        <v>10</v>
+      </c>
+      <c r="F60" t="s">
+        <v>185</v>
+      </c>
+      <c r="G60" t="s">
+        <v>63</v>
+      </c>
+      <c r="H60" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="61" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>186</v>
+      </c>
+      <c r="B61" t="s">
+        <v>187</v>
+      </c>
+      <c r="C61" t="s">
+        <v>62</v>
+      </c>
+      <c r="D61" t="s">
+        <v>63</v>
+      </c>
+      <c r="E61" t="s">
+        <v>10</v>
+      </c>
+      <c r="F61" t="s">
+        <v>188</v>
+      </c>
+      <c r="G61" t="s">
+        <v>63</v>
+      </c>
+      <c r="H61" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="62" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>189</v>
+      </c>
+      <c r="B62" t="s">
+        <v>190</v>
+      </c>
+      <c r="C62" t="s">
+        <v>62</v>
+      </c>
+      <c r="D62" t="s">
+        <v>63</v>
+      </c>
+      <c r="E62" t="s">
+        <v>10</v>
+      </c>
+      <c r="F62" t="s">
+        <v>191</v>
+      </c>
+      <c r="G62" t="s">
+        <v>63</v>
+      </c>
+      <c r="H62" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="63" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>192</v>
+      </c>
+      <c r="B63" t="s">
+        <v>193</v>
+      </c>
+      <c r="C63" t="s">
+        <v>62</v>
+      </c>
+      <c r="D63" t="s">
+        <v>63</v>
+      </c>
+      <c r="E63" t="s">
+        <v>10</v>
+      </c>
+      <c r="F63" t="s">
+        <v>194</v>
+      </c>
+      <c r="G63" t="s">
+        <v>63</v>
+      </c>
+      <c r="H63" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="64" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>195</v>
+      </c>
+      <c r="B64" t="s">
+        <v>196</v>
+      </c>
+      <c r="C64" t="s">
+        <v>62</v>
+      </c>
+      <c r="D64" t="s">
+        <v>63</v>
+      </c>
+      <c r="E64" t="s">
+        <v>10</v>
+      </c>
+      <c r="F64" t="s">
+        <v>67</v>
+      </c>
+      <c r="G64" t="s">
+        <v>63</v>
+      </c>
+      <c r="H64" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="65" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>197</v>
+      </c>
+      <c r="B65" t="s">
+        <v>198</v>
+      </c>
+      <c r="C65" t="s">
+        <v>62</v>
+      </c>
+      <c r="D65" t="s">
+        <v>63</v>
+      </c>
+      <c r="E65" t="s">
+        <v>10</v>
+      </c>
+      <c r="F65" t="s">
+        <v>67</v>
+      </c>
+      <c r="G65" t="s">
+        <v>63</v>
+      </c>
+      <c r="H65" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="66" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>199</v>
+      </c>
+      <c r="B66" t="s">
+        <v>200</v>
+      </c>
+      <c r="C66" t="s">
+        <v>62</v>
+      </c>
+      <c r="D66" t="s">
+        <v>63</v>
+      </c>
+      <c r="E66" t="s">
+        <v>10</v>
+      </c>
+      <c r="F66" t="s">
+        <v>201</v>
+      </c>
+      <c r="G66" t="s">
+        <v>63</v>
+      </c>
+      <c r="H66" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="67" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>202</v>
+      </c>
+      <c r="B67" t="s">
+        <v>203</v>
+      </c>
+      <c r="C67" t="s">
+        <v>62</v>
+      </c>
+      <c r="D67" t="s">
+        <v>63</v>
+      </c>
+      <c r="E67" t="s">
+        <v>10</v>
+      </c>
+      <c r="F67" t="s">
+        <v>204</v>
+      </c>
+      <c r="G67" t="s">
+        <v>63</v>
+      </c>
+      <c r="H67" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="68" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>205</v>
+      </c>
+      <c r="B68" t="s">
+        <v>206</v>
+      </c>
+      <c r="C68" t="s">
+        <v>62</v>
+      </c>
+      <c r="D68" t="s">
+        <v>63</v>
+      </c>
+      <c r="E68" t="s">
+        <v>10</v>
+      </c>
+      <c r="F68" t="s">
+        <v>207</v>
+      </c>
+      <c r="G68" t="s">
+        <v>63</v>
+      </c>
+      <c r="H68" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="69" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>208</v>
+      </c>
+      <c r="B69" t="s">
+        <v>209</v>
+      </c>
+      <c r="C69" t="s">
+        <v>62</v>
+      </c>
+      <c r="D69" t="s">
+        <v>63</v>
+      </c>
+      <c r="E69" t="s">
+        <v>10</v>
+      </c>
+      <c r="F69" t="s">
+        <v>110</v>
+      </c>
+      <c r="G69" t="s">
+        <v>63</v>
+      </c>
+      <c r="H69" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="70" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>210</v>
+      </c>
+      <c r="B70" t="s">
+        <v>211</v>
+      </c>
+      <c r="C70" t="s">
+        <v>62</v>
+      </c>
+      <c r="D70" t="s">
+        <v>63</v>
+      </c>
+      <c r="E70" t="s">
+        <v>10</v>
+      </c>
+      <c r="F70" t="s">
+        <v>110</v>
+      </c>
+      <c r="G70" t="s">
+        <v>63</v>
+      </c>
+      <c r="H70" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="71" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>212</v>
+      </c>
+      <c r="B71" t="s">
+        <v>213</v>
+      </c>
+      <c r="C71" t="s">
+        <v>62</v>
+      </c>
+      <c r="D71" t="s">
+        <v>63</v>
+      </c>
+      <c r="E71" t="s">
+        <v>10</v>
+      </c>
+      <c r="F71" t="s">
+        <v>125</v>
+      </c>
+      <c r="G71" t="s">
+        <v>63</v>
+      </c>
+      <c r="H71" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="72" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>214</v>
+      </c>
+      <c r="B72" t="s">
+        <v>215</v>
+      </c>
+      <c r="C72" t="s">
+        <v>62</v>
+      </c>
+      <c r="D72" t="s">
+        <v>63</v>
+      </c>
+      <c r="E72" t="s">
+        <v>10</v>
+      </c>
+      <c r="F72" t="s">
+        <v>104</v>
+      </c>
+      <c r="G72" t="s">
+        <v>63</v>
+      </c>
+      <c r="H72" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="73" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>216</v>
+      </c>
+      <c r="B73" t="s">
+        <v>217</v>
+      </c>
+      <c r="C73" t="s">
+        <v>62</v>
+      </c>
+      <c r="D73" t="s">
+        <v>63</v>
+      </c>
+      <c r="E73" t="s">
+        <v>10</v>
+      </c>
+      <c r="F73" t="s">
+        <v>218</v>
+      </c>
+      <c r="G73" t="s">
+        <v>63</v>
+      </c>
+      <c r="H73" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="74" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>219</v>
+      </c>
+      <c r="B74" t="s">
+        <v>220</v>
+      </c>
+      <c r="C74" t="s">
+        <v>62</v>
+      </c>
+      <c r="D74" t="s">
+        <v>63</v>
+      </c>
+      <c r="E74" t="s">
+        <v>10</v>
+      </c>
+      <c r="F74" t="s">
+        <v>104</v>
+      </c>
+      <c r="G74" t="s">
+        <v>63</v>
+      </c>
+      <c r="H74" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="75" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>221</v>
+      </c>
+      <c r="B75" t="s">
+        <v>222</v>
+      </c>
+      <c r="C75" t="s">
+        <v>62</v>
+      </c>
+      <c r="D75" t="s">
+        <v>63</v>
+      </c>
+      <c r="E75" t="s">
+        <v>10</v>
+      </c>
+      <c r="F75" t="s">
+        <v>104</v>
+      </c>
+      <c r="G75" t="s">
+        <v>63</v>
+      </c>
+      <c r="H75" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="76" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>223</v>
+      </c>
+      <c r="B76" t="s">
+        <v>224</v>
+      </c>
+      <c r="C76" t="s">
+        <v>62</v>
+      </c>
+      <c r="D76" t="s">
+        <v>63</v>
+      </c>
+      <c r="E76" t="s">
+        <v>10</v>
+      </c>
+      <c r="F76" t="s">
+        <v>225</v>
+      </c>
+      <c r="G76" t="s">
+        <v>63</v>
+      </c>
+      <c r="H76" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="77" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>226</v>
+      </c>
+      <c r="B77" t="s">
+        <v>227</v>
+      </c>
+      <c r="C77" t="s">
+        <v>62</v>
+      </c>
+      <c r="D77" t="s">
+        <v>63</v>
+      </c>
+      <c r="E77" t="s">
+        <v>10</v>
+      </c>
+      <c r="F77" t="s">
+        <v>228</v>
+      </c>
+      <c r="G77" t="s">
+        <v>63</v>
+      </c>
+      <c r="H77" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="78" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>229</v>
+      </c>
+      <c r="B78" t="s">
+        <v>230</v>
+      </c>
+      <c r="C78" t="s">
+        <v>62</v>
+      </c>
+      <c r="D78" t="s">
+        <v>63</v>
+      </c>
+      <c r="E78" t="s">
+        <v>10</v>
+      </c>
+      <c r="F78" t="s">
+        <v>231</v>
+      </c>
+      <c r="G78" t="s">
+        <v>63</v>
+      </c>
+      <c r="H78" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="79" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>232</v>
+      </c>
+      <c r="B79" t="s">
+        <v>233</v>
+      </c>
+      <c r="C79" t="s">
+        <v>62</v>
+      </c>
+      <c r="D79" t="s">
+        <v>63</v>
+      </c>
+      <c r="E79" t="s">
+        <v>10</v>
+      </c>
+      <c r="F79" t="s">
+        <v>234</v>
+      </c>
+      <c r="G79" t="s">
+        <v>63</v>
+      </c>
+      <c r="H79" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="80" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>235</v>
+      </c>
+      <c r="B80" t="s">
+        <v>236</v>
+      </c>
+      <c r="C80" t="s">
+        <v>62</v>
+      </c>
+      <c r="D80" t="s">
+        <v>63</v>
+      </c>
+      <c r="E80" t="s">
+        <v>10</v>
+      </c>
+      <c r="F80" t="s">
+        <v>237</v>
+      </c>
+      <c r="G80" t="s">
+        <v>63</v>
+      </c>
+      <c r="H80" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="81" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>238</v>
+      </c>
+      <c r="B81" t="s">
+        <v>239</v>
+      </c>
+      <c r="C81" t="s">
+        <v>62</v>
+      </c>
+      <c r="D81" t="s">
+        <v>63</v>
+      </c>
+      <c r="E81" t="s">
+        <v>10</v>
+      </c>
+      <c r="F81" t="s">
+        <v>240</v>
+      </c>
+      <c r="G81" t="s">
+        <v>63</v>
+      </c>
+      <c r="H81" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="82" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>241</v>
+      </c>
+      <c r="B82" t="s">
+        <v>242</v>
+      </c>
+      <c r="C82" t="s">
+        <v>62</v>
+      </c>
+      <c r="D82" t="s">
+        <v>63</v>
+      </c>
+      <c r="E82" t="s">
+        <v>10</v>
+      </c>
+      <c r="F82" t="s">
+        <v>243</v>
+      </c>
+      <c r="G82" t="s">
+        <v>63</v>
+      </c>
+      <c r="H82" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="83" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>244</v>
+      </c>
+      <c r="B83" t="s">
+        <v>245</v>
+      </c>
+      <c r="C83" t="s">
+        <v>62</v>
+      </c>
+      <c r="D83" t="s">
+        <v>63</v>
+      </c>
+      <c r="E83" t="s">
+        <v>10</v>
+      </c>
+      <c r="F83" t="s">
+        <v>246</v>
+      </c>
+      <c r="G83" t="s">
+        <v>63</v>
+      </c>
+      <c r="H83" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="84" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>247</v>
+      </c>
+      <c r="B84" t="s">
+        <v>248</v>
+      </c>
+      <c r="C84" t="s">
+        <v>62</v>
+      </c>
+      <c r="D84" t="s">
+        <v>63</v>
+      </c>
+      <c r="E84" t="s">
+        <v>10</v>
+      </c>
+      <c r="F84" t="s">
+        <v>249</v>
+      </c>
+      <c r="G84" t="s">
+        <v>63</v>
+      </c>
+      <c r="H84" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="85" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>250</v>
+      </c>
+      <c r="B85" t="s">
+        <v>251</v>
+      </c>
+      <c r="C85" t="s">
+        <v>62</v>
+      </c>
+      <c r="D85" t="s">
+        <v>63</v>
+      </c>
+      <c r="E85" t="s">
+        <v>10</v>
+      </c>
+      <c r="F85" t="s">
+        <v>252</v>
+      </c>
+      <c r="G85" t="s">
+        <v>63</v>
+      </c>
+      <c r="H85" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="86" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>253</v>
+      </c>
+      <c r="B86" t="s">
+        <v>254</v>
+      </c>
+      <c r="C86" t="s">
+        <v>62</v>
+      </c>
+      <c r="D86" t="s">
+        <v>63</v>
+      </c>
+      <c r="E86" t="s">
+        <v>10</v>
+      </c>
+      <c r="F86" t="s">
+        <v>255</v>
+      </c>
+      <c r="G86" t="s">
+        <v>63</v>
+      </c>
+      <c r="H86" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="87" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>256</v>
+      </c>
+      <c r="B87" t="s">
+        <v>257</v>
+      </c>
+      <c r="C87" t="s">
+        <v>62</v>
+      </c>
+      <c r="D87" t="s">
+        <v>63</v>
+      </c>
+      <c r="E87" t="s">
+        <v>10</v>
+      </c>
+      <c r="F87" t="s">
+        <v>258</v>
+      </c>
+      <c r="G87" t="s">
+        <v>63</v>
+      </c>
+      <c r="H87" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="88" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>259</v>
+      </c>
+      <c r="B88" t="s">
+        <v>260</v>
+      </c>
+      <c r="C88" t="s">
+        <v>62</v>
+      </c>
+      <c r="D88" t="s">
+        <v>63</v>
+      </c>
+      <c r="E88" t="s">
+        <v>10</v>
+      </c>
+      <c r="F88" t="s">
+        <v>252</v>
+      </c>
+      <c r="G88" t="s">
+        <v>63</v>
+      </c>
+      <c r="H88" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="89" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>261</v>
+      </c>
+      <c r="B89" t="s">
+        <v>262</v>
+      </c>
+      <c r="C89" t="s">
+        <v>62</v>
+      </c>
+      <c r="D89" t="s">
+        <v>63</v>
+      </c>
+      <c r="E89" t="s">
+        <v>10</v>
+      </c>
+      <c r="F89" t="s">
+        <v>263</v>
+      </c>
+      <c r="G89" t="s">
+        <v>63</v>
+      </c>
+      <c r="H89" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="90" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>264</v>
+      </c>
+      <c r="B90" t="s">
+        <v>265</v>
+      </c>
+      <c r="C90" t="s">
+        <v>62</v>
+      </c>
+      <c r="D90" t="s">
+        <v>63</v>
+      </c>
+      <c r="E90" t="s">
+        <v>10</v>
+      </c>
+      <c r="F90" t="s">
+        <v>116</v>
+      </c>
+      <c r="G90" t="s">
+        <v>63</v>
+      </c>
+      <c r="H90" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="91" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>266</v>
+      </c>
+      <c r="B91" t="s">
+        <v>267</v>
+      </c>
+      <c r="C91" t="s">
+        <v>62</v>
+      </c>
+      <c r="D91" t="s">
+        <v>63</v>
+      </c>
+      <c r="E91" t="s">
+        <v>10</v>
+      </c>
+      <c r="F91" t="s">
+        <v>116</v>
+      </c>
+      <c r="G91" t="s">
+        <v>63</v>
+      </c>
+      <c r="H91" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="92" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>268</v>
+      </c>
+      <c r="B92" t="s">
+        <v>269</v>
+      </c>
+      <c r="C92" t="s">
+        <v>62</v>
+      </c>
+      <c r="D92" t="s">
+        <v>63</v>
+      </c>
+      <c r="E92" t="s">
+        <v>10</v>
+      </c>
+      <c r="F92" t="s">
+        <v>270</v>
+      </c>
+      <c r="G92" t="s">
+        <v>63</v>
+      </c>
+      <c r="H92" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="93" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>271</v>
+      </c>
+      <c r="B93" t="s">
+        <v>272</v>
+      </c>
+      <c r="C93" t="s">
+        <v>62</v>
+      </c>
+      <c r="D93" t="s">
+        <v>63</v>
+      </c>
+      <c r="E93" t="s">
+        <v>10</v>
+      </c>
+      <c r="F93" t="s">
+        <v>273</v>
+      </c>
+      <c r="G93" t="s">
+        <v>63</v>
+      </c>
+      <c r="H93" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="94" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>274</v>
+      </c>
+      <c r="B94" t="s">
+        <v>275</v>
+      </c>
+      <c r="C94" t="s">
+        <v>62</v>
+      </c>
+      <c r="D94" t="s">
+        <v>63</v>
+      </c>
+      <c r="E94" t="s">
+        <v>10</v>
+      </c>
+      <c r="F94" t="s">
+        <v>122</v>
+      </c>
+      <c r="G94" t="s">
+        <v>63</v>
+      </c>
+      <c r="H94" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="95" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>276</v>
+      </c>
+      <c r="B95" t="s">
+        <v>277</v>
+      </c>
+      <c r="C95" t="s">
+        <v>62</v>
+      </c>
+      <c r="D95" t="s">
+        <v>63</v>
+      </c>
+      <c r="E95" t="s">
+        <v>10</v>
+      </c>
+      <c r="F95" t="s">
+        <v>116</v>
+      </c>
+      <c r="G95" t="s">
+        <v>63</v>
+      </c>
+      <c r="H95" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="96" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>278</v>
+      </c>
+      <c r="B96" t="s">
+        <v>279</v>
+      </c>
+      <c r="C96" t="s">
+        <v>62</v>
+      </c>
+      <c r="D96" t="s">
+        <v>63</v>
+      </c>
+      <c r="E96" t="s">
+        <v>10</v>
+      </c>
+      <c r="F96" t="s">
+        <v>280</v>
+      </c>
+      <c r="G96" t="s">
+        <v>63</v>
+      </c>
+      <c r="H96" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="97" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>281</v>
+      </c>
+      <c r="B97" t="s">
+        <v>282</v>
+      </c>
+      <c r="C97" t="s">
+        <v>62</v>
+      </c>
+      <c r="D97" t="s">
+        <v>63</v>
+      </c>
+      <c r="E97" t="s">
+        <v>10</v>
+      </c>
+      <c r="F97" t="s">
+        <v>283</v>
+      </c>
+      <c r="G97" t="s">
+        <v>63</v>
+      </c>
+      <c r="H97" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="98" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>284</v>
+      </c>
+      <c r="B98" t="s">
+        <v>285</v>
+      </c>
+      <c r="C98" t="s">
+        <v>62</v>
+      </c>
+      <c r="D98" t="s">
+        <v>63</v>
+      </c>
+      <c r="E98" t="s">
+        <v>10</v>
+      </c>
+      <c r="F98" t="s">
+        <v>286</v>
+      </c>
+      <c r="G98" t="s">
+        <v>63</v>
+      </c>
+      <c r="H98" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="99" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>287</v>
+      </c>
+      <c r="B99" t="s">
+        <v>288</v>
+      </c>
+      <c r="C99" t="s">
+        <v>62</v>
+      </c>
+      <c r="D99" t="s">
+        <v>63</v>
+      </c>
+      <c r="E99" t="s">
+        <v>10</v>
+      </c>
+      <c r="F99" t="s">
+        <v>148</v>
+      </c>
+      <c r="G99" t="s">
+        <v>63</v>
+      </c>
+      <c r="H99" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="100" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>289</v>
+      </c>
+      <c r="B100" t="s">
+        <v>290</v>
+      </c>
+      <c r="C100" t="s">
+        <v>62</v>
+      </c>
+      <c r="D100" t="s">
+        <v>63</v>
+      </c>
+      <c r="E100" t="s">
+        <v>10</v>
+      </c>
+      <c r="F100" t="s">
+        <v>291</v>
+      </c>
+      <c r="G100" t="s">
+        <v>63</v>
+      </c>
+      <c r="H100" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="101" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>292</v>
+      </c>
+      <c r="B101" t="s">
+        <v>293</v>
+      </c>
+      <c r="C101" t="s">
+        <v>62</v>
+      </c>
+      <c r="D101" t="s">
+        <v>63</v>
+      </c>
+      <c r="E101" t="s">
+        <v>10</v>
+      </c>
+      <c r="F101" t="s">
+        <v>294</v>
+      </c>
+      <c r="G101" t="s">
+        <v>63</v>
+      </c>
+      <c r="H101" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="102" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>295</v>
+      </c>
+      <c r="B102" t="s">
+        <v>296</v>
+      </c>
+      <c r="C102" t="s">
+        <v>62</v>
+      </c>
+      <c r="D102" t="s">
+        <v>63</v>
+      </c>
+      <c r="E102" t="s">
+        <v>10</v>
+      </c>
+      <c r="F102" t="s">
+        <v>297</v>
+      </c>
+      <c r="G102" t="s">
+        <v>63</v>
+      </c>
+      <c r="H102" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="103" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>298</v>
+      </c>
+      <c r="B103" t="s">
+        <v>299</v>
+      </c>
+      <c r="C103" t="s">
+        <v>62</v>
+      </c>
+      <c r="D103" t="s">
+        <v>63</v>
+      </c>
+      <c r="E103" t="s">
+        <v>10</v>
+      </c>
+      <c r="F103" t="s">
+        <v>300</v>
+      </c>
+      <c r="G103" t="s">
+        <v>63</v>
+      </c>
+      <c r="H103" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="104" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>301</v>
+      </c>
+      <c r="B104" t="s">
+        <v>302</v>
+      </c>
+      <c r="C104" t="s">
+        <v>62</v>
+      </c>
+      <c r="D104" t="s">
+        <v>63</v>
+      </c>
+      <c r="E104" t="s">
+        <v>10</v>
+      </c>
+      <c r="F104" t="s">
+        <v>303</v>
+      </c>
+      <c r="G104" t="s">
+        <v>63</v>
+      </c>
+      <c r="H104" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="105" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>304</v>
+      </c>
+      <c r="B105" t="s">
+        <v>305</v>
+      </c>
+      <c r="C105" t="s">
+        <v>62</v>
+      </c>
+      <c r="D105" t="s">
+        <v>63</v>
+      </c>
+      <c r="E105" t="s">
+        <v>10</v>
+      </c>
+      <c r="F105" t="s">
+        <v>306</v>
+      </c>
+      <c r="G105" t="s">
+        <v>63</v>
+      </c>
+      <c r="H105" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="106" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>307</v>
+      </c>
+      <c r="B106" t="s">
+        <v>308</v>
+      </c>
+      <c r="C106" t="s">
+        <v>62</v>
+      </c>
+      <c r="D106" t="s">
+        <v>63</v>
+      </c>
+      <c r="E106" t="s">
+        <v>10</v>
+      </c>
+      <c r="F106" t="s">
+        <v>309</v>
+      </c>
+      <c r="G106" t="s">
+        <v>63</v>
+      </c>
+      <c r="H106" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="107" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>310</v>
+      </c>
+      <c r="B107" t="s">
+        <v>311</v>
+      </c>
+      <c r="C107" t="s">
+        <v>62</v>
+      </c>
+      <c r="D107" t="s">
+        <v>63</v>
+      </c>
+      <c r="E107" t="s">
+        <v>10</v>
+      </c>
+      <c r="F107" t="s">
+        <v>312</v>
+      </c>
+      <c r="G107" t="s">
+        <v>63</v>
+      </c>
+      <c r="H107" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="108" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>313</v>
+      </c>
+      <c r="B108" t="s">
+        <v>314</v>
+      </c>
+      <c r="C108" t="s">
+        <v>62</v>
+      </c>
+      <c r="D108" t="s">
+        <v>63</v>
+      </c>
+      <c r="E108" t="s">
+        <v>10</v>
+      </c>
+      <c r="F108" t="s">
+        <v>315</v>
+      </c>
+      <c r="G108" t="s">
+        <v>63</v>
+      </c>
+      <c r="H108" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="109" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>316</v>
+      </c>
+      <c r="B109" t="s">
+        <v>317</v>
+      </c>
+      <c r="C109" t="s">
+        <v>62</v>
+      </c>
+      <c r="D109" t="s">
+        <v>63</v>
+      </c>
+      <c r="E109" t="s">
+        <v>10</v>
+      </c>
+      <c r="F109" t="s">
+        <v>318</v>
+      </c>
+      <c r="G109" t="s">
+        <v>63</v>
+      </c>
+      <c r="H109" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="110" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>319</v>
+      </c>
+      <c r="B110" t="s">
+        <v>320</v>
+      </c>
+      <c r="C110" t="s">
+        <v>62</v>
+      </c>
+      <c r="D110" t="s">
+        <v>63</v>
+      </c>
+      <c r="E110" t="s">
+        <v>10</v>
+      </c>
+      <c r="F110" t="s">
+        <v>321</v>
+      </c>
+      <c r="G110" t="s">
+        <v>63</v>
+      </c>
+      <c r="H110" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="111" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>322</v>
+      </c>
+      <c r="B111" t="s">
+        <v>323</v>
+      </c>
+      <c r="C111" t="s">
+        <v>62</v>
+      </c>
+      <c r="D111" t="s">
+        <v>63</v>
+      </c>
+      <c r="E111" t="s">
+        <v>10</v>
+      </c>
+      <c r="F111" t="s">
+        <v>324</v>
+      </c>
+      <c r="G111" t="s">
+        <v>63</v>
+      </c>
+      <c r="H111" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="112" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>325</v>
+      </c>
+      <c r="B112" t="s">
+        <v>326</v>
+      </c>
+      <c r="C112" t="s">
+        <v>62</v>
+      </c>
+      <c r="D112" t="s">
+        <v>63</v>
+      </c>
+      <c r="E112" t="s">
+        <v>10</v>
+      </c>
+      <c r="F112" t="s">
+        <v>327</v>
+      </c>
+      <c r="G112" t="s">
+        <v>63</v>
+      </c>
+      <c r="H112" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="113" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>328</v>
+      </c>
+      <c r="B113" t="s">
+        <v>329</v>
+      </c>
+      <c r="C113" t="s">
+        <v>62</v>
+      </c>
+      <c r="D113" t="s">
+        <v>63</v>
+      </c>
+      <c r="E113" t="s">
+        <v>10</v>
+      </c>
+      <c r="F113" t="s">
+        <v>330</v>
+      </c>
+      <c r="G113" t="s">
+        <v>63</v>
+      </c>
+      <c r="H113" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="114" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>331</v>
+      </c>
+      <c r="B114" t="s">
+        <v>332</v>
+      </c>
+      <c r="C114" t="s">
+        <v>62</v>
+      </c>
+      <c r="D114" t="s">
+        <v>63</v>
+      </c>
+      <c r="E114" t="s">
+        <v>10</v>
+      </c>
+      <c r="F114" t="s">
+        <v>122</v>
+      </c>
+      <c r="G114" t="s">
+        <v>63</v>
+      </c>
+      <c r="H114" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="115" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>333</v>
+      </c>
+      <c r="B115" t="s">
+        <v>334</v>
+      </c>
+      <c r="C115" t="s">
+        <v>62</v>
+      </c>
+      <c r="D115" t="s">
+        <v>63</v>
+      </c>
+      <c r="E115" t="s">
+        <v>10</v>
+      </c>
+      <c r="F115" t="s">
+        <v>335</v>
+      </c>
+      <c r="G115" t="s">
+        <v>63</v>
+      </c>
+      <c r="H115" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="116" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>336</v>
+      </c>
+      <c r="B116" t="s">
+        <v>337</v>
+      </c>
+      <c r="C116" t="s">
+        <v>62</v>
+      </c>
+      <c r="D116" t="s">
+        <v>63</v>
+      </c>
+      <c r="E116" t="s">
+        <v>10</v>
+      </c>
+      <c r="F116" t="s">
+        <v>338</v>
+      </c>
+      <c r="G116" t="s">
+        <v>63</v>
+      </c>
+      <c r="H116" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="117" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>339</v>
+      </c>
+      <c r="B117" t="s">
+        <v>340</v>
+      </c>
+      <c r="C117" t="s">
+        <v>62</v>
+      </c>
+      <c r="D117" t="s">
+        <v>63</v>
+      </c>
+      <c r="E117" t="s">
+        <v>10</v>
+      </c>
+      <c r="F117" t="s">
+        <v>341</v>
+      </c>
+      <c r="G117" t="s">
+        <v>63</v>
+      </c>
+      <c r="H117" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="118" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>342</v>
+      </c>
+      <c r="B118" t="s">
+        <v>343</v>
+      </c>
+      <c r="C118" t="s">
+        <v>62</v>
+      </c>
+      <c r="D118" t="s">
+        <v>63</v>
+      </c>
+      <c r="E118" t="s">
+        <v>10</v>
+      </c>
+      <c r="F118" t="s">
+        <v>344</v>
+      </c>
+      <c r="G118" t="s">
+        <v>63</v>
+      </c>
+      <c r="H118" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="119" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>345</v>
+      </c>
+      <c r="B119" t="s">
+        <v>346</v>
+      </c>
+      <c r="C119" t="s">
+        <v>62</v>
+      </c>
+      <c r="D119" t="s">
+        <v>63</v>
+      </c>
+      <c r="E119" t="s">
+        <v>10</v>
+      </c>
+      <c r="F119" t="s">
+        <v>347</v>
+      </c>
+      <c r="G119" t="s">
+        <v>63</v>
+      </c>
+      <c r="H119" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="120" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>348</v>
+      </c>
+      <c r="B120" t="s">
+        <v>349</v>
+      </c>
+      <c r="C120" t="s">
+        <v>62</v>
+      </c>
+      <c r="D120" t="s">
+        <v>63</v>
+      </c>
+      <c r="E120" t="s">
+        <v>10</v>
+      </c>
+      <c r="F120" t="s">
+        <v>350</v>
+      </c>
+      <c r="G120" t="s">
+        <v>63</v>
+      </c>
+      <c r="H120" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="121" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>351</v>
+      </c>
+      <c r="B121" t="s">
+        <v>352</v>
+      </c>
+      <c r="C121" t="s">
+        <v>62</v>
+      </c>
+      <c r="D121" t="s">
+        <v>63</v>
+      </c>
+      <c r="E121" t="s">
+        <v>10</v>
+      </c>
+      <c r="F121" t="s">
+        <v>125</v>
+      </c>
+      <c r="G121" t="s">
+        <v>63</v>
+      </c>
+      <c r="H121" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="122" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>353</v>
+      </c>
+      <c r="B122" t="s">
+        <v>354</v>
+      </c>
+      <c r="C122" t="s">
+        <v>62</v>
+      </c>
+      <c r="D122" t="s">
+        <v>63</v>
+      </c>
+      <c r="E122" t="s">
+        <v>10</v>
+      </c>
+      <c r="F122" t="s">
+        <v>355</v>
+      </c>
+      <c r="G122" t="s">
+        <v>63</v>
+      </c>
+      <c r="H122" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="123" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>356</v>
+      </c>
+      <c r="B123" t="s">
+        <v>357</v>
+      </c>
+      <c r="C123" t="s">
+        <v>62</v>
+      </c>
+      <c r="D123" t="s">
+        <v>63</v>
+      </c>
+      <c r="E123" t="s">
+        <v>10</v>
+      </c>
+      <c r="F123" t="s">
+        <v>358</v>
+      </c>
+      <c r="G123" t="s">
+        <v>63</v>
+      </c>
+      <c r="H123" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="124" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>359</v>
+      </c>
+      <c r="B124" t="s">
+        <v>360</v>
+      </c>
+      <c r="C124" t="s">
+        <v>62</v>
+      </c>
+      <c r="D124" t="s">
+        <v>63</v>
+      </c>
+      <c r="E124" t="s">
+        <v>10</v>
+      </c>
+      <c r="F124" t="s">
+        <v>361</v>
+      </c>
+      <c r="G124" t="s">
+        <v>63</v>
+      </c>
+      <c r="H124" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="125" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>362</v>
+      </c>
+      <c r="B125" t="s">
+        <v>363</v>
+      </c>
+      <c r="C125" t="s">
+        <v>62</v>
+      </c>
+      <c r="D125" t="s">
+        <v>63</v>
+      </c>
+      <c r="E125" t="s">
+        <v>10</v>
+      </c>
+      <c r="F125" t="s">
+        <v>364</v>
+      </c>
+      <c r="G125" t="s">
+        <v>63</v>
+      </c>
+      <c r="H125" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="126" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>365</v>
+      </c>
+      <c r="B126" t="s">
+        <v>366</v>
+      </c>
+      <c r="C126" t="s">
+        <v>62</v>
+      </c>
+      <c r="D126" t="s">
+        <v>63</v>
+      </c>
+      <c r="E126" t="s">
+        <v>10</v>
+      </c>
+      <c r="F126" t="s">
+        <v>367</v>
+      </c>
+      <c r="G126" t="s">
+        <v>63</v>
+      </c>
+      <c r="H126" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="127" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>368</v>
+      </c>
+      <c r="B127" t="s">
+        <v>369</v>
+      </c>
+      <c r="C127" t="s">
+        <v>62</v>
+      </c>
+      <c r="D127" t="s">
+        <v>63</v>
+      </c>
+      <c r="E127" t="s">
+        <v>10</v>
+      </c>
+      <c r="F127" t="s">
+        <v>370</v>
+      </c>
+      <c r="G127" t="s">
+        <v>63</v>
+      </c>
+      <c r="H127" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="128" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>371</v>
+      </c>
+      <c r="B128" t="s">
+        <v>372</v>
+      </c>
+      <c r="C128" t="s">
+        <v>62</v>
+      </c>
+      <c r="D128" t="s">
+        <v>63</v>
+      </c>
+      <c r="E128" t="s">
+        <v>10</v>
+      </c>
+      <c r="F128" t="s">
+        <v>373</v>
+      </c>
+      <c r="G128" t="s">
+        <v>63</v>
+      </c>
+      <c r="H128" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="129" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>374</v>
+      </c>
+      <c r="B129" t="s">
+        <v>375</v>
+      </c>
+      <c r="C129" t="s">
+        <v>62</v>
+      </c>
+      <c r="D129" t="s">
+        <v>63</v>
+      </c>
+      <c r="E129" t="s">
+        <v>10</v>
+      </c>
+      <c r="F129" t="s">
+        <v>376</v>
+      </c>
+      <c r="G129" t="s">
+        <v>63</v>
+      </c>
+      <c r="H129" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="130" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>377</v>
+      </c>
+      <c r="B130" t="s">
+        <v>378</v>
+      </c>
+      <c r="C130" t="s">
+        <v>62</v>
+      </c>
+      <c r="D130" t="s">
+        <v>63</v>
+      </c>
+      <c r="E130" t="s">
+        <v>10</v>
+      </c>
+      <c r="F130" t="s">
+        <v>379</v>
+      </c>
+      <c r="G130" t="s">
+        <v>63</v>
+      </c>
+      <c r="H130" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="131" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>380</v>
+      </c>
+      <c r="B131" t="s">
+        <v>381</v>
+      </c>
+      <c r="C131" t="s">
+        <v>62</v>
+      </c>
+      <c r="D131" t="s">
+        <v>63</v>
+      </c>
+      <c r="E131" t="s">
+        <v>10</v>
+      </c>
+      <c r="F131" t="s">
+        <v>382</v>
+      </c>
+      <c r="G131" t="s">
+        <v>63</v>
+      </c>
+      <c r="H131" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="132" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>383</v>
+      </c>
+      <c r="B132" t="s">
+        <v>384</v>
+      </c>
+      <c r="C132" t="s">
+        <v>62</v>
+      </c>
+      <c r="D132" t="s">
+        <v>63</v>
+      </c>
+      <c r="E132" t="s">
+        <v>10</v>
+      </c>
+      <c r="F132" t="s">
+        <v>385</v>
+      </c>
+      <c r="G132" t="s">
+        <v>63</v>
+      </c>
+      <c r="H132" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="133" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>386</v>
+      </c>
+      <c r="B133" t="s">
+        <v>387</v>
+      </c>
+      <c r="C133" t="s">
+        <v>62</v>
+      </c>
+      <c r="D133" t="s">
+        <v>63</v>
+      </c>
+      <c r="E133" t="s">
+        <v>10</v>
+      </c>
+      <c r="F133" t="s">
+        <v>388</v>
+      </c>
+      <c r="G133" t="s">
+        <v>63</v>
+      </c>
+      <c r="H133" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="134" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>389</v>
+      </c>
+      <c r="B134" t="s">
+        <v>390</v>
+      </c>
+      <c r="C134" t="s">
+        <v>62</v>
+      </c>
+      <c r="D134" t="s">
+        <v>63</v>
+      </c>
+      <c r="E134" t="s">
+        <v>10</v>
+      </c>
+      <c r="F134" t="s">
+        <v>391</v>
+      </c>
+      <c r="G134" t="s">
+        <v>63</v>
+      </c>
+      <c r="H134" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="135" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>392</v>
+      </c>
+      <c r="B135" t="s">
+        <v>393</v>
+      </c>
+      <c r="C135" t="s">
+        <v>62</v>
+      </c>
+      <c r="D135" t="s">
+        <v>63</v>
+      </c>
+      <c r="E135" t="s">
+        <v>10</v>
+      </c>
+      <c r="F135" t="s">
+        <v>394</v>
+      </c>
+      <c r="G135" t="s">
+        <v>63</v>
+      </c>
+      <c r="H135" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="136" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>395</v>
+      </c>
+      <c r="B136" t="s">
+        <v>396</v>
+      </c>
+      <c r="C136" t="s">
+        <v>62</v>
+      </c>
+      <c r="D136" t="s">
+        <v>63</v>
+      </c>
+      <c r="E136" t="s">
+        <v>10</v>
+      </c>
+      <c r="F136" t="s">
+        <v>148</v>
+      </c>
+      <c r="G136" t="s">
+        <v>63</v>
+      </c>
+      <c r="H136" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="137" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>397</v>
+      </c>
+      <c r="B137" t="s">
+        <v>398</v>
+      </c>
+      <c r="C137" t="s">
+        <v>62</v>
+      </c>
+      <c r="D137" t="s">
+        <v>63</v>
+      </c>
+      <c r="E137" t="s">
+        <v>10</v>
+      </c>
+      <c r="F137" t="s">
+        <v>399</v>
+      </c>
+      <c r="G137" t="s">
+        <v>63</v>
+      </c>
+      <c r="H137" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="138" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>400</v>
+      </c>
+      <c r="B138" t="s">
+        <v>401</v>
+      </c>
+      <c r="C138" t="s">
+        <v>62</v>
+      </c>
+      <c r="D138" t="s">
+        <v>63</v>
+      </c>
+      <c r="E138" t="s">
+        <v>10</v>
+      </c>
+      <c r="F138" t="s">
+        <v>132</v>
+      </c>
+      <c r="G138" t="s">
+        <v>63</v>
+      </c>
+      <c r="H138" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="139" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>402</v>
+      </c>
+      <c r="B139" t="s">
+        <v>403</v>
+      </c>
+      <c r="C139" t="s">
+        <v>62</v>
+      </c>
+      <c r="D139" t="s">
+        <v>63</v>
+      </c>
+      <c r="E139" t="s">
+        <v>10</v>
+      </c>
+      <c r="F139" t="s">
+        <v>404</v>
+      </c>
+      <c r="G139" t="s">
+        <v>63</v>
+      </c>
+      <c r="H139" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="140" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>405</v>
+      </c>
+      <c r="B140" t="s">
+        <v>406</v>
+      </c>
+      <c r="C140" t="s">
+        <v>62</v>
+      </c>
+      <c r="D140" t="s">
+        <v>63</v>
+      </c>
+      <c r="E140" t="s">
+        <v>10</v>
+      </c>
+      <c r="F140" t="s">
+        <v>407</v>
+      </c>
+      <c r="G140" t="s">
+        <v>63</v>
+      </c>
+      <c r="H140" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="141" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>408</v>
+      </c>
+      <c r="B141" t="s">
+        <v>409</v>
+      </c>
+      <c r="C141" t="s">
+        <v>62</v>
+      </c>
+      <c r="D141" t="s">
+        <v>63</v>
+      </c>
+      <c r="E141" t="s">
+        <v>10</v>
+      </c>
+      <c r="F141" t="s">
+        <v>410</v>
+      </c>
+      <c r="G141" t="s">
+        <v>63</v>
+      </c>
+      <c r="H141" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="142" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>411</v>
+      </c>
+      <c r="B142" t="s">
+        <v>412</v>
+      </c>
+      <c r="C142" t="s">
+        <v>62</v>
+      </c>
+      <c r="D142" t="s">
+        <v>63</v>
+      </c>
+      <c r="E142" t="s">
+        <v>10</v>
+      </c>
+      <c r="F142" t="s">
+        <v>413</v>
+      </c>
+      <c r="G142" t="s">
+        <v>63</v>
+      </c>
+      <c r="H142" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="143" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>414</v>
+      </c>
+      <c r="B143" t="s">
+        <v>415</v>
+      </c>
+      <c r="C143" t="s">
+        <v>62</v>
+      </c>
+      <c r="D143" t="s">
+        <v>63</v>
+      </c>
+      <c r="E143" t="s">
+        <v>10</v>
+      </c>
+      <c r="F143" t="s">
+        <v>148</v>
+      </c>
+      <c r="G143" t="s">
+        <v>63</v>
+      </c>
+      <c r="H143" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="144" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>416</v>
+      </c>
+      <c r="B144" t="s">
+        <v>417</v>
+      </c>
+      <c r="C144" t="s">
+        <v>62</v>
+      </c>
+      <c r="D144" t="s">
+        <v>63</v>
+      </c>
+      <c r="E144" t="s">
+        <v>10</v>
+      </c>
+      <c r="F144" t="s">
+        <v>418</v>
+      </c>
+      <c r="G144" t="s">
+        <v>63</v>
+      </c>
+      <c r="H144" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="145" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>419</v>
+      </c>
+      <c r="B145" t="s">
+        <v>420</v>
+      </c>
+      <c r="C145" t="s">
+        <v>62</v>
+      </c>
+      <c r="D145" t="s">
+        <v>63</v>
+      </c>
+      <c r="E145" t="s">
+        <v>10</v>
+      </c>
+      <c r="F145" t="s">
+        <v>421</v>
+      </c>
+      <c r="G145" t="s">
+        <v>63</v>
+      </c>
+      <c r="H145" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="146" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>422</v>
+      </c>
+      <c r="B146" t="s">
+        <v>423</v>
+      </c>
+      <c r="C146" t="s">
+        <v>62</v>
+      </c>
+      <c r="D146" t="s">
+        <v>63</v>
+      </c>
+      <c r="E146" t="s">
+        <v>10</v>
+      </c>
+      <c r="F146" t="s">
+        <v>424</v>
+      </c>
+      <c r="G146" t="s">
+        <v>63</v>
+      </c>
+      <c r="H146" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="147" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>425</v>
+      </c>
+      <c r="B147" t="s">
+        <v>426</v>
+      </c>
+      <c r="C147" t="s">
+        <v>62</v>
+      </c>
+      <c r="D147" t="s">
+        <v>63</v>
+      </c>
+      <c r="E147" t="s">
+        <v>10</v>
+      </c>
+      <c r="F147" t="s">
+        <v>427</v>
+      </c>
+      <c r="G147" t="s">
+        <v>63</v>
+      </c>
+      <c r="H147" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="148" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>428</v>
+      </c>
+      <c r="B148" t="s">
+        <v>429</v>
+      </c>
+      <c r="C148" t="s">
+        <v>62</v>
+      </c>
+      <c r="D148" t="s">
+        <v>63</v>
+      </c>
+      <c r="E148" t="s">
+        <v>10</v>
+      </c>
+      <c r="F148" t="s">
+        <v>430</v>
+      </c>
+      <c r="G148" t="s">
+        <v>63</v>
+      </c>
+      <c r="H148" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="149" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>431</v>
+      </c>
+      <c r="B149" t="s">
+        <v>432</v>
+      </c>
+      <c r="C149" t="s">
+        <v>62</v>
+      </c>
+      <c r="D149" t="s">
+        <v>63</v>
+      </c>
+      <c r="E149" t="s">
+        <v>10</v>
+      </c>
+      <c r="F149" t="s">
+        <v>433</v>
+      </c>
+      <c r="G149" t="s">
+        <v>63</v>
+      </c>
+      <c r="H149" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="150" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>434</v>
+      </c>
+      <c r="B150" t="s">
+        <v>435</v>
+      </c>
+      <c r="C150" t="s">
+        <v>62</v>
+      </c>
+      <c r="D150" t="s">
+        <v>63</v>
+      </c>
+      <c r="E150" t="s">
+        <v>10</v>
+      </c>
+      <c r="F150" t="s">
+        <v>436</v>
+      </c>
+      <c r="G150" t="s">
+        <v>63</v>
+      </c>
+      <c r="H150" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="151" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>437</v>
+      </c>
+      <c r="B151" t="s">
+        <v>438</v>
+      </c>
+      <c r="C151" t="s">
+        <v>62</v>
+      </c>
+      <c r="D151" t="s">
+        <v>63</v>
+      </c>
+      <c r="E151" t="s">
+        <v>10</v>
+      </c>
+      <c r="F151" t="s">
+        <v>439</v>
+      </c>
+      <c r="G151" t="s">
+        <v>63</v>
+      </c>
+      <c r="H151" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="152" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>440</v>
+      </c>
+      <c r="B152" t="s">
+        <v>441</v>
+      </c>
+      <c r="C152" t="s">
+        <v>62</v>
+      </c>
+      <c r="D152" t="s">
+        <v>63</v>
+      </c>
+      <c r="E152" t="s">
+        <v>10</v>
+      </c>
+      <c r="F152" t="s">
+        <v>442</v>
+      </c>
+      <c r="G152" t="s">
+        <v>63</v>
+      </c>
+      <c r="H152" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="153" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>443</v>
+      </c>
+      <c r="B153" t="s">
+        <v>444</v>
+      </c>
+      <c r="C153" t="s">
+        <v>62</v>
+      </c>
+      <c r="D153" t="s">
+        <v>63</v>
+      </c>
+      <c r="E153" t="s">
+        <v>10</v>
+      </c>
+      <c r="F153" t="s">
+        <v>445</v>
+      </c>
+      <c r="G153" t="s">
+        <v>63</v>
+      </c>
+      <c r="H153" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="154" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>446</v>
+      </c>
+      <c r="B154" t="s">
+        <v>447</v>
+      </c>
+      <c r="C154" t="s">
+        <v>62</v>
+      </c>
+      <c r="D154" t="s">
+        <v>63</v>
+      </c>
+      <c r="E154" t="s">
+        <v>10</v>
+      </c>
+      <c r="F154" t="s">
+        <v>448</v>
+      </c>
+      <c r="G154" t="s">
+        <v>63</v>
+      </c>
+      <c r="H154" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="155" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>449</v>
+      </c>
+      <c r="B155" t="s">
+        <v>450</v>
+      </c>
+      <c r="C155" t="s">
+        <v>62</v>
+      </c>
+      <c r="D155" t="s">
+        <v>63</v>
+      </c>
+      <c r="E155" t="s">
+        <v>10</v>
+      </c>
+      <c r="F155" t="s">
+        <v>451</v>
+      </c>
+      <c r="G155" t="s">
+        <v>63</v>
+      </c>
+      <c r="H155" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="156" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>452</v>
+      </c>
+      <c r="B156" t="s">
+        <v>453</v>
+      </c>
+      <c r="C156" t="s">
+        <v>62</v>
+      </c>
+      <c r="D156" t="s">
+        <v>63</v>
+      </c>
+      <c r="E156" t="s">
+        <v>10</v>
+      </c>
+      <c r="F156" t="s">
+        <v>148</v>
+      </c>
+      <c r="G156" t="s">
+        <v>63</v>
+      </c>
+      <c r="H156" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="157" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>454</v>
+      </c>
+      <c r="B157" t="s">
+        <v>455</v>
+      </c>
+      <c r="C157" t="s">
+        <v>62</v>
+      </c>
+      <c r="D157" t="s">
+        <v>63</v>
+      </c>
+      <c r="E157" t="s">
+        <v>10</v>
+      </c>
+      <c r="F157" t="s">
+        <v>456</v>
+      </c>
+      <c r="G157" t="s">
+        <v>63</v>
+      </c>
+      <c r="H157" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="158" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>457</v>
+      </c>
+      <c r="B158" t="s">
+        <v>458</v>
+      </c>
+      <c r="C158" t="s">
+        <v>62</v>
+      </c>
+      <c r="D158" t="s">
+        <v>63</v>
+      </c>
+      <c r="E158" t="s">
+        <v>10</v>
+      </c>
+      <c r="F158" t="s">
+        <v>459</v>
+      </c>
+      <c r="G158" t="s">
+        <v>63</v>
+      </c>
+      <c r="H158" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="159" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>460</v>
+      </c>
+      <c r="B159" t="s">
+        <v>461</v>
+      </c>
+      <c r="C159" t="s">
+        <v>62</v>
+      </c>
+      <c r="D159" t="s">
+        <v>63</v>
+      </c>
+      <c r="E159" t="s">
+        <v>10</v>
+      </c>
+      <c r="F159" t="s">
+        <v>462</v>
+      </c>
+      <c r="G159" t="s">
+        <v>63</v>
+      </c>
+      <c r="H159" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="160" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
+        <v>463</v>
+      </c>
+      <c r="B160" t="s">
+        <v>464</v>
+      </c>
+      <c r="C160" t="s">
+        <v>62</v>
+      </c>
+      <c r="D160" t="s">
+        <v>63</v>
+      </c>
+      <c r="E160" t="s">
+        <v>10</v>
+      </c>
+      <c r="F160" t="s">
+        <v>465</v>
+      </c>
+      <c r="G160" t="s">
+        <v>63</v>
+      </c>
+      <c r="H160" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="161" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
+        <v>466</v>
+      </c>
+      <c r="B161" t="s">
+        <v>467</v>
+      </c>
+      <c r="C161" t="s">
+        <v>62</v>
+      </c>
+      <c r="D161" t="s">
+        <v>63</v>
+      </c>
+      <c r="E161" t="s">
+        <v>10</v>
+      </c>
+      <c r="F161" t="s">
+        <v>122</v>
+      </c>
+      <c r="G161" t="s">
+        <v>63</v>
+      </c>
+      <c r="H161" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="162" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A162" t="s">
+        <v>468</v>
+      </c>
+      <c r="B162" t="s">
+        <v>469</v>
+      </c>
+      <c r="C162" t="s">
+        <v>62</v>
+      </c>
+      <c r="D162" t="s">
+        <v>63</v>
+      </c>
+      <c r="E162" t="s">
+        <v>10</v>
+      </c>
+      <c r="F162" t="s">
+        <v>470</v>
+      </c>
+      <c r="G162" t="s">
+        <v>63</v>
+      </c>
+      <c r="H162" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="163" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A163" t="s">
+        <v>471</v>
+      </c>
+      <c r="B163" t="s">
+        <v>472</v>
+      </c>
+      <c r="C163" t="s">
+        <v>62</v>
+      </c>
+      <c r="D163" t="s">
+        <v>63</v>
+      </c>
+      <c r="E163" t="s">
+        <v>10</v>
+      </c>
+      <c r="F163" t="s">
+        <v>473</v>
+      </c>
+      <c r="G163" t="s">
+        <v>63</v>
+      </c>
+      <c r="H163" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="164" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A164" t="s">
+        <v>474</v>
+      </c>
+      <c r="B164" t="s">
+        <v>475</v>
+      </c>
+      <c r="C164" t="s">
+        <v>62</v>
+      </c>
+      <c r="D164" t="s">
+        <v>63</v>
+      </c>
+      <c r="E164" t="s">
+        <v>10</v>
+      </c>
+      <c r="F164" t="s">
+        <v>476</v>
+      </c>
+      <c r="G164" t="s">
+        <v>63</v>
+      </c>
+      <c r="H164" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="165" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A165" t="s">
+        <v>477</v>
+      </c>
+      <c r="B165" t="s">
+        <v>478</v>
+      </c>
+      <c r="C165" t="s">
+        <v>62</v>
+      </c>
+      <c r="D165" t="s">
+        <v>63</v>
+      </c>
+      <c r="E165" t="s">
+        <v>10</v>
+      </c>
+      <c r="F165" t="s">
+        <v>479</v>
+      </c>
+      <c r="G165" t="s">
+        <v>63</v>
+      </c>
+      <c r="H165" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="166" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A166" t="s">
+        <v>480</v>
+      </c>
+      <c r="B166" t="s">
+        <v>481</v>
+      </c>
+      <c r="C166" t="s">
+        <v>62</v>
+      </c>
+      <c r="D166" t="s">
+        <v>63</v>
+      </c>
+      <c r="E166" t="s">
+        <v>10</v>
+      </c>
+      <c r="F166" t="s">
+        <v>482</v>
+      </c>
+      <c r="G166" t="s">
+        <v>63</v>
+      </c>
+      <c r="H166" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="167" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A167" t="s">
+        <v>483</v>
+      </c>
+      <c r="B167" t="s">
+        <v>484</v>
+      </c>
+      <c r="C167" t="s">
+        <v>62</v>
+      </c>
+      <c r="D167" t="s">
+        <v>63</v>
+      </c>
+      <c r="E167" t="s">
+        <v>10</v>
+      </c>
+      <c r="F167" t="s">
+        <v>485</v>
+      </c>
+      <c r="G167" t="s">
+        <v>63</v>
+      </c>
+      <c r="H167" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="168" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A168" t="s">
+        <v>486</v>
+      </c>
+      <c r="B168" t="s">
+        <v>487</v>
+      </c>
+      <c r="C168" t="s">
+        <v>62</v>
+      </c>
+      <c r="D168" t="s">
+        <v>63</v>
+      </c>
+      <c r="E168" t="s">
+        <v>10</v>
+      </c>
+      <c r="F168" t="s">
+        <v>488</v>
+      </c>
+      <c r="G168" t="s">
+        <v>63</v>
+      </c>
+      <c r="H168" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="169" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A169" t="s">
+        <v>489</v>
+      </c>
+      <c r="B169" t="s">
+        <v>490</v>
+      </c>
+      <c r="C169" t="s">
+        <v>62</v>
+      </c>
+      <c r="D169" t="s">
+        <v>63</v>
+      </c>
+      <c r="E169" t="s">
+        <v>10</v>
+      </c>
+      <c r="F169" t="s">
+        <v>491</v>
+      </c>
+      <c r="G169" t="s">
+        <v>63</v>
+      </c>
+      <c r="H169" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="170" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A170" t="s">
+        <v>492</v>
+      </c>
+      <c r="B170" t="s">
+        <v>493</v>
+      </c>
+      <c r="C170" t="s">
+        <v>62</v>
+      </c>
+      <c r="D170" t="s">
+        <v>63</v>
+      </c>
+      <c r="E170" t="s">
+        <v>10</v>
+      </c>
+      <c r="F170" t="s">
+        <v>494</v>
+      </c>
+      <c r="G170" t="s">
+        <v>63</v>
+      </c>
+      <c r="H170" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="171" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A171" t="s">
+        <v>495</v>
+      </c>
+      <c r="B171" t="s">
+        <v>496</v>
+      </c>
+      <c r="C171" t="s">
+        <v>62</v>
+      </c>
+      <c r="D171" t="s">
+        <v>63</v>
+      </c>
+      <c r="E171" t="s">
+        <v>10</v>
+      </c>
+      <c r="F171" t="s">
+        <v>497</v>
+      </c>
+      <c r="G171" t="s">
+        <v>63</v>
+      </c>
+      <c r="H171" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="172" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A172" t="s">
+        <v>498</v>
+      </c>
+      <c r="B172" t="s">
+        <v>499</v>
+      </c>
+      <c r="C172" t="s">
+        <v>62</v>
+      </c>
+      <c r="D172" t="s">
+        <v>63</v>
+      </c>
+      <c r="E172" t="s">
+        <v>10</v>
+      </c>
+      <c r="F172" t="s">
+        <v>500</v>
+      </c>
+      <c r="G172" t="s">
+        <v>63</v>
+      </c>
+      <c r="H172" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="173" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A173" t="s">
+        <v>501</v>
+      </c>
+      <c r="B173" t="s">
+        <v>502</v>
+      </c>
+      <c r="C173" t="s">
+        <v>62</v>
+      </c>
+      <c r="D173" t="s">
+        <v>63</v>
+      </c>
+      <c r="E173" t="s">
+        <v>10</v>
+      </c>
+      <c r="F173" t="s">
+        <v>482</v>
+      </c>
+      <c r="G173" t="s">
+        <v>63</v>
+      </c>
+      <c r="H173" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="174" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A174" t="s">
+        <v>503</v>
+      </c>
+      <c r="B174" t="s">
+        <v>504</v>
+      </c>
+      <c r="C174" t="s">
+        <v>62</v>
+      </c>
+      <c r="D174" t="s">
+        <v>63</v>
+      </c>
+      <c r="E174" t="s">
+        <v>10</v>
+      </c>
+      <c r="F174" t="s">
+        <v>505</v>
+      </c>
+      <c r="G174" t="s">
+        <v>63</v>
+      </c>
+      <c r="H174" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="175" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A175" t="s">
+        <v>506</v>
+      </c>
+      <c r="B175" t="s">
+        <v>507</v>
+      </c>
+      <c r="C175" t="s">
+        <v>62</v>
+      </c>
+      <c r="D175" t="s">
+        <v>63</v>
+      </c>
+      <c r="E175" t="s">
+        <v>10</v>
+      </c>
+      <c r="F175" t="s">
+        <v>508</v>
+      </c>
+      <c r="G175" t="s">
+        <v>63</v>
+      </c>
+      <c r="H175" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="176" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A176" t="s">
+        <v>509</v>
+      </c>
+      <c r="B176" t="s">
+        <v>510</v>
+      </c>
+      <c r="C176" t="s">
+        <v>62</v>
+      </c>
+      <c r="D176" t="s">
+        <v>63</v>
+      </c>
+      <c r="E176" t="s">
+        <v>10</v>
+      </c>
+      <c r="F176" t="s">
+        <v>511</v>
+      </c>
+      <c r="G176" t="s">
+        <v>63</v>
+      </c>
+      <c r="H176" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="177" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A177" t="s">
+        <v>512</v>
+      </c>
+      <c r="B177" t="s">
+        <v>513</v>
+      </c>
+      <c r="C177" t="s">
+        <v>62</v>
+      </c>
+      <c r="D177" t="s">
+        <v>63</v>
+      </c>
+      <c r="E177" t="s">
+        <v>10</v>
+      </c>
+      <c r="F177" t="s">
+        <v>514</v>
+      </c>
+      <c r="G177" t="s">
+        <v>63</v>
+      </c>
+      <c r="H177" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="178" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A178" t="s">
+        <v>515</v>
+      </c>
+      <c r="B178" t="s">
+        <v>516</v>
+      </c>
+      <c r="C178" t="s">
+        <v>62</v>
+      </c>
+      <c r="D178" t="s">
+        <v>63</v>
+      </c>
+      <c r="E178" t="s">
+        <v>10</v>
+      </c>
+      <c r="F178" t="s">
+        <v>517</v>
+      </c>
+      <c r="G178" t="s">
+        <v>63</v>
+      </c>
+      <c r="H178" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="179" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A179" t="s">
+        <v>518</v>
+      </c>
+      <c r="B179" t="s">
+        <v>519</v>
+      </c>
+      <c r="C179" t="s">
+        <v>62</v>
+      </c>
+      <c r="D179" t="s">
+        <v>63</v>
+      </c>
+      <c r="E179" t="s">
+        <v>10</v>
+      </c>
+      <c r="F179" t="s">
+        <v>122</v>
+      </c>
+      <c r="G179" t="s">
+        <v>63</v>
+      </c>
+      <c r="H179" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="180" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A180" t="s">
+        <v>520</v>
+      </c>
+      <c r="B180" t="s">
+        <v>521</v>
+      </c>
+      <c r="C180" t="s">
+        <v>62</v>
+      </c>
+      <c r="D180" t="s">
+        <v>63</v>
+      </c>
+      <c r="E180" t="s">
+        <v>10</v>
+      </c>
+      <c r="F180" t="s">
+        <v>522</v>
+      </c>
+      <c r="G180" t="s">
+        <v>63</v>
+      </c>
+      <c r="H180" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="181" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A181" t="s">
+        <v>523</v>
+      </c>
+      <c r="B181" t="s">
+        <v>524</v>
+      </c>
+      <c r="C181" t="s">
+        <v>62</v>
+      </c>
+      <c r="D181" t="s">
+        <v>63</v>
+      </c>
+      <c r="E181" t="s">
+        <v>10</v>
+      </c>
+      <c r="F181" t="s">
+        <v>116</v>
+      </c>
+      <c r="G181" t="s">
+        <v>63</v>
+      </c>
+      <c r="H181" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="182" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A182" t="s">
+        <v>525</v>
+      </c>
+      <c r="B182" t="s">
+        <v>526</v>
+      </c>
+      <c r="C182" t="s">
+        <v>62</v>
+      </c>
+      <c r="D182" t="s">
+        <v>63</v>
+      </c>
+      <c r="E182" t="s">
+        <v>10</v>
+      </c>
+      <c r="F182" t="s">
+        <v>527</v>
+      </c>
+      <c r="G182" t="s">
+        <v>63</v>
+      </c>
+      <c r="H182" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="183" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A183" t="s">
+        <v>528</v>
+      </c>
+      <c r="B183" t="s">
+        <v>529</v>
+      </c>
+      <c r="C183" t="s">
+        <v>62</v>
+      </c>
+      <c r="D183" t="s">
+        <v>63</v>
+      </c>
+      <c r="E183" t="s">
+        <v>10</v>
+      </c>
+      <c r="F183" t="s">
+        <v>530</v>
+      </c>
+      <c r="G183" t="s">
+        <v>63</v>
+      </c>
+      <c r="H183" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="184" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A184" t="s">
+        <v>531</v>
+      </c>
+      <c r="B184" t="s">
+        <v>532</v>
+      </c>
+      <c r="C184" t="s">
+        <v>62</v>
+      </c>
+      <c r="D184" t="s">
+        <v>63</v>
+      </c>
+      <c r="E184" t="s">
+        <v>10</v>
+      </c>
+      <c r="F184" t="s">
+        <v>533</v>
+      </c>
+      <c r="G184" t="s">
+        <v>63</v>
+      </c>
+      <c r="H184" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="185" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A185" t="s">
+        <v>534</v>
+      </c>
+      <c r="B185" t="s">
+        <v>535</v>
+      </c>
+      <c r="C185" t="s">
+        <v>62</v>
+      </c>
+      <c r="D185" t="s">
+        <v>63</v>
+      </c>
+      <c r="E185" t="s">
+        <v>10</v>
+      </c>
+      <c r="F185" t="s">
+        <v>116</v>
+      </c>
+      <c r="G185" t="s">
+        <v>63</v>
+      </c>
+      <c r="H185" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="186" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A186" t="s">
+        <v>536</v>
+      </c>
+      <c r="B186" t="s">
+        <v>537</v>
+      </c>
+      <c r="C186" t="s">
+        <v>62</v>
+      </c>
+      <c r="D186" t="s">
+        <v>63</v>
+      </c>
+      <c r="E186" t="s">
+        <v>10</v>
+      </c>
+      <c r="F186" t="s">
+        <v>538</v>
+      </c>
+      <c r="G186" t="s">
+        <v>63</v>
+      </c>
+      <c r="H186" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="187" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A187" t="s">
+        <v>539</v>
+      </c>
+      <c r="B187" t="s">
+        <v>540</v>
+      </c>
+      <c r="C187" t="s">
+        <v>62</v>
+      </c>
+      <c r="D187" t="s">
+        <v>63</v>
+      </c>
+      <c r="E187" t="s">
+        <v>10</v>
+      </c>
+      <c r="F187" t="s">
+        <v>541</v>
+      </c>
+      <c r="G187" t="s">
+        <v>63</v>
+      </c>
+      <c r="H187" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="188" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A188" t="s">
+        <v>542</v>
+      </c>
+      <c r="B188" t="s">
+        <v>543</v>
+      </c>
+      <c r="C188" t="s">
+        <v>62</v>
+      </c>
+      <c r="D188" t="s">
+        <v>63</v>
+      </c>
+      <c r="E188" t="s">
+        <v>10</v>
+      </c>
+      <c r="F188" t="s">
+        <v>544</v>
+      </c>
+      <c r="G188" t="s">
+        <v>63</v>
+      </c>
+      <c r="H188" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="189" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A189" t="s">
+        <v>545</v>
+      </c>
+      <c r="B189" t="s">
+        <v>546</v>
+      </c>
+      <c r="C189" t="s">
+        <v>62</v>
+      </c>
+      <c r="D189" t="s">
+        <v>63</v>
+      </c>
+      <c r="E189" t="s">
+        <v>10</v>
+      </c>
+      <c r="F189" t="s">
+        <v>547</v>
+      </c>
+      <c r="G189" t="s">
+        <v>63</v>
+      </c>
+      <c r="H189" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="190" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A190" t="s">
+        <v>548</v>
+      </c>
+      <c r="B190" t="s">
+        <v>549</v>
+      </c>
+      <c r="C190" t="s">
+        <v>62</v>
+      </c>
+      <c r="D190" t="s">
+        <v>63</v>
+      </c>
+      <c r="E190" t="s">
+        <v>10</v>
+      </c>
+      <c r="F190" t="s">
+        <v>550</v>
+      </c>
+      <c r="G190" t="s">
+        <v>63</v>
+      </c>
+      <c r="H190" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="191" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A191" t="s">
+        <v>551</v>
+      </c>
+      <c r="B191" t="s">
+        <v>552</v>
+      </c>
+      <c r="C191" t="s">
+        <v>62</v>
+      </c>
+      <c r="D191" t="s">
+        <v>63</v>
+      </c>
+      <c r="E191" t="s">
+        <v>10</v>
+      </c>
+      <c r="F191" t="s">
+        <v>553</v>
+      </c>
+      <c r="G191" t="s">
+        <v>63</v>
+      </c>
+      <c r="H191" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="192" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A192" t="s">
+        <v>554</v>
+      </c>
+      <c r="B192" t="s">
+        <v>555</v>
+      </c>
+      <c r="C192" t="s">
+        <v>62</v>
+      </c>
+      <c r="D192" t="s">
+        <v>63</v>
+      </c>
+      <c r="E192" t="s">
+        <v>10</v>
+      </c>
+      <c r="F192" t="s">
+        <v>556</v>
+      </c>
+      <c r="G192" t="s">
+        <v>63</v>
+      </c>
+      <c r="H192" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="193" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A193" t="s">
+        <v>557</v>
+      </c>
+      <c r="B193" t="s">
+        <v>558</v>
+      </c>
+      <c r="C193" t="s">
+        <v>62</v>
+      </c>
+      <c r="D193" t="s">
+        <v>63</v>
+      </c>
+      <c r="E193" t="s">
+        <v>10</v>
+      </c>
+      <c r="F193" t="s">
+        <v>559</v>
+      </c>
+      <c r="G193" t="s">
+        <v>63</v>
+      </c>
+      <c r="H193" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="194" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A194" t="s">
+        <v>560</v>
+      </c>
+      <c r="B194" t="s">
+        <v>561</v>
+      </c>
+      <c r="C194" t="s">
+        <v>62</v>
+      </c>
+      <c r="D194" t="s">
+        <v>63</v>
+      </c>
+      <c r="E194" t="s">
+        <v>10</v>
+      </c>
+      <c r="F194" t="s">
+        <v>562</v>
+      </c>
+      <c r="G194" t="s">
+        <v>63</v>
+      </c>
+      <c r="H194" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="195" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A195" t="s">
+        <v>563</v>
+      </c>
+      <c r="B195" t="s">
+        <v>564</v>
+      </c>
+      <c r="C195" t="s">
+        <v>62</v>
+      </c>
+      <c r="D195" t="s">
+        <v>63</v>
+      </c>
+      <c r="E195" t="s">
+        <v>10</v>
+      </c>
+      <c r="F195" t="s">
+        <v>565</v>
+      </c>
+      <c r="G195" t="s">
+        <v>63</v>
+      </c>
+      <c r="H195" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="196" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A196" t="s">
+        <v>566</v>
+      </c>
+      <c r="B196" t="s">
+        <v>567</v>
+      </c>
+      <c r="C196" t="s">
+        <v>62</v>
+      </c>
+      <c r="D196" t="s">
+        <v>63</v>
+      </c>
+      <c r="E196" t="s">
+        <v>10</v>
+      </c>
+      <c r="F196" t="s">
+        <v>488</v>
+      </c>
+      <c r="G196" t="s">
+        <v>63</v>
+      </c>
+      <c r="H196" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="197" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A197" t="s">
+        <v>568</v>
+      </c>
+      <c r="B197" t="s">
+        <v>569</v>
+      </c>
+      <c r="C197" t="s">
+        <v>62</v>
+      </c>
+      <c r="D197" t="s">
+        <v>63</v>
+      </c>
+      <c r="E197" t="s">
+        <v>10</v>
+      </c>
+      <c r="F197" t="s">
+        <v>570</v>
+      </c>
+      <c r="G197" t="s">
+        <v>63</v>
+      </c>
+      <c r="H197" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="198" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A198" t="s">
+        <v>571</v>
+      </c>
+      <c r="B198" t="s">
+        <v>572</v>
+      </c>
+      <c r="C198" t="s">
+        <v>62</v>
+      </c>
+      <c r="D198" t="s">
+        <v>63</v>
+      </c>
+      <c r="E198" t="s">
+        <v>10</v>
+      </c>
+      <c r="F198" t="s">
+        <v>573</v>
+      </c>
+      <c r="G198" t="s">
+        <v>63</v>
+      </c>
+      <c r="H198" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="199" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A199" t="s">
+        <v>574</v>
+      </c>
+      <c r="B199" t="s">
+        <v>575</v>
+      </c>
+      <c r="C199" t="s">
+        <v>62</v>
+      </c>
+      <c r="D199" t="s">
+        <v>63</v>
+      </c>
+      <c r="E199" t="s">
+        <v>10</v>
+      </c>
+      <c r="F199" t="s">
+        <v>576</v>
+      </c>
+      <c r="G199" t="s">
+        <v>63</v>
+      </c>
+      <c r="H199" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="200" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A200" t="s">
+        <v>577</v>
+      </c>
+      <c r="B200" t="s">
+        <v>578</v>
+      </c>
+      <c r="C200" t="s">
+        <v>62</v>
+      </c>
+      <c r="D200" t="s">
+        <v>63</v>
+      </c>
+      <c r="E200" t="s">
+        <v>10</v>
+      </c>
+      <c r="F200" t="s">
+        <v>579</v>
+      </c>
+      <c r="G200" t="s">
+        <v>63</v>
+      </c>
+      <c r="H200" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="201" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A201" t="s">
+        <v>580</v>
+      </c>
+      <c r="B201" t="s">
+        <v>581</v>
+      </c>
+      <c r="C201" t="s">
+        <v>62</v>
+      </c>
+      <c r="D201" t="s">
+        <v>63</v>
+      </c>
+      <c r="E201" t="s">
+        <v>10</v>
+      </c>
+      <c r="F201" t="s">
+        <v>582</v>
+      </c>
+      <c r="G201" t="s">
+        <v>63</v>
+      </c>
+      <c r="H201" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="202" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A202" t="s">
+        <v>583</v>
+      </c>
+      <c r="B202" t="s">
+        <v>584</v>
+      </c>
+      <c r="C202" t="s">
+        <v>62</v>
+      </c>
+      <c r="D202" t="s">
+        <v>63</v>
+      </c>
+      <c r="E202" t="s">
+        <v>10</v>
+      </c>
+      <c r="F202" t="s">
+        <v>585</v>
+      </c>
+      <c r="G202" t="s">
+        <v>63</v>
+      </c>
+      <c r="H202" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="203" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A203" t="s">
+        <v>586</v>
+      </c>
+      <c r="B203" t="s">
+        <v>587</v>
+      </c>
+      <c r="C203" t="s">
+        <v>62</v>
+      </c>
+      <c r="D203" t="s">
+        <v>63</v>
+      </c>
+      <c r="E203" t="s">
+        <v>10</v>
+      </c>
+      <c r="F203" t="s">
+        <v>588</v>
+      </c>
+      <c r="G203" t="s">
+        <v>63</v>
+      </c>
+      <c r="H203" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="204" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A204" t="s">
+        <v>589</v>
+      </c>
+      <c r="B204" t="s">
+        <v>590</v>
+      </c>
+      <c r="C204" t="s">
+        <v>62</v>
+      </c>
+      <c r="D204" t="s">
+        <v>63</v>
+      </c>
+      <c r="E204" t="s">
+        <v>10</v>
+      </c>
+      <c r="F204" t="s">
+        <v>591</v>
+      </c>
+      <c r="G204" t="s">
+        <v>63</v>
+      </c>
+      <c r="H204" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="205" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A205" t="s">
+        <v>592</v>
+      </c>
+      <c r="B205" t="s">
+        <v>593</v>
+      </c>
+      <c r="C205" t="s">
+        <v>62</v>
+      </c>
+      <c r="D205" t="s">
+        <v>63</v>
+      </c>
+      <c r="E205" t="s">
+        <v>10</v>
+      </c>
+      <c r="F205" t="s">
+        <v>594</v>
+      </c>
+      <c r="G205" t="s">
+        <v>63</v>
+      </c>
+      <c r="H205" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="206" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A206" t="s">
+        <v>595</v>
+      </c>
+      <c r="B206" t="s">
+        <v>596</v>
+      </c>
+      <c r="C206" t="s">
+        <v>62</v>
+      </c>
+      <c r="D206" t="s">
+        <v>63</v>
+      </c>
+      <c r="E206" t="s">
+        <v>10</v>
+      </c>
+      <c r="F206" t="s">
+        <v>597</v>
+      </c>
+      <c r="G206" t="s">
+        <v>63</v>
+      </c>
+      <c r="H206" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="207" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A207" t="s">
+        <v>598</v>
+      </c>
+      <c r="B207" t="s">
+        <v>599</v>
+      </c>
+      <c r="C207" t="s">
+        <v>62</v>
+      </c>
+      <c r="D207" t="s">
+        <v>63</v>
+      </c>
+      <c r="E207" t="s">
+        <v>10</v>
+      </c>
+      <c r="F207" t="s">
+        <v>600</v>
+      </c>
+      <c r="G207" t="s">
+        <v>63</v>
+      </c>
+      <c r="H207" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="208" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A208" t="s">
+        <v>601</v>
+      </c>
+      <c r="B208" t="s">
+        <v>602</v>
+      </c>
+      <c r="C208" t="s">
+        <v>62</v>
+      </c>
+      <c r="D208" t="s">
+        <v>63</v>
+      </c>
+      <c r="E208" t="s">
+        <v>10</v>
+      </c>
+      <c r="F208" t="s">
+        <v>603</v>
+      </c>
+      <c r="G208" t="s">
+        <v>63</v>
+      </c>
+      <c r="H208" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="209" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A209" t="s">
+        <v>604</v>
+      </c>
+      <c r="B209" t="s">
+        <v>605</v>
+      </c>
+      <c r="C209" t="s">
+        <v>62</v>
+      </c>
+      <c r="D209" t="s">
+        <v>63</v>
+      </c>
+      <c r="E209" t="s">
+        <v>10</v>
+      </c>
+      <c r="F209" t="s">
+        <v>110</v>
+      </c>
+      <c r="G209" t="s">
+        <v>63</v>
+      </c>
+      <c r="H209" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="210" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A210" t="s">
+        <v>606</v>
+      </c>
+      <c r="B210" t="s">
+        <v>607</v>
+      </c>
+      <c r="C210" t="s">
+        <v>62</v>
+      </c>
+      <c r="D210" t="s">
+        <v>63</v>
+      </c>
+      <c r="E210" t="s">
+        <v>10</v>
+      </c>
+      <c r="F210" t="s">
+        <v>608</v>
+      </c>
+      <c r="G210" t="s">
+        <v>63</v>
+      </c>
+      <c r="H210" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="211" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A211" t="s">
+        <v>609</v>
+      </c>
+      <c r="B211" t="s">
+        <v>610</v>
+      </c>
+      <c r="C211" t="s">
+        <v>62</v>
+      </c>
+      <c r="D211" t="s">
+        <v>63</v>
+      </c>
+      <c r="E211" t="s">
+        <v>10</v>
+      </c>
+      <c r="F211" t="s">
+        <v>611</v>
+      </c>
+      <c r="G211" t="s">
+        <v>63</v>
+      </c>
+      <c r="H211" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="212" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A212" t="s">
+        <v>612</v>
+      </c>
+      <c r="B212" t="s">
+        <v>613</v>
+      </c>
+      <c r="C212" t="s">
+        <v>62</v>
+      </c>
+      <c r="D212" t="s">
+        <v>63</v>
+      </c>
+      <c r="E212" t="s">
+        <v>10</v>
+      </c>
+      <c r="F212" t="s">
+        <v>614</v>
+      </c>
+      <c r="G212" t="s">
+        <v>63</v>
+      </c>
+      <c r="H212" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="213" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A213" t="s">
+        <v>615</v>
+      </c>
+      <c r="B213" t="s">
+        <v>616</v>
+      </c>
+      <c r="C213" t="s">
+        <v>62</v>
+      </c>
+      <c r="D213" t="s">
+        <v>63</v>
+      </c>
+      <c r="E213" t="s">
+        <v>10</v>
+      </c>
+      <c r="F213" t="s">
+        <v>617</v>
+      </c>
+      <c r="G213" t="s">
+        <v>63</v>
+      </c>
+      <c r="H213" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="214" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A214" t="s">
+        <v>618</v>
+      </c>
+      <c r="B214" t="s">
+        <v>619</v>
+      </c>
+      <c r="C214" t="s">
+        <v>62</v>
+      </c>
+      <c r="D214" t="s">
+        <v>63</v>
+      </c>
+      <c r="E214" t="s">
+        <v>10</v>
+      </c>
+      <c r="F214" t="s">
+        <v>620</v>
+      </c>
+      <c r="G214" t="s">
+        <v>63</v>
+      </c>
+      <c r="H214" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="215" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A215" t="s">
+        <v>621</v>
+      </c>
+      <c r="B215" t="s">
+        <v>622</v>
+      </c>
+      <c r="C215" t="s">
+        <v>62</v>
+      </c>
+      <c r="D215" t="s">
+        <v>63</v>
+      </c>
+      <c r="E215" t="s">
+        <v>10</v>
+      </c>
+      <c r="F215" t="s">
+        <v>623</v>
+      </c>
+      <c r="G215" t="s">
+        <v>63</v>
+      </c>
+      <c r="H215" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="216" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A216" t="s">
+        <v>624</v>
+      </c>
+      <c r="B216" t="s">
+        <v>625</v>
+      </c>
+      <c r="C216" t="s">
+        <v>62</v>
+      </c>
+      <c r="D216" t="s">
+        <v>63</v>
+      </c>
+      <c r="E216" t="s">
+        <v>10</v>
+      </c>
+      <c r="F216" t="s">
+        <v>626</v>
+      </c>
+      <c r="G216" t="s">
+        <v>63</v>
+      </c>
+      <c r="H216" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="217" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A217" t="s">
+        <v>627</v>
+      </c>
+      <c r="B217" t="s">
+        <v>628</v>
+      </c>
+      <c r="C217" t="s">
+        <v>62</v>
+      </c>
+      <c r="D217" t="s">
+        <v>63</v>
+      </c>
+      <c r="E217" t="s">
+        <v>10</v>
+      </c>
+      <c r="F217" t="s">
+        <v>629</v>
+      </c>
+      <c r="G217" t="s">
+        <v>63</v>
+      </c>
+      <c r="H217" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="218" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A218" t="s">
+        <v>630</v>
+      </c>
+      <c r="B218" t="s">
+        <v>631</v>
+      </c>
+      <c r="C218" t="s">
+        <v>62</v>
+      </c>
+      <c r="D218" t="s">
+        <v>63</v>
+      </c>
+      <c r="E218" t="s">
+        <v>10</v>
+      </c>
+      <c r="F218" t="s">
+        <v>632</v>
+      </c>
+      <c r="G218" t="s">
+        <v>63</v>
+      </c>
+      <c r="H218" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="219" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A219" t="s">
+        <v>633</v>
+      </c>
+      <c r="B219" t="s">
+        <v>634</v>
+      </c>
+      <c r="C219" t="s">
+        <v>62</v>
+      </c>
+      <c r="D219" t="s">
+        <v>63</v>
+      </c>
+      <c r="E219" t="s">
+        <v>10</v>
+      </c>
+      <c r="F219" t="s">
+        <v>635</v>
+      </c>
+      <c r="G219" t="s">
+        <v>63</v>
+      </c>
+      <c r="H219" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="220" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A220" t="s">
+        <v>636</v>
+      </c>
+      <c r="B220" t="s">
+        <v>637</v>
+      </c>
+      <c r="C220" t="s">
+        <v>62</v>
+      </c>
+      <c r="D220" t="s">
+        <v>63</v>
+      </c>
+      <c r="E220" t="s">
+        <v>10</v>
+      </c>
+      <c r="F220" t="s">
+        <v>638</v>
+      </c>
+      <c r="G220" t="s">
+        <v>63</v>
+      </c>
+      <c r="H220" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="221" ht="14.4" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A221" t="s">
+        <v>639</v>
+      </c>
+      <c r="B221" t="s">
+        <v>640</v>
+      </c>
+      <c r="C221" t="s">
+        <v>62</v>
+      </c>
+      <c r="D221" t="s">
+        <v>63</v>
+      </c>
+      <c r="E221" t="s">
+        <v>10</v>
+      </c>
+      <c r="F221" t="s">
+        <v>641</v>
+      </c>
+      <c r="G221" t="s">
+        <v>63</v>
+      </c>
+      <c r="H221" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="222" ht="14.4" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A222" s="6"/>
@@ -6826,19 +11413,19 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>93</v>
+        <v>642</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>94</v>
+        <v>643</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>95</v>
+        <v>644</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>96</v>
+        <v>645</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>97</v>
+        <v>646</v>
       </c>
       <c r="H1" s="4"/>
       <c r="I1" s="4"/>
@@ -7047,7 +11634,7 @@
     </row>
     <row r="15" ht="15.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>98</v>
+        <v>647</v>
       </c>
       <c r="B15" s="6" t="e">
         <f>IF(A15="","",VLOOKUP(A15,'Master Data'!A:B,2,FALSE))</f>
@@ -11637,34 +16224,34 @@
         <v>6</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>93</v>
+        <v>642</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>96</v>
+        <v>645</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>97</v>
+        <v>646</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>99</v>
+        <v>648</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>100</v>
+        <v>649</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>101</v>
+        <v>650</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>102</v>
+        <v>651</v>
       </c>
       <c r="L1" s="5" t="s">
-        <v>103</v>
+        <v>652</v>
       </c>
       <c r="M1" s="5" t="s">
-        <v>104</v>
+        <v>653</v>
       </c>
       <c r="N1" s="5" t="s">
-        <v>105</v>
+        <v>654</v>
       </c>
       <c r="O1" s="6"/>
     </row>
@@ -21161,7 +25748,7 @@
   <sheetData>
     <row r="1" ht="15.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>106</v>
+        <v>655</v>
       </c>
       <c r="B1" s="10" t="s">
         <v>2</v>
@@ -21169,71 +25756,71 @@
     </row>
     <row r="2" ht="15.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
-        <v>107</v>
+        <v>656</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>108</v>
+        <v>657</v>
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
-        <v>109</v>
+        <v>658</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>110</v>
+        <v>659</v>
       </c>
     </row>
     <row r="4" ht="15.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>111</v>
+        <v>660</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>112</v>
+        <v>661</v>
       </c>
     </row>
     <row r="5" ht="15.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
-        <v>113</v>
+        <v>662</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>114</v>
+        <v>663</v>
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>115</v>
+        <v>664</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>116</v>
+        <v>665</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>117</v>
+        <v>666</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>118</v>
+        <v>667</v>
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
-        <v>119</v>
+        <v>668</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>120</v>
+        <v>669</v>
       </c>
     </row>
     <row r="9" ht="15.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
-        <v>121</v>
+        <v>670</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>122</v>
+        <v>671</v>
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
-        <v>123</v>
+        <v>672</v>
       </c>
       <c r="B10" s="9" t="s">
         <v>62</v>
@@ -21241,26 +25828,26 @@
     </row>
     <row r="11" ht="15.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
-        <v>124</v>
+        <v>673</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>125</v>
+        <v>674</v>
       </c>
     </row>
     <row r="12" ht="15.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
-        <v>126</v>
+        <v>675</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>127</v>
+        <v>676</v>
       </c>
     </row>
     <row r="13" ht="15.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
-        <v>128</v>
+        <v>677</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>129</v>
+        <v>678</v>
       </c>
     </row>
   </sheetData>
